--- a/results/模型评分与成本汇总.xlsx
+++ b/results/模型评分与成本汇总.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Task 1" sheetId="1" r:id="R6be2a5663a2041ab"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Task 2" sheetId="2" r:id="R4501040b256c4ac9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Task 3" sheetId="3" r:id="Rfe83d5f852314e79"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="综合汇总" sheetId="4" r:id="R0fe4d1f3c1494615"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Task 1" sheetId="1" r:id="R19d59aa9b7924f4d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Task 2" sheetId="2" r:id="R17b7bf357d3c4af6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Task 3" sheetId="3" r:id="R59e281f42be2427f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="综合汇总" sheetId="4" r:id="R1c705ce9ca5b443f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -86,12 +86,42 @@
       <x:name val="Arial"/>
     </x:font>
   </x:fonts>
-  <x:fills count="8">
+  <x:fills count="14">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="gray125"/>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF7E0C6E"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF4EFF4"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF7E0C6E"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF4EFF4"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF7E0C6E"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF4EFF4"/>
+      </x:patternFill>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
@@ -153,7 +183,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="83">
+  <x:cellXfs count="135">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -387,11 +417,200 @@
     <x:xf numFmtId="204" fontId="2" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="right" vertical="center"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="9" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="9" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="2" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="2" fillId="9" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="2" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="2" fillId="9" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="9" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="9" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="204" fontId="2" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="11" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="11" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="2" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="2" fillId="11" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="2" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="2" fillId="11" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="11" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="11" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="204" fontId="2" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="13" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="13" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="2" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="2" fillId="13" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="2" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="2" fillId="13" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="13" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="13" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="204" fontId="2" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="常规" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="4">
+  <x:dxfs count="7">
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF2D5828"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFE5EEE3"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF2D5828"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFE5EEE3"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF2D5828"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFE5EEE3"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
     <x:dxf>
       <x:font>
         <x:b/>
@@ -484,6 +703,72 @@
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:tx>
+            <c:v>6.1 Sol max</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="C43E66"/>
+            </a:solidFill>
+          </c:spPr>
+          <c:xVal>
+            <c:numLit>
+              <c:formatCode>General</c:formatCode>
+              <c:ptCount val="1"/>
+              <c:pt idx="0">
+                <c:v>0.6604860157849677</c:v>
+              </c:pt>
+            </c:numLit>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'综合汇总'!$P$6</c:f>
+              <c:numCache>
+                <c:formatCode>0</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>98</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>6.1 Sol xhigh</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="15746B"/>
+            </a:solidFill>
+          </c:spPr>
+          <c:xVal>
+            <c:numLit>
+              <c:formatCode>General</c:formatCode>
+              <c:ptCount val="1"/>
+              <c:pt idx="0">
+                <c:v>0.6121478383264869</c:v>
+              </c:pt>
+            </c:numLit>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'综合汇总'!$P$7</c:f>
+              <c:numCache>
+                <c:formatCode>0</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>97</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
             <c:v>Astra high</c:v>
           </c:tx>
           <c:spPr>
@@ -502,7 +787,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'综合汇总'!$P$6</c:f>
+              <c:f>'综合汇总'!$P$8</c:f>
               <c:numCache>
                 <c:formatCode>0</c:formatCode>
                 <c:ptCount val="1"/>
@@ -514,8 +799,8 @@
           </c:yVal>
         </c:ser>
         <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
+          <c:idx val="3"/>
+          <c:order val="3"/>
           <c:tx>
             <c:v>Sol max</c:v>
           </c:tx>
@@ -535,7 +820,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'综合汇总'!$P$7</c:f>
+              <c:f>'综合汇总'!$P$9</c:f>
               <c:numCache>
                 <c:formatCode>0</c:formatCode>
                 <c:ptCount val="1"/>
@@ -547,8 +832,8 @@
           </c:yVal>
         </c:ser>
         <c:ser>
-          <c:idx val="2"/>
-          <c:order val="2"/>
+          <c:idx val="4"/>
+          <c:order val="4"/>
           <c:tx>
             <c:v>Opus 5.5 xhigh</c:v>
           </c:tx>
@@ -568,7 +853,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'综合汇总'!$P$8</c:f>
+              <c:f>'综合汇总'!$P$10</c:f>
               <c:numCache>
                 <c:formatCode>0</c:formatCode>
                 <c:ptCount val="1"/>
@@ -580,8 +865,8 @@
           </c:yVal>
         </c:ser>
         <c:ser>
-          <c:idx val="3"/>
-          <c:order val="3"/>
+          <c:idx val="5"/>
+          <c:order val="5"/>
           <c:tx>
             <c:v>Sol xhigh</c:v>
           </c:tx>
@@ -601,7 +886,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'综合汇总'!$P$9</c:f>
+              <c:f>'综合汇总'!$P$11</c:f>
               <c:numCache>
                 <c:formatCode>0</c:formatCode>
                 <c:ptCount val="1"/>
@@ -613,8 +898,8 @@
           </c:yVal>
         </c:ser>
         <c:ser>
-          <c:idx val="4"/>
-          <c:order val="4"/>
+          <c:idx val="6"/>
+          <c:order val="6"/>
           <c:tx>
             <c:v>5.6 Sol xhigh</c:v>
           </c:tx>
@@ -634,7 +919,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'综合汇总'!$P$10</c:f>
+              <c:f>'综合汇总'!$P$12</c:f>
               <c:numCache>
                 <c:formatCode>0</c:formatCode>
                 <c:ptCount val="1"/>
@@ -646,8 +931,8 @@
           </c:yVal>
         </c:ser>
         <c:ser>
-          <c:idx val="5"/>
-          <c:order val="5"/>
+          <c:idx val="7"/>
+          <c:order val="7"/>
           <c:tx>
             <c:v>Luna max</c:v>
           </c:tx>
@@ -667,7 +952,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'综合汇总'!$P$11</c:f>
+              <c:f>'综合汇总'!$P$13</c:f>
               <c:numCache>
                 <c:formatCode>0</c:formatCode>
                 <c:ptCount val="1"/>
@@ -679,8 +964,8 @@
           </c:yVal>
         </c:ser>
         <c:ser>
-          <c:idx val="6"/>
-          <c:order val="6"/>
+          <c:idx val="8"/>
+          <c:order val="8"/>
           <c:tx>
             <c:v>DeepSeek Flash max</c:v>
           </c:tx>
@@ -700,7 +985,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'综合汇总'!$P$12</c:f>
+              <c:f>'综合汇总'!$P$14</c:f>
               <c:numCache>
                 <c:formatCode>0</c:formatCode>
                 <c:ptCount val="1"/>
@@ -712,8 +997,8 @@
           </c:yVal>
         </c:ser>
         <c:ser>
-          <c:idx val="7"/>
-          <c:order val="7"/>
+          <c:idx val="9"/>
+          <c:order val="9"/>
           <c:tx>
             <c:v>Grok 4.7 high</c:v>
           </c:tx>
@@ -733,7 +1018,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'综合汇总'!$P$13</c:f>
+              <c:f>'综合汇总'!$P$15</c:f>
               <c:numCache>
                 <c:formatCode>0</c:formatCode>
                 <c:ptCount val="1"/>
@@ -906,7 +1191,7 @@
                 <a:ea typeface="Arial"/>
                 <a:cs typeface="Arial"/>
               </a:rPr>
-              <a:t>第 1 题：得分与实际成本</a:t>
+              <a:t>第 1 题：得分与记录成本</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -933,6 +1218,72 @@
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:tx>
+            <c:v>6.1 Sol max</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="C43E66"/>
+            </a:solidFill>
+          </c:spPr>
+          <c:xVal>
+            <c:numLit>
+              <c:formatCode>General</c:formatCode>
+              <c:ptCount val="1"/>
+              <c:pt idx="0">
+                <c:v>0.25406445291433793</c:v>
+              </c:pt>
+            </c:numLit>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'综合汇总'!$P$19</c:f>
+              <c:numCache>
+                <c:formatCode>0</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>97</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>6.1 Sol xhigh</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="15746B"/>
+            </a:solidFill>
+          </c:spPr>
+          <c:xVal>
+            <c:numLit>
+              <c:formatCode>General</c:formatCode>
+              <c:ptCount val="1"/>
+              <c:pt idx="0">
+                <c:v>0.20736503746907187</c:v>
+              </c:pt>
+            </c:numLit>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'综合汇总'!$P$20</c:f>
+              <c:numCache>
+                <c:formatCode>0</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>95</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
             <c:v>Sol max</c:v>
           </c:tx>
           <c:spPr>
@@ -951,7 +1302,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'综合汇总'!$P$19</c:f>
+              <c:f>'综合汇总'!$P$21</c:f>
               <c:numCache>
                 <c:formatCode>0</c:formatCode>
                 <c:ptCount val="1"/>
@@ -963,8 +1314,8 @@
           </c:yVal>
         </c:ser>
         <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
+          <c:idx val="3"/>
+          <c:order val="3"/>
           <c:tx>
             <c:v>Astra high</c:v>
           </c:tx>
@@ -984,7 +1335,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'综合汇总'!$P$20</c:f>
+              <c:f>'综合汇总'!$P$22</c:f>
               <c:numCache>
                 <c:formatCode>0</c:formatCode>
                 <c:ptCount val="1"/>
@@ -996,8 +1347,8 @@
           </c:yVal>
         </c:ser>
         <c:ser>
-          <c:idx val="2"/>
-          <c:order val="2"/>
+          <c:idx val="4"/>
+          <c:order val="4"/>
           <c:tx>
             <c:v>Opus 5.5 xhigh</c:v>
           </c:tx>
@@ -1017,7 +1368,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'综合汇总'!$P$21</c:f>
+              <c:f>'综合汇总'!$P$23</c:f>
               <c:numCache>
                 <c:formatCode>0</c:formatCode>
                 <c:ptCount val="1"/>
@@ -1029,8 +1380,8 @@
           </c:yVal>
         </c:ser>
         <c:ser>
-          <c:idx val="3"/>
-          <c:order val="3"/>
+          <c:idx val="5"/>
+          <c:order val="5"/>
           <c:tx>
             <c:v>5.6 Sol xhigh</c:v>
           </c:tx>
@@ -1050,7 +1401,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'综合汇总'!$P$22</c:f>
+              <c:f>'综合汇总'!$P$24</c:f>
               <c:numCache>
                 <c:formatCode>0</c:formatCode>
                 <c:ptCount val="1"/>
@@ -1062,8 +1413,8 @@
           </c:yVal>
         </c:ser>
         <c:ser>
-          <c:idx val="4"/>
-          <c:order val="4"/>
+          <c:idx val="6"/>
+          <c:order val="6"/>
           <c:tx>
             <c:v>Sol xhigh</c:v>
           </c:tx>
@@ -1083,7 +1434,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'综合汇总'!$P$23</c:f>
+              <c:f>'综合汇总'!$P$25</c:f>
               <c:numCache>
                 <c:formatCode>0</c:formatCode>
                 <c:ptCount val="1"/>
@@ -1095,8 +1446,8 @@
           </c:yVal>
         </c:ser>
         <c:ser>
-          <c:idx val="5"/>
-          <c:order val="5"/>
+          <c:idx val="7"/>
+          <c:order val="7"/>
           <c:tx>
             <c:v>Luna max</c:v>
           </c:tx>
@@ -1116,7 +1467,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'综合汇总'!$P$24</c:f>
+              <c:f>'综合汇总'!$P$26</c:f>
               <c:numCache>
                 <c:formatCode>0</c:formatCode>
                 <c:ptCount val="1"/>
@@ -1128,8 +1479,8 @@
           </c:yVal>
         </c:ser>
         <c:ser>
-          <c:idx val="6"/>
-          <c:order val="6"/>
+          <c:idx val="8"/>
+          <c:order val="8"/>
           <c:tx>
             <c:v>DeepSeek Flash max</c:v>
           </c:tx>
@@ -1149,7 +1500,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'综合汇总'!$P$25</c:f>
+              <c:f>'综合汇总'!$P$27</c:f>
               <c:numCache>
                 <c:formatCode>0</c:formatCode>
                 <c:ptCount val="1"/>
@@ -1161,8 +1512,8 @@
           </c:yVal>
         </c:ser>
         <c:ser>
-          <c:idx val="7"/>
-          <c:order val="7"/>
+          <c:idx val="9"/>
+          <c:order val="9"/>
           <c:tx>
             <c:v>Grok 4.7 high</c:v>
           </c:tx>
@@ -1182,7 +1533,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'综合汇总'!$P$26</c:f>
+              <c:f>'综合汇总'!$P$28</c:f>
               <c:numCache>
                 <c:formatCode>0</c:formatCode>
                 <c:ptCount val="1"/>
@@ -1355,7 +1706,7 @@
                 <a:ea typeface="Arial"/>
                 <a:cs typeface="Arial"/>
               </a:rPr>
-              <a:t>第 2 题：得分与实际成本</a:t>
+              <a:t>第 2 题：得分与记录成本</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -1382,6 +1733,72 @@
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:tx>
+            <c:v>6.1 Sol xhigh</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="15746B"/>
+            </a:solidFill>
+          </c:spPr>
+          <c:xVal>
+            <c:numLit>
+              <c:formatCode>General</c:formatCode>
+              <c:ptCount val="1"/>
+              <c:pt idx="0">
+                <c:v>0.04571405894086761</c:v>
+              </c:pt>
+            </c:numLit>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'综合汇总'!$P$31</c:f>
+              <c:numCache>
+                <c:formatCode>0</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>98</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>6.1 Sol max</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="C43E66"/>
+            </a:solidFill>
+          </c:spPr>
+          <c:xVal>
+            <c:numLit>
+              <c:formatCode>General</c:formatCode>
+              <c:ptCount val="1"/>
+              <c:pt idx="0">
+                <c:v>0.05690485133647255</c:v>
+              </c:pt>
+            </c:numLit>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'综合汇总'!$P$32</c:f>
+              <c:numCache>
+                <c:formatCode>0</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>98</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
             <c:v>Astra high</c:v>
           </c:tx>
           <c:spPr>
@@ -1400,7 +1817,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'综合汇总'!$P$31</c:f>
+              <c:f>'综合汇总'!$P$33</c:f>
               <c:numCache>
                 <c:formatCode>0</c:formatCode>
                 <c:ptCount val="1"/>
@@ -1412,8 +1829,8 @@
           </c:yVal>
         </c:ser>
         <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
+          <c:idx val="3"/>
+          <c:order val="3"/>
           <c:tx>
             <c:v>Sol max</c:v>
           </c:tx>
@@ -1433,7 +1850,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'综合汇总'!$P$32</c:f>
+              <c:f>'综合汇总'!$P$34</c:f>
               <c:numCache>
                 <c:formatCode>0</c:formatCode>
                 <c:ptCount val="1"/>
@@ -1445,8 +1862,8 @@
           </c:yVal>
         </c:ser>
         <c:ser>
-          <c:idx val="2"/>
-          <c:order val="2"/>
+          <c:idx val="4"/>
+          <c:order val="4"/>
           <c:tx>
             <c:v>Opus 5.5 xhigh</c:v>
           </c:tx>
@@ -1466,7 +1883,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'综合汇总'!$P$33</c:f>
+              <c:f>'综合汇总'!$P$35</c:f>
               <c:numCache>
                 <c:formatCode>0</c:formatCode>
                 <c:ptCount val="1"/>
@@ -1478,8 +1895,8 @@
           </c:yVal>
         </c:ser>
         <c:ser>
-          <c:idx val="3"/>
-          <c:order val="3"/>
+          <c:idx val="5"/>
+          <c:order val="5"/>
           <c:tx>
             <c:v>Sol xhigh</c:v>
           </c:tx>
@@ -1499,7 +1916,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'综合汇总'!$P$34</c:f>
+              <c:f>'综合汇总'!$P$36</c:f>
               <c:numCache>
                 <c:formatCode>0</c:formatCode>
                 <c:ptCount val="1"/>
@@ -1511,8 +1928,8 @@
           </c:yVal>
         </c:ser>
         <c:ser>
-          <c:idx val="4"/>
-          <c:order val="4"/>
+          <c:idx val="6"/>
+          <c:order val="6"/>
           <c:tx>
             <c:v>5.6 Sol xhigh</c:v>
           </c:tx>
@@ -1532,7 +1949,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'综合汇总'!$P$35</c:f>
+              <c:f>'综合汇总'!$P$37</c:f>
               <c:numCache>
                 <c:formatCode>0</c:formatCode>
                 <c:ptCount val="1"/>
@@ -1544,8 +1961,8 @@
           </c:yVal>
         </c:ser>
         <c:ser>
-          <c:idx val="5"/>
-          <c:order val="5"/>
+          <c:idx val="7"/>
+          <c:order val="7"/>
           <c:tx>
             <c:v>Luna max</c:v>
           </c:tx>
@@ -1565,7 +1982,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'综合汇总'!$P$36</c:f>
+              <c:f>'综合汇总'!$P$38</c:f>
               <c:numCache>
                 <c:formatCode>0</c:formatCode>
                 <c:ptCount val="1"/>
@@ -1577,8 +1994,8 @@
           </c:yVal>
         </c:ser>
         <c:ser>
-          <c:idx val="6"/>
-          <c:order val="6"/>
+          <c:idx val="8"/>
+          <c:order val="8"/>
           <c:tx>
             <c:v>DeepSeek Flash max</c:v>
           </c:tx>
@@ -1598,7 +2015,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'综合汇总'!$P$37</c:f>
+              <c:f>'综合汇总'!$P$39</c:f>
               <c:numCache>
                 <c:formatCode>0</c:formatCode>
                 <c:ptCount val="1"/>
@@ -1610,8 +2027,8 @@
           </c:yVal>
         </c:ser>
         <c:ser>
-          <c:idx val="7"/>
-          <c:order val="7"/>
+          <c:idx val="9"/>
+          <c:order val="9"/>
           <c:tx>
             <c:v>Grok 4.7 high</c:v>
           </c:tx>
@@ -1631,7 +2048,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'综合汇总'!$P$38</c:f>
+              <c:f>'综合汇总'!$P$40</c:f>
               <c:numCache>
                 <c:formatCode>0</c:formatCode>
                 <c:ptCount val="1"/>
@@ -1804,7 +2221,7 @@
                 <a:ea typeface="Arial"/>
                 <a:cs typeface="Arial"/>
               </a:rPr>
-              <a:t>第 3 题：得分与实际成本</a:t>
+              <a:t>第 3 题：得分与记录成本</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -1831,6 +2248,39 @@
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:tx>
+            <c:v>6.1 Sol max</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="C43E66"/>
+            </a:solidFill>
+          </c:spPr>
+          <c:xVal>
+            <c:numLit>
+              <c:formatCode>General</c:formatCode>
+              <c:ptCount val="1"/>
+              <c:pt idx="0">
+                <c:v>0.21510858105309322</c:v>
+              </c:pt>
+            </c:numLit>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'综合汇总'!$P$43</c:f>
+              <c:numCache>
+                <c:formatCode>0</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>99</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
             <c:v>Astra high</c:v>
           </c:tx>
           <c:spPr>
@@ -1849,7 +2299,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'综合汇总'!$P$43</c:f>
+              <c:f>'综合汇总'!$P$44</c:f>
               <c:numCache>
                 <c:formatCode>0</c:formatCode>
                 <c:ptCount val="1"/>
@@ -1861,8 +2311,41 @@
           </c:yVal>
         </c:ser>
         <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:v>6.1 Sol xhigh</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="15746B"/>
+            </a:solidFill>
+          </c:spPr>
+          <c:xVal>
+            <c:numLit>
+              <c:formatCode>General</c:formatCode>
+              <c:ptCount val="1"/>
+              <c:pt idx="0">
+                <c:v>0.13703745478951265</c:v>
+              </c:pt>
+            </c:numLit>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'综合汇总'!$P$45</c:f>
+              <c:numCache>
+                <c:formatCode>0</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>98</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
           <c:tx>
             <c:v>Sol max</c:v>
           </c:tx>
@@ -1882,7 +2365,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'综合汇总'!$P$44</c:f>
+              <c:f>'综合汇总'!$P$46</c:f>
               <c:numCache>
                 <c:formatCode>0</c:formatCode>
                 <c:ptCount val="1"/>
@@ -1894,8 +2377,8 @@
           </c:yVal>
         </c:ser>
         <c:ser>
-          <c:idx val="2"/>
-          <c:order val="2"/>
+          <c:idx val="4"/>
+          <c:order val="4"/>
           <c:tx>
             <c:v>Sol xhigh</c:v>
           </c:tx>
@@ -1915,7 +2398,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'综合汇总'!$P$45</c:f>
+              <c:f>'综合汇总'!$P$47</c:f>
               <c:numCache>
                 <c:formatCode>0</c:formatCode>
                 <c:ptCount val="1"/>
@@ -1927,8 +2410,8 @@
           </c:yVal>
         </c:ser>
         <c:ser>
-          <c:idx val="3"/>
-          <c:order val="3"/>
+          <c:idx val="5"/>
+          <c:order val="5"/>
           <c:tx>
             <c:v>5.6 Sol xhigh</c:v>
           </c:tx>
@@ -1948,7 +2431,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'综合汇总'!$P$46</c:f>
+              <c:f>'综合汇总'!$P$48</c:f>
               <c:numCache>
                 <c:formatCode>0</c:formatCode>
                 <c:ptCount val="1"/>
@@ -1960,8 +2443,8 @@
           </c:yVal>
         </c:ser>
         <c:ser>
-          <c:idx val="4"/>
-          <c:order val="4"/>
+          <c:idx val="6"/>
+          <c:order val="6"/>
           <c:tx>
             <c:v>Opus 5.5 xhigh</c:v>
           </c:tx>
@@ -1981,7 +2464,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'综合汇总'!$P$47</c:f>
+              <c:f>'综合汇总'!$P$49</c:f>
               <c:numCache>
                 <c:formatCode>0</c:formatCode>
                 <c:ptCount val="1"/>
@@ -1993,8 +2476,8 @@
           </c:yVal>
         </c:ser>
         <c:ser>
-          <c:idx val="5"/>
-          <c:order val="5"/>
+          <c:idx val="7"/>
+          <c:order val="7"/>
           <c:tx>
             <c:v>Luna max</c:v>
           </c:tx>
@@ -2014,7 +2497,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'综合汇总'!$P$48</c:f>
+              <c:f>'综合汇总'!$P$50</c:f>
               <c:numCache>
                 <c:formatCode>0</c:formatCode>
                 <c:ptCount val="1"/>
@@ -2026,8 +2509,8 @@
           </c:yVal>
         </c:ser>
         <c:ser>
-          <c:idx val="6"/>
-          <c:order val="6"/>
+          <c:idx val="8"/>
+          <c:order val="8"/>
           <c:tx>
             <c:v>Grok 4.7 high</c:v>
           </c:tx>
@@ -2047,7 +2530,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'综合汇总'!$P$49</c:f>
+              <c:f>'综合汇总'!$P$51</c:f>
               <c:numCache>
                 <c:formatCode>0</c:formatCode>
                 <c:ptCount val="1"/>
@@ -2059,8 +2542,8 @@
           </c:yVal>
         </c:ser>
         <c:ser>
-          <c:idx val="7"/>
-          <c:order val="7"/>
+          <c:idx val="9"/>
+          <c:order val="9"/>
           <c:tx>
             <c:v>DeepSeek Flash max</c:v>
           </c:tx>
@@ -2080,7 +2563,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'综合汇总'!$P$50</c:f>
+              <c:f>'综合汇总'!$P$52</c:f>
               <c:numCache>
                 <c:formatCode>0</c:formatCode>
                 <c:ptCount val="1"/>
@@ -2242,13 +2725,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>41</xdr:row>
+      <xdr:row>47</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>63</xdr:row>
+      <xdr:row>69</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -2262,7 +2745,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R615f541631aa4c6a"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rad45c2cb192b486a"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2272,13 +2755,13 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>41</xdr:row>
+      <xdr:row>47</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>63</xdr:row>
+      <xdr:row>69</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -2292,7 +2775,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rb1cada467d924104"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R7c5c233aa7eb4663"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2302,13 +2785,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>64</xdr:row>
+      <xdr:row>70</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>86</xdr:row>
+      <xdr:row>92</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -2322,7 +2805,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rc62ac7fba53a4ff2"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R5d4f38fc2c1d4686"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2332,13 +2815,13 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>64</xdr:row>
+      <xdr:row>70</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>86</xdr:row>
+      <xdr:row>92</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -2352,7 +2835,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Racdd3c8b6db849ff"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rd26900fb087a483e"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2688,6 +3171,34 @@
         <x:v>47</x:v>
       </x:c>
     </x:row>
+    <x:row r="10" ht="21" customHeight="1">
+      <x:c r="A10" s="44" t="str">
+        <x:v>s2_1a</x:v>
+      </x:c>
+      <x:c r="B10" s="44" t="str">
+        <x:v>GPT-6.1 Sol xhigh</x:v>
+      </x:c>
+      <x:c r="C10" s="45" t="n">
+        <x:v>1.612</x:v>
+      </x:c>
+      <x:c r="D10" s="46" t="n">
+        <x:v>95</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="21" customHeight="1">
+      <x:c r="A11" s="44" t="str">
+        <x:v>s2_1b</x:v>
+      </x:c>
+      <x:c r="B11" s="44" t="str">
+        <x:v>GPT-6.1 Sol max</x:v>
+      </x:c>
+      <x:c r="C11" s="45" t="n">
+        <x:v>1.795</x:v>
+      </x:c>
+      <x:c r="D11" s="46" t="n">
+        <x:v>97</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -2829,6 +3340,34 @@
         <x:v>75</x:v>
       </x:c>
     </x:row>
+    <x:row r="10" ht="21" customHeight="1">
+      <x:c r="A10" s="44" t="str">
+        <x:v>s2_2a</x:v>
+      </x:c>
+      <x:c r="B10" s="44" t="str">
+        <x:v>GPT-6.1 Sol xhigh</x:v>
+      </x:c>
+      <x:c r="C10" s="45" t="n">
+        <x:v>1.111</x:v>
+      </x:c>
+      <x:c r="D10" s="46" t="n">
+        <x:v>98</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="21" customHeight="1">
+      <x:c r="A11" s="44" t="str">
+        <x:v>s2_2b</x:v>
+      </x:c>
+      <x:c r="B11" s="44" t="str">
+        <x:v>GPT-6.1 Sol max</x:v>
+      </x:c>
+      <x:c r="C11" s="45" t="n">
+        <x:v>1.14</x:v>
+      </x:c>
+      <x:c r="D11" s="46" t="n">
+        <x:v>98</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -2970,6 +3509,34 @@
         <x:v>54</x:v>
       </x:c>
     </x:row>
+    <x:row r="10" ht="21" customHeight="1">
+      <x:c r="A10" s="44" t="str">
+        <x:v>s2_3a</x:v>
+      </x:c>
+      <x:c r="B10" s="44" t="str">
+        <x:v>GPT-6.1 Sol xhigh</x:v>
+      </x:c>
+      <x:c r="C10" s="45" t="n">
+        <x:v>1.371</x:v>
+      </x:c>
+      <x:c r="D10" s="46" t="n">
+        <x:v>98</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="21" customHeight="1">
+      <x:c r="A11" s="44" t="str">
+        <x:v>s2_3b</x:v>
+      </x:c>
+      <x:c r="B11" s="44" t="str">
+        <x:v>GPT-6.1 Sol max</x:v>
+      </x:c>
+      <x:c r="C11" s="45" t="n">
+        <x:v>1.641</x:v>
+      </x:c>
+      <x:c r="D11" s="46" t="n">
+        <x:v>99</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -2979,8 +3546,8 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="28.75" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="9" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="29.3799991607666" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="9.380000114440918" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="11" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="11" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="11" hidden="0" customWidth="1"/>
@@ -2988,14 +3555,14 @@
     <x:col min="7" max="7" width="11" hidden="0" customWidth="1"/>
     <x:col min="8" max="8" width="12.5" hidden="0" customWidth="1"/>
     <x:col min="9" max="9" width="12.5" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="12.5" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="14.75" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="13.130000114440918" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="15" hidden="0" customWidth="1"/>
     <x:col min="12" max="12" width="2.5" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="27.75" customHeight="1">
       <x:c r="A1" s="3" t="str">
-        <x:v>三道数学物理研究题：完整表现与实际成本</x:v>
+        <x:v>三道理论物理研究题：完整表现与记录成本</x:v>
       </x:c>
       <x:c r="B1" s="3"/>
       <x:c r="C1" s="3"/>
@@ -3021,7 +3588,7 @@
     </x:row>
     <x:row r="2" ht="21" customHeight="1">
       <x:c r="A2" s="4" t="str">
-        <x:v>2026-09-23 · 8 个模型配置 × 3 题 = 24 项有效结果 · 每题 100 分 · 美元成本 · 三题等权</x:v>
+        <x:v>2026-09-30 · 10 个模型配置 × 3 题 = 30 项采用结果 · 每题 100 分 · 美元参考成本 · 三题等权</x:v>
       </x:c>
       <x:c r="B2" s="4"/>
       <x:c r="C2" s="4"/>
@@ -3047,7 +3614,7 @@
     </x:row>
     <x:row r="3" ht="21" customHeight="1">
       <x:c r="A3" s="4" t="str">
-        <x:v>Opus 5.5 xhigh 采用补充报告的评分；三题成本沿用原记录，各计一次。身份揭晓后沿用已完成的评分。</x:v>
+        <x:v>分数沿用身份与用量揭晓前的评阅；新增 GPT-6.1 Sol xhigh / max，成本由参与者提供。</x:v>
       </x:c>
       <x:c r="B3" s="4"/>
       <x:c r="C3" s="4"/>
@@ -3096,37 +3663,37 @@
       <x:c r="V4" s="2"/>
     </x:row>
     <x:row r="5" ht="35" customHeight="1">
-      <x:c r="A5" s="69" t="str">
+      <x:c r="A5" s="120" t="str">
         <x:v>模型配置</x:v>
       </x:c>
-      <x:c r="B5" s="69" t="str">
+      <x:c r="B5" s="120" t="str">
         <x:v>第 1 题</x:v>
       </x:c>
-      <x:c r="C5" s="69" t="str">
+      <x:c r="C5" s="120" t="str">
         <x:v>成本 USD</x:v>
       </x:c>
-      <x:c r="D5" s="69" t="str">
+      <x:c r="D5" s="120" t="str">
         <x:v>第 2 题</x:v>
       </x:c>
-      <x:c r="E5" s="69" t="str">
+      <x:c r="E5" s="120" t="str">
         <x:v>成本 USD</x:v>
       </x:c>
-      <x:c r="F5" s="69" t="str">
+      <x:c r="F5" s="120" t="str">
         <x:v>第 3 题</x:v>
       </x:c>
-      <x:c r="G5" s="69" t="str">
+      <x:c r="G5" s="120" t="str">
         <x:v>成本 USD</x:v>
       </x:c>
-      <x:c r="H5" s="69" t="str">
+      <x:c r="H5" s="120" t="str">
         <x:v>总分 /300</x:v>
       </x:c>
-      <x:c r="I5" s="69" t="str">
+      <x:c r="I5" s="120" t="str">
         <x:v>均分 /100</x:v>
       </x:c>
-      <x:c r="J5" s="69" t="str">
+      <x:c r="J5" s="120" t="str">
         <x:v>总成本 USD</x:v>
       </x:c>
-      <x:c r="K5" s="69" t="str">
+      <x:c r="K5" s="120" t="str">
         <x:v>最弱一题</x:v>
       </x:c>
       <x:c r="L5" s="2"/>
@@ -3149,60 +3716,60 @@
     </x:row>
     <x:row r="6" ht="21" customHeight="1">
       <x:c r="A6" s="2" t="str">
-        <x:v>GPT-6 Astra high</x:v>
+        <x:v>GPT-6.1 Sol max</x:v>
       </x:c>
       <x:c r="B6" s="12" t="n">
-        <x:f>'Task 1'!D3</x:f>
-        <x:v>92</x:v>
+        <x:f>'Task 1'!D11</x:f>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C6" s="20" t="n">
-        <x:f>'Task 1'!C3</x:f>
-        <x:v>5.614</x:v>
+        <x:f>'Task 1'!C11</x:f>
+        <x:v>1.795</x:v>
       </x:c>
       <x:c r="D6" s="12" t="n">
-        <x:f>'Task 2'!D6</x:f>
-        <x:v>97</x:v>
+        <x:f>'Task 2'!D11</x:f>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="E6" s="20" t="n">
-        <x:f>'Task 2'!C6</x:f>
-        <x:v>4.55</x:v>
+        <x:f>'Task 2'!C11</x:f>
+        <x:v>1.14</x:v>
       </x:c>
       <x:c r="F6" s="12" t="n">
-        <x:f>'Task 3'!D6</x:f>
-        <x:v>98</x:v>
+        <x:f>'Task 3'!D11</x:f>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="G6" s="20" t="n">
-        <x:f>'Task 3'!C6</x:f>
-        <x:v>4.206</x:v>
+        <x:f>'Task 3'!C11</x:f>
+        <x:v>1.641</x:v>
       </x:c>
       <x:c r="H6" s="12" t="n">
         <x:f>SUM(B6,D6,F6)</x:f>
-        <x:v>287</x:v>
+        <x:v>294</x:v>
       </x:c>
       <x:c r="I6" s="23" t="n">
         <x:f>H6/3</x:f>
-        <x:v>95.66666666666667</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="J6" s="20" t="n">
         <x:f>SUM(C6,E6,G6)</x:f>
-        <x:v>14.370000000000001</x:v>
+        <x:v>4.576</x:v>
       </x:c>
       <x:c r="K6" s="12" t="n">
         <x:f>MIN(B6,D6,F6)</x:f>
-        <x:v>92</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="L6" s="2"/>
       <x:c r="M6" s="2"/>
       <x:c r="N6" s="2" t="str">
-        <x:v>GPT-6 Astra high</x:v>
+        <x:v>GPT-6.1 Sol max</x:v>
       </x:c>
       <x:c r="O6" s="2" t="n">
         <x:f>LOG10(J6)</x:f>
-        <x:v>1.15745676813423</x:v>
+        <x:v>0.660486015784968</x:v>
       </x:c>
       <x:c r="P6" s="2" t="n">
         <x:f>I6</x:f>
-        <x:v>95.66666666666667</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="Q6" s="2"/>
       <x:c r="R6" s="2"/>
@@ -3212,61 +3779,61 @@
       <x:c r="V6" s="2"/>
     </x:row>
     <x:row r="7" ht="21" customHeight="1">
-      <x:c r="A7" s="70" t="str">
-        <x:v>GPT-6 Sol max</x:v>
-      </x:c>
-      <x:c r="B7" s="71" t="n">
-        <x:f>'Task 1'!D7</x:f>
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="C7" s="74" t="n">
-        <x:f>'Task 1'!C7</x:f>
-        <x:v>4.118</x:v>
-      </x:c>
-      <x:c r="D7" s="71" t="n">
-        <x:f>'Task 2'!D4</x:f>
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="E7" s="74" t="n">
-        <x:f>'Task 2'!C4</x:f>
-        <x:v>1.814</x:v>
-      </x:c>
-      <x:c r="F7" s="71" t="n">
-        <x:f>'Task 3'!D4</x:f>
+      <x:c r="A7" s="121" t="str">
+        <x:v>GPT-6.1 Sol xhigh</x:v>
+      </x:c>
+      <x:c r="B7" s="122" t="n">
+        <x:f>'Task 1'!D10</x:f>
         <x:v>95</x:v>
       </x:c>
-      <x:c r="G7" s="74" t="n">
-        <x:f>'Task 3'!C4</x:f>
-        <x:v>2.32</x:v>
-      </x:c>
-      <x:c r="H7" s="71" t="n">
+      <x:c r="C7" s="125" t="n">
+        <x:f>'Task 1'!C10</x:f>
+        <x:v>1.612</x:v>
+      </x:c>
+      <x:c r="D7" s="122" t="n">
+        <x:f>'Task 2'!D10</x:f>
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="E7" s="125" t="n">
+        <x:f>'Task 2'!C10</x:f>
+        <x:v>1.111</x:v>
+      </x:c>
+      <x:c r="F7" s="122" t="n">
+        <x:f>'Task 3'!D10</x:f>
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="G7" s="125" t="n">
+        <x:f>'Task 3'!C10</x:f>
+        <x:v>1.371</x:v>
+      </x:c>
+      <x:c r="H7" s="122" t="n">
         <x:f>SUM(B7,D7,F7)</x:f>
-        <x:v>283</x:v>
-      </x:c>
-      <x:c r="I7" s="76" t="n">
+        <x:v>291</x:v>
+      </x:c>
+      <x:c r="I7" s="127" t="n">
         <x:f>H7/3</x:f>
-        <x:v>94.33333333333333</x:v>
-      </x:c>
-      <x:c r="J7" s="74" t="n">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="J7" s="125" t="n">
         <x:f>SUM(C7,E7,G7)</x:f>
-        <x:v>8.252</x:v>
-      </x:c>
-      <x:c r="K7" s="71" t="n">
+        <x:v>4.093999999999999</x:v>
+      </x:c>
+      <x:c r="K7" s="122" t="n">
         <x:f>MIN(B7,D7,F7)</x:f>
-        <x:v>94</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="L7" s="2"/>
       <x:c r="M7" s="2"/>
       <x:c r="N7" s="2" t="str">
-        <x:v>GPT-6 Sol max</x:v>
+        <x:v>GPT-6.1 Sol xhigh</x:v>
       </x:c>
       <x:c r="O7" s="2" t="n">
         <x:f>LOG10(J7)</x:f>
-        <x:v>0.916559219301114</x:v>
+        <x:v>0.612147838326487</x:v>
       </x:c>
       <x:c r="P7" s="2" t="n">
         <x:f>I7</x:f>
-        <x:v>94.33333333333333</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="Q7" s="2"/>
       <x:c r="R7" s="2"/>
@@ -3277,60 +3844,60 @@
     </x:row>
     <x:row r="8" ht="21" customHeight="1">
       <x:c r="A8" s="2" t="str">
-        <x:v>Opus 5.5 xhigh</x:v>
+        <x:v>GPT-6 Astra high</x:v>
       </x:c>
       <x:c r="B8" s="12" t="n">
-        <x:f>'Task 1'!D6</x:f>
-        <x:v>87</x:v>
+        <x:f>'Task 1'!D3</x:f>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C8" s="20" t="n">
-        <x:f>'Task 1'!C6</x:f>
-        <x:v>24.056</x:v>
+        <x:f>'Task 1'!C3</x:f>
+        <x:v>5.614</x:v>
       </x:c>
       <x:c r="D8" s="12" t="n">
-        <x:f>'Task 2'!D8</x:f>
-        <x:v>93</x:v>
+        <x:f>'Task 2'!D6</x:f>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="E8" s="20" t="n">
-        <x:f>'Task 2'!C8</x:f>
-        <x:v>12.33</x:v>
+        <x:f>'Task 2'!C6</x:f>
+        <x:v>4.55</x:v>
       </x:c>
       <x:c r="F8" s="12" t="n">
-        <x:f>'Task 3'!D8</x:f>
-        <x:v>81</x:v>
+        <x:f>'Task 3'!D6</x:f>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="G8" s="20" t="n">
-        <x:f>'Task 3'!C8</x:f>
-        <x:v>14.384</x:v>
+        <x:f>'Task 3'!C6</x:f>
+        <x:v>4.206</x:v>
       </x:c>
       <x:c r="H8" s="12" t="n">
         <x:f>SUM(B8,D8,F8)</x:f>
-        <x:v>261</x:v>
+        <x:v>287</x:v>
       </x:c>
       <x:c r="I8" s="23" t="n">
         <x:f>H8/3</x:f>
-        <x:v>87</x:v>
+        <x:v>95.66666666666667</x:v>
       </x:c>
       <x:c r="J8" s="20" t="n">
         <x:f>SUM(C8,E8,G8)</x:f>
-        <x:v>50.77</x:v>
+        <x:v>14.370000000000001</x:v>
       </x:c>
       <x:c r="K8" s="12" t="n">
         <x:f>MIN(B8,D8,F8)</x:f>
-        <x:v>81</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="L8" s="2"/>
       <x:c r="M8" s="2"/>
       <x:c r="N8" s="2" t="str">
-        <x:v>Opus 5.5 xhigh</x:v>
+        <x:v>GPT-6 Astra high</x:v>
       </x:c>
       <x:c r="O8" s="2" t="n">
         <x:f>LOG10(J8)</x:f>
-        <x:v>1.7056071634046</x:v>
+        <x:v>1.15745676813423</x:v>
       </x:c>
       <x:c r="P8" s="2" t="n">
         <x:f>I8</x:f>
-        <x:v>87</x:v>
+        <x:v>95.66666666666667</x:v>
       </x:c>
       <x:c r="Q8" s="2"/>
       <x:c r="R8" s="2"/>
@@ -3340,61 +3907,61 @@
       <x:c r="V8" s="2"/>
     </x:row>
     <x:row r="9" ht="21" customHeight="1">
-      <x:c r="A9" s="70" t="str">
-        <x:v>GPT-6 Sol xhigh</x:v>
-      </x:c>
-      <x:c r="B9" s="71" t="n">
-        <x:f>'Task 1'!D4</x:f>
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="C9" s="74" t="n">
-        <x:f>'Task 1'!C4</x:f>
-        <x:v>2.386</x:v>
-      </x:c>
-      <x:c r="D9" s="71" t="n">
-        <x:f>'Task 2'!D5</x:f>
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="E9" s="74" t="n">
-        <x:f>'Task 2'!C5</x:f>
-        <x:v>2.155</x:v>
-      </x:c>
-      <x:c r="F9" s="71" t="n">
-        <x:f>'Task 3'!D5</x:f>
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="G9" s="74" t="n">
-        <x:f>'Task 3'!C5</x:f>
-        <x:v>1.643</x:v>
-      </x:c>
-      <x:c r="H9" s="71" t="n">
+      <x:c r="A9" s="121" t="str">
+        <x:v>GPT-6 Sol max</x:v>
+      </x:c>
+      <x:c r="B9" s="122" t="n">
+        <x:f>'Task 1'!D7</x:f>
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="C9" s="125" t="n">
+        <x:f>'Task 1'!C7</x:f>
+        <x:v>4.118</x:v>
+      </x:c>
+      <x:c r="D9" s="122" t="n">
+        <x:f>'Task 2'!D4</x:f>
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="E9" s="125" t="n">
+        <x:f>'Task 2'!C4</x:f>
+        <x:v>1.814</x:v>
+      </x:c>
+      <x:c r="F9" s="122" t="n">
+        <x:f>'Task 3'!D4</x:f>
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="G9" s="125" t="n">
+        <x:f>'Task 3'!C4</x:f>
+        <x:v>2.32</x:v>
+      </x:c>
+      <x:c r="H9" s="122" t="n">
         <x:f>SUM(B9,D9,F9)</x:f>
-        <x:v>236</x:v>
-      </x:c>
-      <x:c r="I9" s="76" t="n">
+        <x:v>283</x:v>
+      </x:c>
+      <x:c r="I9" s="127" t="n">
         <x:f>H9/3</x:f>
-        <x:v>78.66666666666667</x:v>
-      </x:c>
-      <x:c r="J9" s="74" t="n">
+        <x:v>94.33333333333333</x:v>
+      </x:c>
+      <x:c r="J9" s="125" t="n">
         <x:f>SUM(C9,E9,G9)</x:f>
-        <x:v>6.184</x:v>
-      </x:c>
-      <x:c r="K9" s="71" t="n">
+        <x:v>8.252</x:v>
+      </x:c>
+      <x:c r="K9" s="122" t="n">
         <x:f>MIN(B9,D9,F9)</x:f>
-        <x:v>54</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="L9" s="2"/>
       <x:c r="M9" s="2"/>
       <x:c r="N9" s="2" t="str">
-        <x:v>GPT-6 Sol xhigh</x:v>
+        <x:v>GPT-6 Sol max</x:v>
       </x:c>
       <x:c r="O9" s="2" t="n">
         <x:f>LOG10(J9)</x:f>
-        <x:v>0.791269480910268</x:v>
+        <x:v>0.916559219301114</x:v>
       </x:c>
       <x:c r="P9" s="2" t="n">
         <x:f>I9</x:f>
-        <x:v>78.66666666666667</x:v>
+        <x:v>94.33333333333333</x:v>
       </x:c>
       <x:c r="Q9" s="2"/>
       <x:c r="R9" s="2"/>
@@ -3405,60 +3972,60 @@
     </x:row>
     <x:row r="10" ht="21" customHeight="1">
       <x:c r="A10" s="2" t="str">
-        <x:v>GPT-5.6 Sol xhigh</x:v>
+        <x:v>Opus 5.5 xhigh</x:v>
       </x:c>
       <x:c r="B10" s="12" t="n">
-        <x:f>'Task 1'!D2</x:f>
-        <x:v>57</x:v>
+        <x:f>'Task 1'!D6</x:f>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C10" s="20" t="n">
-        <x:f>'Task 1'!C2</x:f>
-        <x:v>4.082</x:v>
+        <x:f>'Task 1'!C6</x:f>
+        <x:v>24.056</x:v>
       </x:c>
       <x:c r="D10" s="12" t="n">
-        <x:f>'Task 2'!D2</x:f>
-        <x:v>87</x:v>
+        <x:f>'Task 2'!D8</x:f>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="E10" s="20" t="n">
-        <x:f>'Task 2'!C2</x:f>
-        <x:v>2.763</x:v>
+        <x:f>'Task 2'!C8</x:f>
+        <x:v>12.33</x:v>
       </x:c>
       <x:c r="F10" s="12" t="n">
-        <x:f>'Task 3'!D2</x:f>
-        <x:v>82</x:v>
+        <x:f>'Task 3'!D8</x:f>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="G10" s="20" t="n">
-        <x:f>'Task 3'!C2</x:f>
-        <x:v>13.96</x:v>
+        <x:f>'Task 3'!C8</x:f>
+        <x:v>14.384</x:v>
       </x:c>
       <x:c r="H10" s="12" t="n">
         <x:f>SUM(B10,D10,F10)</x:f>
-        <x:v>226</x:v>
+        <x:v>261</x:v>
       </x:c>
       <x:c r="I10" s="23" t="n">
         <x:f>H10/3</x:f>
-        <x:v>75.33333333333333</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="J10" s="20" t="n">
         <x:f>SUM(C10,E10,G10)</x:f>
-        <x:v>20.805</x:v>
+        <x:v>50.77</x:v>
       </x:c>
       <x:c r="K10" s="12" t="n">
         <x:f>MIN(B10,D10,F10)</x:f>
-        <x:v>57</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="L10" s="2"/>
       <x:c r="M10" s="2"/>
       <x:c r="N10" s="2" t="str">
-        <x:v>GPT-5.6 Sol xhigh</x:v>
+        <x:v>Opus 5.5 xhigh</x:v>
       </x:c>
       <x:c r="O10" s="2" t="n">
         <x:f>LOG10(J10)</x:f>
-        <x:v>1.31816772012897</x:v>
+        <x:v>1.7056071634046</x:v>
       </x:c>
       <x:c r="P10" s="2" t="n">
         <x:f>I10</x:f>
-        <x:v>75.33333333333333</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="Q10" s="2"/>
       <x:c r="R10" s="2"/>
@@ -3468,61 +4035,61 @@
       <x:c r="V10" s="2"/>
     </x:row>
     <x:row r="11" ht="21" customHeight="1">
-      <x:c r="A11" s="70" t="str">
-        <x:v>GPT-6 Luna max</x:v>
-      </x:c>
-      <x:c r="B11" s="71" t="n">
-        <x:f>'Task 1'!D8</x:f>
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="C11" s="74" t="n">
-        <x:f>'Task 1'!C8</x:f>
-        <x:v>0.178</x:v>
-      </x:c>
-      <x:c r="D11" s="71" t="n">
-        <x:f>'Task 2'!D3</x:f>
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="E11" s="74" t="n">
-        <x:f>'Task 2'!C3</x:f>
-        <x:v>0.143</x:v>
-      </x:c>
-      <x:c r="F11" s="71" t="n">
-        <x:f>'Task 3'!D3</x:f>
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="G11" s="74" t="n">
-        <x:f>'Task 3'!C3</x:f>
-        <x:v>0.143</x:v>
-      </x:c>
-      <x:c r="H11" s="71" t="n">
+      <x:c r="A11" s="121" t="str">
+        <x:v>GPT-6 Sol xhigh</x:v>
+      </x:c>
+      <x:c r="B11" s="122" t="n">
+        <x:f>'Task 1'!D4</x:f>
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="C11" s="125" t="n">
+        <x:f>'Task 1'!C4</x:f>
+        <x:v>2.386</x:v>
+      </x:c>
+      <x:c r="D11" s="122" t="n">
+        <x:f>'Task 2'!D5</x:f>
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="E11" s="125" t="n">
+        <x:f>'Task 2'!C5</x:f>
+        <x:v>2.155</x:v>
+      </x:c>
+      <x:c r="F11" s="122" t="n">
+        <x:f>'Task 3'!D5</x:f>
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="G11" s="125" t="n">
+        <x:f>'Task 3'!C5</x:f>
+        <x:v>1.643</x:v>
+      </x:c>
+      <x:c r="H11" s="122" t="n">
         <x:f>SUM(B11,D11,F11)</x:f>
-        <x:v>215</x:v>
-      </x:c>
-      <x:c r="I11" s="76" t="n">
+        <x:v>236</x:v>
+      </x:c>
+      <x:c r="I11" s="127" t="n">
         <x:f>H11/3</x:f>
-        <x:v>71.66666666666667</x:v>
-      </x:c>
-      <x:c r="J11" s="74" t="n">
+        <x:v>78.66666666666667</x:v>
+      </x:c>
+      <x:c r="J11" s="125" t="n">
         <x:f>SUM(C11,E11,G11)</x:f>
-        <x:v>0.46399999999999997</x:v>
-      </x:c>
-      <x:c r="K11" s="71" t="n">
+        <x:v>6.184</x:v>
+      </x:c>
+      <x:c r="K11" s="122" t="n">
         <x:f>MIN(B11,D11,F11)</x:f>
-        <x:v>53</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="L11" s="2"/>
       <x:c r="M11" s="2"/>
       <x:c r="N11" s="2" t="str">
-        <x:v>GPT-6 Luna max</x:v>
+        <x:v>GPT-6 Sol xhigh</x:v>
       </x:c>
       <x:c r="O11" s="2" t="n">
         <x:f>LOG10(J11)</x:f>
-        <x:v>-0.333482019445119</x:v>
+        <x:v>0.791269480910268</x:v>
       </x:c>
       <x:c r="P11" s="2" t="n">
         <x:f>I11</x:f>
-        <x:v>71.66666666666667</x:v>
+        <x:v>78.66666666666667</x:v>
       </x:c>
       <x:c r="Q11" s="2"/>
       <x:c r="R11" s="2"/>
@@ -3533,60 +4100,60 @@
     </x:row>
     <x:row r="12" ht="21" customHeight="1">
       <x:c r="A12" s="2" t="str">
-        <x:v>DeepSeek V4.1 Flash max</x:v>
+        <x:v>GPT-5.6 Sol xhigh</x:v>
       </x:c>
       <x:c r="B12" s="12" t="n">
-        <x:f>'Task 1'!D9</x:f>
-        <x:v>47</x:v>
+        <x:f>'Task 1'!D2</x:f>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C12" s="20" t="n">
-        <x:f>'Task 1'!C9</x:f>
-        <x:v>0.414</x:v>
+        <x:f>'Task 1'!C2</x:f>
+        <x:v>4.082</x:v>
       </x:c>
       <x:c r="D12" s="12" t="n">
-        <x:f>'Task 2'!D9</x:f>
-        <x:v>75</x:v>
+        <x:f>'Task 2'!D2</x:f>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="E12" s="20" t="n">
-        <x:f>'Task 2'!C9</x:f>
-        <x:v>0.43</x:v>
+        <x:f>'Task 2'!C2</x:f>
+        <x:v>2.763</x:v>
       </x:c>
       <x:c r="F12" s="12" t="n">
-        <x:f>'Task 3'!D9</x:f>
-        <x:v>54</x:v>
+        <x:f>'Task 3'!D2</x:f>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="G12" s="20" t="n">
-        <x:f>'Task 3'!C9</x:f>
-        <x:v>0.477</x:v>
+        <x:f>'Task 3'!C2</x:f>
+        <x:v>13.96</x:v>
       </x:c>
       <x:c r="H12" s="12" t="n">
         <x:f>SUM(B12,D12,F12)</x:f>
-        <x:v>176</x:v>
+        <x:v>226</x:v>
       </x:c>
       <x:c r="I12" s="23" t="n">
         <x:f>H12/3</x:f>
-        <x:v>58.666666666666664</x:v>
+        <x:v>75.33333333333333</x:v>
       </x:c>
       <x:c r="J12" s="20" t="n">
         <x:f>SUM(C12,E12,G12)</x:f>
-        <x:v>1.321</x:v>
+        <x:v>20.805</x:v>
       </x:c>
       <x:c r="K12" s="12" t="n">
         <x:f>MIN(B12,D12,F12)</x:f>
-        <x:v>47</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="L12" s="2"/>
       <x:c r="M12" s="2"/>
       <x:c r="N12" s="2" t="str">
-        <x:v>DeepSeek V4.1 Flash max</x:v>
+        <x:v>GPT-5.6 Sol xhigh</x:v>
       </x:c>
       <x:c r="O12" s="2" t="n">
         <x:f>LOG10(J12)</x:f>
-        <x:v>0.120902817614527</x:v>
+        <x:v>1.31816772012897</x:v>
       </x:c>
       <x:c r="P12" s="2" t="n">
         <x:f>I12</x:f>
-        <x:v>58.666666666666664</x:v>
+        <x:v>75.33333333333333</x:v>
       </x:c>
       <x:c r="Q12" s="2"/>
       <x:c r="R12" s="2"/>
@@ -3596,61 +4163,61 @@
       <x:c r="V12" s="2"/>
     </x:row>
     <x:row r="13" ht="21" customHeight="1">
-      <x:c r="A13" s="72" t="str">
-        <x:v>Grok 4.7 high</x:v>
-      </x:c>
-      <x:c r="B13" s="73" t="n">
-        <x:f>'Task 1'!D5</x:f>
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="C13" s="75" t="n">
-        <x:f>'Task 1'!C5</x:f>
-        <x:v>4.514</x:v>
-      </x:c>
-      <x:c r="D13" s="73" t="n">
-        <x:f>'Task 2'!D7</x:f>
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="E13" s="75" t="n">
-        <x:f>'Task 2'!C7</x:f>
-        <x:v>4.274</x:v>
-      </x:c>
-      <x:c r="F13" s="73" t="n">
-        <x:f>'Task 3'!D7</x:f>
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="G13" s="75" t="n">
-        <x:f>'Task 3'!C7</x:f>
-        <x:v>5.888</x:v>
-      </x:c>
-      <x:c r="H13" s="73" t="n">
+      <x:c r="A13" s="121" t="str">
+        <x:v>GPT-6 Luna max</x:v>
+      </x:c>
+      <x:c r="B13" s="122" t="n">
+        <x:f>'Task 1'!D8</x:f>
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="C13" s="125" t="n">
+        <x:f>'Task 1'!C8</x:f>
+        <x:v>0.178</x:v>
+      </x:c>
+      <x:c r="D13" s="122" t="n">
+        <x:f>'Task 2'!D3</x:f>
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="E13" s="125" t="n">
+        <x:f>'Task 2'!C3</x:f>
+        <x:v>0.143</x:v>
+      </x:c>
+      <x:c r="F13" s="122" t="n">
+        <x:f>'Task 3'!D3</x:f>
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="G13" s="125" t="n">
+        <x:f>'Task 3'!C3</x:f>
+        <x:v>0.143</x:v>
+      </x:c>
+      <x:c r="H13" s="122" t="n">
         <x:f>SUM(B13,D13,F13)</x:f>
-        <x:v>169</x:v>
-      </x:c>
-      <x:c r="I13" s="77" t="n">
+        <x:v>215</x:v>
+      </x:c>
+      <x:c r="I13" s="127" t="n">
         <x:f>H13/3</x:f>
-        <x:v>56.333333333333336</x:v>
-      </x:c>
-      <x:c r="J13" s="75" t="n">
+        <x:v>71.66666666666667</x:v>
+      </x:c>
+      <x:c r="J13" s="125" t="n">
         <x:f>SUM(C13,E13,G13)</x:f>
-        <x:v>14.676</x:v>
-      </x:c>
-      <x:c r="K13" s="73" t="n">
+        <x:v>0.46399999999999997</x:v>
+      </x:c>
+      <x:c r="K13" s="122" t="n">
         <x:f>MIN(B13,D13,F13)</x:f>
-        <x:v>30</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="L13" s="2"/>
       <x:c r="M13" s="2"/>
       <x:c r="N13" s="2" t="str">
-        <x:v>Grok 4.7 high</x:v>
+        <x:v>GPT-6 Luna max</x:v>
       </x:c>
       <x:c r="O13" s="2" t="n">
         <x:f>LOG10(J13)</x:f>
-        <x:v>1.16660770308391</x:v>
+        <x:v>-0.333482019445119</x:v>
       </x:c>
       <x:c r="P13" s="2" t="n">
         <x:f>I13</x:f>
-        <x:v>56.333333333333336</x:v>
+        <x:v>71.66666666666667</x:v>
       </x:c>
       <x:c r="Q13" s="2"/>
       <x:c r="R13" s="2"/>
@@ -3660,22 +4227,62 @@
       <x:c r="V13" s="2"/>
     </x:row>
     <x:row r="14" ht="21" customHeight="1">
-      <x:c r="A14" s="2"/>
-      <x:c r="B14" s="2"/>
-      <x:c r="C14" s="2"/>
-      <x:c r="D14" s="2"/>
-      <x:c r="E14" s="2"/>
-      <x:c r="F14" s="2"/>
-      <x:c r="G14" s="2"/>
-      <x:c r="H14" s="2"/>
-      <x:c r="I14" s="2"/>
-      <x:c r="J14" s="2"/>
-      <x:c r="K14" s="2"/>
+      <x:c r="A14" s="2" t="str">
+        <x:v>DeepSeek V4.1 Flash max</x:v>
+      </x:c>
+      <x:c r="B14" s="12" t="n">
+        <x:f>'Task 1'!D9</x:f>
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="C14" s="20" t="n">
+        <x:f>'Task 1'!C9</x:f>
+        <x:v>0.414</x:v>
+      </x:c>
+      <x:c r="D14" s="12" t="n">
+        <x:f>'Task 2'!D9</x:f>
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="E14" s="20" t="n">
+        <x:f>'Task 2'!C9</x:f>
+        <x:v>0.43</x:v>
+      </x:c>
+      <x:c r="F14" s="12" t="n">
+        <x:f>'Task 3'!D9</x:f>
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="G14" s="20" t="n">
+        <x:f>'Task 3'!C9</x:f>
+        <x:v>0.477</x:v>
+      </x:c>
+      <x:c r="H14" s="12" t="n">
+        <x:f>SUM(B14,D14,F14)</x:f>
+        <x:v>176</x:v>
+      </x:c>
+      <x:c r="I14" s="23" t="n">
+        <x:f>H14/3</x:f>
+        <x:v>58.666666666666664</x:v>
+      </x:c>
+      <x:c r="J14" s="20" t="n">
+        <x:f>SUM(C14,E14,G14)</x:f>
+        <x:v>1.321</x:v>
+      </x:c>
+      <x:c r="K14" s="12" t="n">
+        <x:f>MIN(B14,D14,F14)</x:f>
+        <x:v>47</x:v>
+      </x:c>
       <x:c r="L14" s="2"/>
       <x:c r="M14" s="2"/>
-      <x:c r="N14" s="2"/>
-      <x:c r="O14" s="2"/>
-      <x:c r="P14" s="2"/>
+      <x:c r="N14" s="2" t="str">
+        <x:v>DeepSeek V4.1 Flash max</x:v>
+      </x:c>
+      <x:c r="O14" s="2" t="n">
+        <x:f>LOG10(J14)</x:f>
+        <x:v>0.120902817614527</x:v>
+      </x:c>
+      <x:c r="P14" s="2" t="n">
+        <x:f>I14</x:f>
+        <x:v>58.666666666666664</x:v>
+      </x:c>
       <x:c r="Q14" s="2"/>
       <x:c r="R14" s="2"/>
       <x:c r="S14" s="2"/>
@@ -3684,22 +4291,62 @@
       <x:c r="V14" s="2"/>
     </x:row>
     <x:row r="15" ht="21" customHeight="1">
-      <x:c r="A15" s="2"/>
-      <x:c r="B15" s="2"/>
-      <x:c r="C15" s="2"/>
-      <x:c r="D15" s="2"/>
-      <x:c r="E15" s="2"/>
-      <x:c r="F15" s="2"/>
-      <x:c r="G15" s="2"/>
-      <x:c r="H15" s="2"/>
-      <x:c r="I15" s="2"/>
-      <x:c r="J15" s="2"/>
-      <x:c r="K15" s="2"/>
+      <x:c r="A15" s="123" t="str">
+        <x:v>Grok 4.7 high</x:v>
+      </x:c>
+      <x:c r="B15" s="124" t="n">
+        <x:f>'Task 1'!D5</x:f>
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C15" s="126" t="n">
+        <x:f>'Task 1'!C5</x:f>
+        <x:v>4.514</x:v>
+      </x:c>
+      <x:c r="D15" s="124" t="n">
+        <x:f>'Task 2'!D7</x:f>
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="E15" s="126" t="n">
+        <x:f>'Task 2'!C7</x:f>
+        <x:v>4.274</x:v>
+      </x:c>
+      <x:c r="F15" s="124" t="n">
+        <x:f>'Task 3'!D7</x:f>
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="G15" s="126" t="n">
+        <x:f>'Task 3'!C7</x:f>
+        <x:v>5.888</x:v>
+      </x:c>
+      <x:c r="H15" s="124" t="n">
+        <x:f>SUM(B15,D15,F15)</x:f>
+        <x:v>169</x:v>
+      </x:c>
+      <x:c r="I15" s="128" t="n">
+        <x:f>H15/3</x:f>
+        <x:v>56.333333333333336</x:v>
+      </x:c>
+      <x:c r="J15" s="126" t="n">
+        <x:f>SUM(C15,E15,G15)</x:f>
+        <x:v>14.676</x:v>
+      </x:c>
+      <x:c r="K15" s="124" t="n">
+        <x:f>MIN(B15,D15,F15)</x:f>
+        <x:v>30</x:v>
+      </x:c>
       <x:c r="L15" s="2"/>
       <x:c r="M15" s="2"/>
-      <x:c r="N15" s="2"/>
-      <x:c r="O15" s="2"/>
-      <x:c r="P15" s="2"/>
+      <x:c r="N15" s="2" t="str">
+        <x:v>Grok 4.7 high</x:v>
+      </x:c>
+      <x:c r="O15" s="2" t="n">
+        <x:f>LOG10(J15)</x:f>
+        <x:v>1.16660770308391</x:v>
+      </x:c>
+      <x:c r="P15" s="2" t="n">
+        <x:f>I15</x:f>
+        <x:v>56.333333333333336</x:v>
+      </x:c>
       <x:c r="Q15" s="2"/>
       <x:c r="R15" s="2"/>
       <x:c r="S15" s="2"/>
@@ -3707,20 +4354,18 @@
       <x:c r="U15" s="2"/>
       <x:c r="V15" s="2"/>
     </x:row>
-    <x:row r="16" ht="24" customHeight="1">
-      <x:c r="A16" s="27" t="str">
-        <x:v>三题综合比较与成本—得分前沿</x:v>
-      </x:c>
-      <x:c r="B16" s="27"/>
-      <x:c r="C16" s="27"/>
-      <x:c r="D16" s="27"/>
-      <x:c r="E16" s="27"/>
-      <x:c r="F16" s="27"/>
-      <x:c r="G16" s="27"/>
-      <x:c r="H16" s="27"/>
-      <x:c r="I16" s="27"/>
-      <x:c r="J16" s="27"/>
-      <x:c r="K16" s="27"/>
+    <x:row r="16" ht="21" customHeight="1">
+      <x:c r="A16" s="2"/>
+      <x:c r="B16" s="2"/>
+      <x:c r="C16" s="2"/>
+      <x:c r="D16" s="2"/>
+      <x:c r="E16" s="2"/>
+      <x:c r="F16" s="2"/>
+      <x:c r="G16" s="2"/>
+      <x:c r="H16" s="2"/>
+      <x:c r="I16" s="2"/>
+      <x:c r="J16" s="2"/>
+      <x:c r="K16" s="2"/>
       <x:c r="L16" s="2"/>
       <x:c r="M16" s="2"/>
       <x:c r="N16" s="2"/>
@@ -3757,40 +4402,20 @@
       <x:c r="U17" s="2"/>
       <x:c r="V17" s="2"/>
     </x:row>
-    <x:row r="18" ht="35" customHeight="1">
-      <x:c r="A18" s="69" t="str">
-        <x:v>模型配置</x:v>
-      </x:c>
-      <x:c r="B18" s="69" t="str">
-        <x:v>排名</x:v>
-      </x:c>
-      <x:c r="C18" s="69" t="str">
-        <x:v>总分 /300</x:v>
-      </x:c>
-      <x:c r="D18" s="69" t="str">
-        <x:v>均分 /100</x:v>
-      </x:c>
-      <x:c r="E18" s="69" t="str">
-        <x:v>总成本 USD</x:v>
-      </x:c>
-      <x:c r="F18" s="69" t="str">
-        <x:v>总分 /USD</x:v>
-      </x:c>
-      <x:c r="G18" s="69" t="str">
-        <x:v>评阅下限</x:v>
-      </x:c>
-      <x:c r="H18" s="69" t="str">
-        <x:v>评阅上限</x:v>
-      </x:c>
-      <x:c r="I18" s="69" t="str">
-        <x:v>成本—得分</x:v>
-      </x:c>
-      <x:c r="J18" s="69" t="str">
-        <x:v>最弱一题</x:v>
-      </x:c>
-      <x:c r="K18" s="69" t="str">
-        <x:v>≥80 分题数</x:v>
-      </x:c>
+    <x:row r="18" ht="24" customHeight="1">
+      <x:c r="A18" s="27" t="str">
+        <x:v>三题综合比较与成本—得分前沿</x:v>
+      </x:c>
+      <x:c r="B18" s="27"/>
+      <x:c r="C18" s="27"/>
+      <x:c r="D18" s="27"/>
+      <x:c r="E18" s="27"/>
+      <x:c r="F18" s="27"/>
+      <x:c r="G18" s="27"/>
+      <x:c r="H18" s="27"/>
+      <x:c r="I18" s="27"/>
+      <x:c r="J18" s="27"/>
+      <x:c r="K18" s="27"/>
       <x:c r="L18" s="2"/>
       <x:c r="M18" s="2"/>
       <x:c r="N18" s="2" t="str">
@@ -3810,61 +4435,29 @@
       <x:c r="V18" s="2"/>
     </x:row>
     <x:row r="19" ht="21" customHeight="1">
-      <x:c r="A19" s="2" t="str">
-        <x:v>GPT-6 Astra high</x:v>
-      </x:c>
-      <x:c r="B19" s="12" t="n">
-        <x:f>RANK(C19,$C$19:$C$26,0)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C19" s="12" t="n">
-        <x:f>H6</x:f>
-        <x:v>287</x:v>
-      </x:c>
-      <x:c r="D19" s="23" t="n">
-        <x:f>I6</x:f>
-        <x:v>95.66666666666667</x:v>
-      </x:c>
-      <x:c r="E19" s="20" t="n">
-        <x:f>J6</x:f>
-        <x:v>14.370000000000001</x:v>
-      </x:c>
-      <x:c r="F19" s="23" t="n">
-        <x:f>C19/E19</x:f>
-        <x:v>19.97216423103688</x:v>
-      </x:c>
-      <x:c r="G19" s="23" t="n">
-        <x:f>AVERAGE(I126,I137,I145)</x:f>
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="H19" s="23" t="n">
-        <x:f>AVERAGE(J126,J137,J145)</x:f>
-        <x:v>97.66666666666667</x:v>
-      </x:c>
-      <x:c r="I19" s="12" t="str">
-        <x:f>IF(COUNTIFS($E$19:$E$26,"&lt;="&amp;E19,$C$19:$C$26,"&gt;="&amp;C19)-COUNTIFS($E$19:$E$26,E19,$C$19:$C$26,C19)&gt;0,"被支配","前沿")</x:f>
-        <x:v>前沿</x:v>
-      </x:c>
-      <x:c r="J19" s="12" t="n">
-        <x:f>K6</x:f>
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="K19" s="12" t="n">
-        <x:f>COUNTIF(B6,"&gt;=80")+COUNTIF(D6,"&gt;=80")+COUNTIF(F6,"&gt;=80")</x:f>
-        <x:v>3</x:v>
-      </x:c>
+      <x:c r="A19" s="2"/>
+      <x:c r="B19" s="2"/>
+      <x:c r="C19" s="2"/>
+      <x:c r="D19" s="2"/>
+      <x:c r="E19" s="2"/>
+      <x:c r="F19" s="2"/>
+      <x:c r="G19" s="2"/>
+      <x:c r="H19" s="2"/>
+      <x:c r="I19" s="2"/>
+      <x:c r="J19" s="2"/>
+      <x:c r="K19" s="2"/>
       <x:c r="L19" s="2"/>
       <x:c r="M19" s="2"/>
       <x:c r="N19" s="2" t="str">
-        <x:v>GPT-6 Sol max</x:v>
+        <x:v>GPT-6.1 Sol max</x:v>
       </x:c>
       <x:c r="O19" s="2" t="n">
-        <x:f>LOG10('Task 1'!C7)</x:f>
-        <x:v>0.614686342282013</x:v>
+        <x:f>LOG10('Task 1'!C11)</x:f>
+        <x:v>0.254064452914338</x:v>
       </x:c>
       <x:c r="P19" s="2" t="n">
-        <x:f>'Task 1'!D7</x:f>
-        <x:v>94</x:v>
+        <x:f>'Task 1'!D11</x:f>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="Q19" s="2"/>
       <x:c r="R19" s="2"/>
@@ -3873,62 +4466,52 @@
       <x:c r="U19" s="2"/>
       <x:c r="V19" s="2"/>
     </x:row>
-    <x:row r="20" ht="21" customHeight="1">
-      <x:c r="A20" s="70" t="str">
-        <x:v>GPT-6 Sol max</x:v>
-      </x:c>
-      <x:c r="B20" s="71" t="n">
-        <x:f>RANK(C20,$C$19:$C$26,0)</x:f>
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C20" s="71" t="n">
-        <x:f>H7</x:f>
-        <x:v>283</x:v>
-      </x:c>
-      <x:c r="D20" s="76" t="n">
-        <x:f>I7</x:f>
-        <x:v>94.33333333333333</x:v>
-      </x:c>
-      <x:c r="E20" s="74" t="n">
-        <x:f>J7</x:f>
-        <x:v>8.252</x:v>
-      </x:c>
-      <x:c r="F20" s="76" t="n">
-        <x:f>C20/E20</x:f>
-        <x:v>34.29471643238003</x:v>
-      </x:c>
-      <x:c r="G20" s="76" t="n">
-        <x:f>AVERAGE(I130,I135,I143)</x:f>
-        <x:v>90.66666666666667</x:v>
-      </x:c>
-      <x:c r="H20" s="76" t="n">
-        <x:f>AVERAGE(J130,J135,J143)</x:f>
-        <x:v>97.33333333333333</x:v>
-      </x:c>
-      <x:c r="I20" s="71" t="str">
-        <x:f>IF(COUNTIFS($E$19:$E$26,"&lt;="&amp;E20,$C$19:$C$26,"&gt;="&amp;C20)-COUNTIFS($E$19:$E$26,E20,$C$19:$C$26,C20)&gt;0,"被支配","前沿")</x:f>
-        <x:v>前沿</x:v>
-      </x:c>
-      <x:c r="J20" s="71" t="n">
-        <x:f>K7</x:f>
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="K20" s="71" t="n">
-        <x:f>COUNTIF(B7,"&gt;=80")+COUNTIF(D7,"&gt;=80")+COUNTIF(F7,"&gt;=80")</x:f>
-        <x:v>3</x:v>
+    <x:row r="20" ht="35" customHeight="1">
+      <x:c r="A20" s="120" t="str">
+        <x:v>模型配置</x:v>
+      </x:c>
+      <x:c r="B20" s="120" t="str">
+        <x:v>排名</x:v>
+      </x:c>
+      <x:c r="C20" s="120" t="str">
+        <x:v>总分 /300</x:v>
+      </x:c>
+      <x:c r="D20" s="120" t="str">
+        <x:v>均分 /100</x:v>
+      </x:c>
+      <x:c r="E20" s="120" t="str">
+        <x:v>总成本 USD</x:v>
+      </x:c>
+      <x:c r="F20" s="120" t="str">
+        <x:v>总分 /USD</x:v>
+      </x:c>
+      <x:c r="G20" s="120" t="str">
+        <x:v>评阅下限</x:v>
+      </x:c>
+      <x:c r="H20" s="120" t="str">
+        <x:v>评阅上限</x:v>
+      </x:c>
+      <x:c r="I20" s="120" t="str">
+        <x:v>成本—得分</x:v>
+      </x:c>
+      <x:c r="J20" s="120" t="str">
+        <x:v>最弱一题</x:v>
+      </x:c>
+      <x:c r="K20" s="120" t="str">
+        <x:v>≥80 分题数</x:v>
       </x:c>
       <x:c r="L20" s="2"/>
       <x:c r="M20" s="2"/>
       <x:c r="N20" s="2" t="str">
-        <x:v>GPT-6 Astra high</x:v>
+        <x:v>GPT-6.1 Sol xhigh</x:v>
       </x:c>
       <x:c r="O20" s="2" t="n">
-        <x:f>LOG10('Task 1'!C3)</x:f>
-        <x:v>0.74927240829842</x:v>
+        <x:f>LOG10('Task 1'!C10)</x:f>
+        <x:v>0.207365037469072</x:v>
       </x:c>
       <x:c r="P20" s="2" t="n">
-        <x:f>'Task 1'!D3</x:f>
-        <x:v>92</x:v>
+        <x:f>'Task 1'!D10</x:f>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="Q20" s="2"/>
       <x:c r="R20" s="2"/>
@@ -3939,60 +4522,60 @@
     </x:row>
     <x:row r="21" ht="21" customHeight="1">
       <x:c r="A21" s="2" t="str">
-        <x:v>Opus 5.5 xhigh</x:v>
+        <x:v>GPT-6.1 Sol max</x:v>
       </x:c>
       <x:c r="B21" s="12" t="n">
-        <x:f>RANK(C21,$C$19:$C$26,0)</x:f>
-        <x:v>3</x:v>
+        <x:f>RANK(C21,$C$21:$C$30,0)</x:f>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C21" s="12" t="n">
-        <x:f>H8</x:f>
-        <x:v>261</x:v>
+        <x:f>H6</x:f>
+        <x:v>294</x:v>
       </x:c>
       <x:c r="D21" s="23" t="n">
-        <x:f>I8</x:f>
-        <x:v>87</x:v>
+        <x:f>I6</x:f>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="E21" s="20" t="n">
-        <x:f>J8</x:f>
-        <x:v>50.77</x:v>
+        <x:f>J6</x:f>
+        <x:v>4.576</x:v>
       </x:c>
       <x:c r="F21" s="23" t="n">
         <x:f>C21/E21</x:f>
-        <x:v>5.1408311995272795</x:v>
+        <x:v>64.24825174825175</x:v>
       </x:c>
       <x:c r="G21" s="23" t="n">
-        <x:f>AVERAGE(I129,I139,I147)</x:f>
-        <x:v>82</x:v>
+        <x:f>AVERAGE(I147,I157,I167)</x:f>
+        <x:v>94.66666666666667</x:v>
       </x:c>
       <x:c r="H21" s="23" t="n">
-        <x:f>AVERAGE(J129,J139,J147)</x:f>
-        <x:v>91.66666666666667</x:v>
+        <x:f>AVERAGE(J147,J157,J167)</x:f>
+        <x:v>99.66666666666667</x:v>
       </x:c>
       <x:c r="I21" s="12" t="str">
-        <x:f>IF(COUNTIFS($E$19:$E$26,"&lt;="&amp;E21,$C$19:$C$26,"&gt;="&amp;C21)-COUNTIFS($E$19:$E$26,E21,$C$19:$C$26,C21)&gt;0,"被支配","前沿")</x:f>
-        <x:v>被支配</x:v>
+        <x:f>IF(COUNTIFS($E$21:$E$30,"&lt;="&amp;E21,$C$21:$C$30,"&gt;="&amp;C21)-COUNTIFS($E$21:$E$30,E21,$C$21:$C$30,C21)&gt;0,"被支配","前沿")</x:f>
+        <x:v>前沿</x:v>
       </x:c>
       <x:c r="J21" s="12" t="n">
-        <x:f>K8</x:f>
-        <x:v>81</x:v>
+        <x:f>K6</x:f>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="K21" s="12" t="n">
-        <x:f>COUNTIF(B8,"&gt;=80")+COUNTIF(D8,"&gt;=80")+COUNTIF(F8,"&gt;=80")</x:f>
+        <x:f>COUNTIF(B6,"&gt;=80")+COUNTIF(D6,"&gt;=80")+COUNTIF(F6,"&gt;=80")</x:f>
         <x:v>3</x:v>
       </x:c>
       <x:c r="L21" s="2"/>
       <x:c r="M21" s="2"/>
       <x:c r="N21" s="2" t="str">
-        <x:v>Opus 5.5 xhigh</x:v>
+        <x:v>GPT-6 Sol max</x:v>
       </x:c>
       <x:c r="O21" s="2" t="n">
-        <x:f>LOG10('Task 1'!C6)</x:f>
-        <x:v>1.38122341509246</x:v>
+        <x:f>LOG10('Task 1'!C7)</x:f>
+        <x:v>0.614686342282013</x:v>
       </x:c>
       <x:c r="P21" s="2" t="n">
-        <x:f>'Task 1'!D6</x:f>
-        <x:v>87</x:v>
+        <x:f>'Task 1'!D7</x:f>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="Q21" s="2"/>
       <x:c r="R21" s="2"/>
@@ -4002,61 +4585,61 @@
       <x:c r="V21" s="2"/>
     </x:row>
     <x:row r="22" ht="21" customHeight="1">
-      <x:c r="A22" s="70" t="str">
-        <x:v>GPT-6 Sol xhigh</x:v>
-      </x:c>
-      <x:c r="B22" s="71" t="n">
-        <x:f>RANK(C22,$C$19:$C$26,0)</x:f>
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C22" s="71" t="n">
-        <x:f>H9</x:f>
-        <x:v>236</x:v>
-      </x:c>
-      <x:c r="D22" s="76" t="n">
-        <x:f>I9</x:f>
-        <x:v>78.66666666666667</x:v>
-      </x:c>
-      <x:c r="E22" s="74" t="n">
-        <x:f>J9</x:f>
-        <x:v>6.184</x:v>
-      </x:c>
-      <x:c r="F22" s="76" t="n">
+      <x:c r="A22" s="121" t="str">
+        <x:v>GPT-6.1 Sol xhigh</x:v>
+      </x:c>
+      <x:c r="B22" s="122" t="n">
+        <x:f>RANK(C22,$C$21:$C$30,0)</x:f>
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C22" s="122" t="n">
+        <x:f>H7</x:f>
+        <x:v>291</x:v>
+      </x:c>
+      <x:c r="D22" s="127" t="n">
+        <x:f>I7</x:f>
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="E22" s="125" t="n">
+        <x:f>J7</x:f>
+        <x:v>4.093999999999999</x:v>
+      </x:c>
+      <x:c r="F22" s="127" t="n">
         <x:f>C22/E22</x:f>
-        <x:v>38.16300129366106</x:v>
-      </x:c>
-      <x:c r="G22" s="76" t="n">
-        <x:f>AVERAGE(I127,I136,I144)</x:f>
-        <x:v>74.33333333333333</x:v>
-      </x:c>
-      <x:c r="H22" s="76" t="n">
-        <x:f>AVERAGE(J127,J136,J144)</x:f>
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="I22" s="71" t="str">
-        <x:f>IF(COUNTIFS($E$19:$E$26,"&lt;="&amp;E22,$C$19:$C$26,"&gt;="&amp;C22)-COUNTIFS($E$19:$E$26,E22,$C$19:$C$26,C22)&gt;0,"被支配","前沿")</x:f>
+        <x:v>71.07962872496337</x:v>
+      </x:c>
+      <x:c r="G22" s="127" t="n">
+        <x:f>AVERAGE(I146,I156,I166)</x:f>
+        <x:v>93.66666666666667</x:v>
+      </x:c>
+      <x:c r="H22" s="127" t="n">
+        <x:f>AVERAGE(J146,J156,J166)</x:f>
+        <x:v>99.33333333333333</x:v>
+      </x:c>
+      <x:c r="I22" s="122" t="str">
+        <x:f>IF(COUNTIFS($E$21:$E$30,"&lt;="&amp;E22,$C$21:$C$30,"&gt;="&amp;C22)-COUNTIFS($E$21:$E$30,E22,$C$21:$C$30,C22)&gt;0,"被支配","前沿")</x:f>
         <x:v>前沿</x:v>
       </x:c>
-      <x:c r="J22" s="71" t="n">
-        <x:f>K9</x:f>
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="K22" s="71" t="n">
-        <x:f>COUNTIF(B9,"&gt;=80")+COUNTIF(D9,"&gt;=80")+COUNTIF(F9,"&gt;=80")</x:f>
-        <x:v>2</x:v>
+      <x:c r="J22" s="122" t="n">
+        <x:f>K7</x:f>
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="K22" s="122" t="n">
+        <x:f>COUNTIF(B7,"&gt;=80")+COUNTIF(D7,"&gt;=80")+COUNTIF(F7,"&gt;=80")</x:f>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="L22" s="2"/>
       <x:c r="M22" s="2"/>
       <x:c r="N22" s="2" t="str">
-        <x:v>GPT-5.6 Sol xhigh</x:v>
+        <x:v>GPT-6 Astra high</x:v>
       </x:c>
       <x:c r="O22" s="2" t="n">
-        <x:f>LOG10('Task 1'!C2)</x:f>
-        <x:v>0.610873000380052</x:v>
+        <x:f>LOG10('Task 1'!C3)</x:f>
+        <x:v>0.74927240829842</x:v>
       </x:c>
       <x:c r="P22" s="2" t="n">
-        <x:f>'Task 1'!D2</x:f>
-        <x:v>57</x:v>
+        <x:f>'Task 1'!D3</x:f>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="Q22" s="2"/>
       <x:c r="R22" s="2"/>
@@ -4067,60 +4650,60 @@
     </x:row>
     <x:row r="23" ht="21" customHeight="1">
       <x:c r="A23" s="2" t="str">
-        <x:v>GPT-5.6 Sol xhigh</x:v>
+        <x:v>GPT-6 Astra high</x:v>
       </x:c>
       <x:c r="B23" s="12" t="n">
-        <x:f>RANK(C23,$C$19:$C$26,0)</x:f>
-        <x:v>5</x:v>
+        <x:f>RANK(C23,$C$21:$C$30,0)</x:f>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C23" s="12" t="n">
-        <x:f>H10</x:f>
-        <x:v>226</x:v>
+        <x:f>H8</x:f>
+        <x:v>287</x:v>
       </x:c>
       <x:c r="D23" s="23" t="n">
-        <x:f>I10</x:f>
-        <x:v>75.33333333333333</x:v>
+        <x:f>I8</x:f>
+        <x:v>95.66666666666667</x:v>
       </x:c>
       <x:c r="E23" s="20" t="n">
-        <x:f>J10</x:f>
-        <x:v>20.805</x:v>
+        <x:f>J8</x:f>
+        <x:v>14.370000000000001</x:v>
       </x:c>
       <x:c r="F23" s="23" t="n">
         <x:f>C23/E23</x:f>
-        <x:v>10.862773371785629</x:v>
+        <x:v>19.97216423103688</x:v>
       </x:c>
       <x:c r="G23" s="23" t="n">
-        <x:f>AVERAGE(I125,I133,I141)</x:f>
-        <x:v>71</x:v>
+        <x:f>AVERAGE(I139,I152,I162)</x:f>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="H23" s="23" t="n">
-        <x:f>AVERAGE(J125,J133,J141)</x:f>
-        <x:v>79.66666666666667</x:v>
+        <x:f>AVERAGE(J139,J152,J162)</x:f>
+        <x:v>97.66666666666667</x:v>
       </x:c>
       <x:c r="I23" s="12" t="str">
-        <x:f>IF(COUNTIFS($E$19:$E$26,"&lt;="&amp;E23,$C$19:$C$26,"&gt;="&amp;C23)-COUNTIFS($E$19:$E$26,E23,$C$19:$C$26,C23)&gt;0,"被支配","前沿")</x:f>
+        <x:f>IF(COUNTIFS($E$21:$E$30,"&lt;="&amp;E23,$C$21:$C$30,"&gt;="&amp;C23)-COUNTIFS($E$21:$E$30,E23,$C$21:$C$30,C23)&gt;0,"被支配","前沿")</x:f>
         <x:v>被支配</x:v>
       </x:c>
       <x:c r="J23" s="12" t="n">
-        <x:f>K10</x:f>
-        <x:v>57</x:v>
+        <x:f>K8</x:f>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="K23" s="12" t="n">
-        <x:f>COUNTIF(B10,"&gt;=80")+COUNTIF(D10,"&gt;=80")+COUNTIF(F10,"&gt;=80")</x:f>
-        <x:v>2</x:v>
+        <x:f>COUNTIF(B8,"&gt;=80")+COUNTIF(D8,"&gt;=80")+COUNTIF(F8,"&gt;=80")</x:f>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="L23" s="2"/>
       <x:c r="M23" s="2"/>
       <x:c r="N23" s="2" t="str">
-        <x:v>GPT-6 Sol xhigh</x:v>
+        <x:v>Opus 5.5 xhigh</x:v>
       </x:c>
       <x:c r="O23" s="2" t="n">
-        <x:f>LOG10('Task 1'!C4)</x:f>
-        <x:v>0.377670439334323</x:v>
+        <x:f>LOG10('Task 1'!C6)</x:f>
+        <x:v>1.38122341509246</x:v>
       </x:c>
       <x:c r="P23" s="2" t="n">
-        <x:f>'Task 1'!D4</x:f>
-        <x:v>54</x:v>
+        <x:f>'Task 1'!D6</x:f>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="Q23" s="2"/>
       <x:c r="R23" s="2"/>
@@ -4130,61 +4713,61 @@
       <x:c r="V23" s="2"/>
     </x:row>
     <x:row r="24" ht="21" customHeight="1">
-      <x:c r="A24" s="70" t="str">
-        <x:v>GPT-6 Luna max</x:v>
-      </x:c>
-      <x:c r="B24" s="71" t="n">
-        <x:f>RANK(C24,$C$19:$C$26,0)</x:f>
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C24" s="71" t="n">
-        <x:f>H11</x:f>
-        <x:v>215</x:v>
-      </x:c>
-      <x:c r="D24" s="76" t="n">
-        <x:f>I11</x:f>
-        <x:v>71.66666666666667</x:v>
-      </x:c>
-      <x:c r="E24" s="74" t="n">
-        <x:f>J11</x:f>
-        <x:v>0.46399999999999997</x:v>
-      </x:c>
-      <x:c r="F24" s="76" t="n">
+      <x:c r="A24" s="121" t="str">
+        <x:v>GPT-6 Sol max</x:v>
+      </x:c>
+      <x:c r="B24" s="122" t="n">
+        <x:f>RANK(C24,$C$21:$C$30,0)</x:f>
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C24" s="122" t="n">
+        <x:f>H9</x:f>
+        <x:v>283</x:v>
+      </x:c>
+      <x:c r="D24" s="127" t="n">
+        <x:f>I9</x:f>
+        <x:v>94.33333333333333</x:v>
+      </x:c>
+      <x:c r="E24" s="125" t="n">
+        <x:f>J9</x:f>
+        <x:v>8.252</x:v>
+      </x:c>
+      <x:c r="F24" s="127" t="n">
         <x:f>C24/E24</x:f>
-        <x:v>463.36206896551727</x:v>
-      </x:c>
-      <x:c r="G24" s="76" t="n">
-        <x:f>AVERAGE(I131,I134,I142)</x:f>
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="H24" s="76" t="n">
-        <x:f>AVERAGE(J131,J134,J142)</x:f>
-        <x:v>76.66666666666667</x:v>
-      </x:c>
-      <x:c r="I24" s="71" t="str">
-        <x:f>IF(COUNTIFS($E$19:$E$26,"&lt;="&amp;E24,$C$19:$C$26,"&gt;="&amp;C24)-COUNTIFS($E$19:$E$26,E24,$C$19:$C$26,C24)&gt;0,"被支配","前沿")</x:f>
-        <x:v>前沿</x:v>
-      </x:c>
-      <x:c r="J24" s="71" t="n">
-        <x:f>K11</x:f>
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="K24" s="71" t="n">
-        <x:f>COUNTIF(B11,"&gt;=80")+COUNTIF(D11,"&gt;=80")+COUNTIF(F11,"&gt;=80")</x:f>
-        <x:v>1</x:v>
+        <x:v>34.29471643238003</x:v>
+      </x:c>
+      <x:c r="G24" s="127" t="n">
+        <x:f>AVERAGE(I143,I150,I160)</x:f>
+        <x:v>90.66666666666667</x:v>
+      </x:c>
+      <x:c r="H24" s="127" t="n">
+        <x:f>AVERAGE(J143,J150,J160)</x:f>
+        <x:v>97.33333333333333</x:v>
+      </x:c>
+      <x:c r="I24" s="122" t="str">
+        <x:f>IF(COUNTIFS($E$21:$E$30,"&lt;="&amp;E24,$C$21:$C$30,"&gt;="&amp;C24)-COUNTIFS($E$21:$E$30,E24,$C$21:$C$30,C24)&gt;0,"被支配","前沿")</x:f>
+        <x:v>被支配</x:v>
+      </x:c>
+      <x:c r="J24" s="122" t="n">
+        <x:f>K9</x:f>
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="K24" s="122" t="n">
+        <x:f>COUNTIF(B9,"&gt;=80")+COUNTIF(D9,"&gt;=80")+COUNTIF(F9,"&gt;=80")</x:f>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="L24" s="2"/>
       <x:c r="M24" s="2"/>
       <x:c r="N24" s="2" t="str">
-        <x:v>GPT-6 Luna max</x:v>
+        <x:v>GPT-5.6 Sol xhigh</x:v>
       </x:c>
       <x:c r="O24" s="2" t="n">
-        <x:f>LOG10('Task 1'!C8)</x:f>
-        <x:v>-0.749579997691106</x:v>
+        <x:f>LOG10('Task 1'!C2)</x:f>
+        <x:v>0.610873000380052</x:v>
       </x:c>
       <x:c r="P24" s="2" t="n">
-        <x:f>'Task 1'!D8</x:f>
-        <x:v>53</x:v>
+        <x:f>'Task 1'!D2</x:f>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="Q24" s="2"/>
       <x:c r="R24" s="2"/>
@@ -4195,60 +4778,60 @@
     </x:row>
     <x:row r="25" ht="21" customHeight="1">
       <x:c r="A25" s="2" t="str">
-        <x:v>DeepSeek V4.1 Flash max</x:v>
+        <x:v>Opus 5.5 xhigh</x:v>
       </x:c>
       <x:c r="B25" s="12" t="n">
-        <x:f>RANK(C25,$C$19:$C$26,0)</x:f>
-        <x:v>7</x:v>
+        <x:f>RANK(C25,$C$21:$C$30,0)</x:f>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C25" s="12" t="n">
-        <x:f>H12</x:f>
-        <x:v>176</x:v>
+        <x:f>H10</x:f>
+        <x:v>261</x:v>
       </x:c>
       <x:c r="D25" s="23" t="n">
-        <x:f>I12</x:f>
-        <x:v>58.666666666666664</x:v>
+        <x:f>I10</x:f>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="E25" s="20" t="n">
-        <x:f>J12</x:f>
-        <x:v>1.321</x:v>
+        <x:f>J10</x:f>
+        <x:v>50.77</x:v>
       </x:c>
       <x:c r="F25" s="23" t="n">
         <x:f>C25/E25</x:f>
-        <x:v>133.2323996971991</x:v>
+        <x:v>5.1408311995272795</x:v>
       </x:c>
       <x:c r="G25" s="23" t="n">
-        <x:f>AVERAGE(I132,I140,I148)</x:f>
-        <x:v>53.333333333333336</x:v>
+        <x:f>AVERAGE(I142,I154,I164)</x:f>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="H25" s="23" t="n">
-        <x:f>AVERAGE(J132,J140,J148)</x:f>
-        <x:v>65.33333333333333</x:v>
+        <x:f>AVERAGE(J142,J154,J164)</x:f>
+        <x:v>91.66666666666667</x:v>
       </x:c>
       <x:c r="I25" s="12" t="str">
-        <x:f>IF(COUNTIFS($E$19:$E$26,"&lt;="&amp;E25,$C$19:$C$26,"&gt;="&amp;C25)-COUNTIFS($E$19:$E$26,E25,$C$19:$C$26,C25)&gt;0,"被支配","前沿")</x:f>
+        <x:f>IF(COUNTIFS($E$21:$E$30,"&lt;="&amp;E25,$C$21:$C$30,"&gt;="&amp;C25)-COUNTIFS($E$21:$E$30,E25,$C$21:$C$30,C25)&gt;0,"被支配","前沿")</x:f>
         <x:v>被支配</x:v>
       </x:c>
       <x:c r="J25" s="12" t="n">
-        <x:f>K12</x:f>
-        <x:v>47</x:v>
+        <x:f>K10</x:f>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="K25" s="12" t="n">
-        <x:f>COUNTIF(B12,"&gt;=80")+COUNTIF(D12,"&gt;=80")+COUNTIF(F12,"&gt;=80")</x:f>
-        <x:v>0</x:v>
+        <x:f>COUNTIF(B10,"&gt;=80")+COUNTIF(D10,"&gt;=80")+COUNTIF(F10,"&gt;=80")</x:f>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="L25" s="2"/>
       <x:c r="M25" s="2"/>
       <x:c r="N25" s="2" t="str">
-        <x:v>DeepSeek V4.1 Flash max</x:v>
+        <x:v>GPT-6 Sol xhigh</x:v>
       </x:c>
       <x:c r="O25" s="2" t="n">
-        <x:f>LOG10('Task 1'!C9)</x:f>
-        <x:v>-0.382999658879101</x:v>
+        <x:f>LOG10('Task 1'!C4)</x:f>
+        <x:v>0.377670439334323</x:v>
       </x:c>
       <x:c r="P25" s="2" t="n">
-        <x:f>'Task 1'!D9</x:f>
-        <x:v>47</x:v>
+        <x:f>'Task 1'!D4</x:f>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="Q25" s="2"/>
       <x:c r="R25" s="2"/>
@@ -4258,61 +4841,61 @@
       <x:c r="V25" s="2"/>
     </x:row>
     <x:row r="26" ht="21" customHeight="1">
-      <x:c r="A26" s="72" t="str">
-        <x:v>Grok 4.7 high</x:v>
-      </x:c>
-      <x:c r="B26" s="73" t="n">
-        <x:f>RANK(C26,$C$19:$C$26,0)</x:f>
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C26" s="73" t="n">
-        <x:f>H13</x:f>
-        <x:v>169</x:v>
-      </x:c>
-      <x:c r="D26" s="77" t="n">
-        <x:f>I13</x:f>
-        <x:v>56.333333333333336</x:v>
-      </x:c>
-      <x:c r="E26" s="75" t="n">
-        <x:f>J13</x:f>
-        <x:v>14.676</x:v>
-      </x:c>
-      <x:c r="F26" s="77" t="n">
+      <x:c r="A26" s="121" t="str">
+        <x:v>GPT-6 Sol xhigh</x:v>
+      </x:c>
+      <x:c r="B26" s="122" t="n">
+        <x:f>RANK(C26,$C$21:$C$30,0)</x:f>
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="C26" s="122" t="n">
+        <x:f>H11</x:f>
+        <x:v>236</x:v>
+      </x:c>
+      <x:c r="D26" s="127" t="n">
+        <x:f>I11</x:f>
+        <x:v>78.66666666666667</x:v>
+      </x:c>
+      <x:c r="E26" s="125" t="n">
+        <x:f>J11</x:f>
+        <x:v>6.184</x:v>
+      </x:c>
+      <x:c r="F26" s="127" t="n">
         <x:f>C26/E26</x:f>
-        <x:v>11.515399291360044</x:v>
-      </x:c>
-      <x:c r="G26" s="77" t="n">
-        <x:f>AVERAGE(I128,I138,I146)</x:f>
-        <x:v>51.333333333333336</x:v>
-      </x:c>
-      <x:c r="H26" s="77" t="n">
-        <x:f>AVERAGE(J128,J138,J146)</x:f>
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="I26" s="73" t="str">
-        <x:f>IF(COUNTIFS($E$19:$E$26,"&lt;="&amp;E26,$C$19:$C$26,"&gt;="&amp;C26)-COUNTIFS($E$19:$E$26,E26,$C$19:$C$26,C26)&gt;0,"被支配","前沿")</x:f>
+        <x:v>38.16300129366106</x:v>
+      </x:c>
+      <x:c r="G26" s="127" t="n">
+        <x:f>AVERAGE(I140,I151,I161)</x:f>
+        <x:v>74.33333333333333</x:v>
+      </x:c>
+      <x:c r="H26" s="127" t="n">
+        <x:f>AVERAGE(J140,J151,J161)</x:f>
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="I26" s="122" t="str">
+        <x:f>IF(COUNTIFS($E$21:$E$30,"&lt;="&amp;E26,$C$21:$C$30,"&gt;="&amp;C26)-COUNTIFS($E$21:$E$30,E26,$C$21:$C$30,C26)&gt;0,"被支配","前沿")</x:f>
         <x:v>被支配</x:v>
       </x:c>
-      <x:c r="J26" s="73" t="n">
-        <x:f>K13</x:f>
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="K26" s="73" t="n">
-        <x:f>COUNTIF(B13,"&gt;=80")+COUNTIF(D13,"&gt;=80")+COUNTIF(F13,"&gt;=80")</x:f>
-        <x:v>0</x:v>
+      <x:c r="J26" s="122" t="n">
+        <x:f>K11</x:f>
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="K26" s="122" t="n">
+        <x:f>COUNTIF(B11,"&gt;=80")+COUNTIF(D11,"&gt;=80")+COUNTIF(F11,"&gt;=80")</x:f>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="L26" s="2"/>
       <x:c r="M26" s="2"/>
       <x:c r="N26" s="2" t="str">
-        <x:v>Grok 4.7 high</x:v>
+        <x:v>GPT-6 Luna max</x:v>
       </x:c>
       <x:c r="O26" s="2" t="n">
-        <x:f>LOG10('Task 1'!C5)</x:f>
-        <x:v>0.654561554741743</x:v>
+        <x:f>LOG10('Task 1'!C8)</x:f>
+        <x:v>-0.749579997691106</x:v>
       </x:c>
       <x:c r="P26" s="2" t="n">
-        <x:f>'Task 1'!D5</x:f>
-        <x:v>30</x:v>
+        <x:f>'Task 1'!D8</x:f>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="Q26" s="2"/>
       <x:c r="R26" s="2"/>
@@ -4322,22 +4905,62 @@
       <x:c r="V26" s="2"/>
     </x:row>
     <x:row r="27" ht="21" customHeight="1">
-      <x:c r="A27" s="2"/>
-      <x:c r="B27" s="2"/>
-      <x:c r="C27" s="2"/>
-      <x:c r="D27" s="2"/>
-      <x:c r="E27" s="2"/>
-      <x:c r="F27" s="2"/>
-      <x:c r="G27" s="2"/>
-      <x:c r="H27" s="2"/>
-      <x:c r="I27" s="2"/>
-      <x:c r="J27" s="2"/>
-      <x:c r="K27" s="2"/>
+      <x:c r="A27" s="2" t="str">
+        <x:v>GPT-5.6 Sol xhigh</x:v>
+      </x:c>
+      <x:c r="B27" s="12" t="n">
+        <x:f>RANK(C27,$C$21:$C$30,0)</x:f>
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C27" s="12" t="n">
+        <x:f>H12</x:f>
+        <x:v>226</x:v>
+      </x:c>
+      <x:c r="D27" s="23" t="n">
+        <x:f>I12</x:f>
+        <x:v>75.33333333333333</x:v>
+      </x:c>
+      <x:c r="E27" s="20" t="n">
+        <x:f>J12</x:f>
+        <x:v>20.805</x:v>
+      </x:c>
+      <x:c r="F27" s="23" t="n">
+        <x:f>C27/E27</x:f>
+        <x:v>10.862773371785629</x:v>
+      </x:c>
+      <x:c r="G27" s="23" t="n">
+        <x:f>AVERAGE(I138,I148,I158)</x:f>
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="H27" s="23" t="n">
+        <x:f>AVERAGE(J138,J148,J158)</x:f>
+        <x:v>79.66666666666667</x:v>
+      </x:c>
+      <x:c r="I27" s="12" t="str">
+        <x:f>IF(COUNTIFS($E$21:$E$30,"&lt;="&amp;E27,$C$21:$C$30,"&gt;="&amp;C27)-COUNTIFS($E$21:$E$30,E27,$C$21:$C$30,C27)&gt;0,"被支配","前沿")</x:f>
+        <x:v>被支配</x:v>
+      </x:c>
+      <x:c r="J27" s="12" t="n">
+        <x:f>K12</x:f>
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="K27" s="12" t="n">
+        <x:f>COUNTIF(B12,"&gt;=80")+COUNTIF(D12,"&gt;=80")+COUNTIF(F12,"&gt;=80")</x:f>
+        <x:v>2</x:v>
+      </x:c>
       <x:c r="L27" s="2"/>
       <x:c r="M27" s="2"/>
-      <x:c r="N27" s="2"/>
-      <x:c r="O27" s="2"/>
-      <x:c r="P27" s="2"/>
+      <x:c r="N27" s="2" t="str">
+        <x:v>DeepSeek V4.1 Flash max</x:v>
+      </x:c>
+      <x:c r="O27" s="2" t="n">
+        <x:f>LOG10('Task 1'!C9)</x:f>
+        <x:v>-0.382999658879101</x:v>
+      </x:c>
+      <x:c r="P27" s="2" t="n">
+        <x:f>'Task 1'!D9</x:f>
+        <x:v>47</x:v>
+      </x:c>
       <x:c r="Q27" s="2"/>
       <x:c r="R27" s="2"/>
       <x:c r="S27" s="2"/>
@@ -4346,24 +4969,62 @@
       <x:c r="V27" s="2"/>
     </x:row>
     <x:row r="28" ht="21" customHeight="1">
-      <x:c r="A28" s="4" t="str">
-        <x:v>评阅上下限是三题判断范围端点的均值，不是统计置信区间；前沿以中心分数判定。总分 / USD 仅为辅助指标。</x:v>
-      </x:c>
-      <x:c r="B28" s="4"/>
-      <x:c r="C28" s="4"/>
-      <x:c r="D28" s="4"/>
-      <x:c r="E28" s="4"/>
-      <x:c r="F28" s="4"/>
-      <x:c r="G28" s="4"/>
-      <x:c r="H28" s="4"/>
-      <x:c r="I28" s="4"/>
-      <x:c r="J28" s="4"/>
-      <x:c r="K28" s="4"/>
+      <x:c r="A28" s="121" t="str">
+        <x:v>GPT-6 Luna max</x:v>
+      </x:c>
+      <x:c r="B28" s="122" t="n">
+        <x:f>RANK(C28,$C$21:$C$30,0)</x:f>
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C28" s="122" t="n">
+        <x:f>H13</x:f>
+        <x:v>215</x:v>
+      </x:c>
+      <x:c r="D28" s="127" t="n">
+        <x:f>I13</x:f>
+        <x:v>71.66666666666667</x:v>
+      </x:c>
+      <x:c r="E28" s="125" t="n">
+        <x:f>J13</x:f>
+        <x:v>0.46399999999999997</x:v>
+      </x:c>
+      <x:c r="F28" s="127" t="n">
+        <x:f>C28/E28</x:f>
+        <x:v>463.36206896551727</x:v>
+      </x:c>
+      <x:c r="G28" s="127" t="n">
+        <x:f>AVERAGE(I144,I149,I159)</x:f>
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="H28" s="127" t="n">
+        <x:f>AVERAGE(J144,J149,J159)</x:f>
+        <x:v>76.66666666666667</x:v>
+      </x:c>
+      <x:c r="I28" s="122" t="str">
+        <x:f>IF(COUNTIFS($E$21:$E$30,"&lt;="&amp;E28,$C$21:$C$30,"&gt;="&amp;C28)-COUNTIFS($E$21:$E$30,E28,$C$21:$C$30,C28)&gt;0,"被支配","前沿")</x:f>
+        <x:v>前沿</x:v>
+      </x:c>
+      <x:c r="J28" s="122" t="n">
+        <x:f>K13</x:f>
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="K28" s="122" t="n">
+        <x:f>COUNTIF(B13,"&gt;=80")+COUNTIF(D13,"&gt;=80")+COUNTIF(F13,"&gt;=80")</x:f>
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="L28" s="2"/>
       <x:c r="M28" s="2"/>
-      <x:c r="N28" s="2"/>
-      <x:c r="O28" s="2"/>
-      <x:c r="P28" s="2"/>
+      <x:c r="N28" s="2" t="str">
+        <x:v>Grok 4.7 high</x:v>
+      </x:c>
+      <x:c r="O28" s="2" t="n">
+        <x:f>LOG10('Task 1'!C5)</x:f>
+        <x:v>0.654561554741743</x:v>
+      </x:c>
+      <x:c r="P28" s="2" t="n">
+        <x:f>'Task 1'!D5</x:f>
+        <x:v>30</x:v>
+      </x:c>
       <x:c r="Q28" s="2"/>
       <x:c r="R28" s="2"/>
       <x:c r="S28" s="2"/>
@@ -4372,17 +5033,49 @@
       <x:c r="V28" s="2"/>
     </x:row>
     <x:row r="29" ht="21" customHeight="1">
-      <x:c r="A29" s="2"/>
-      <x:c r="B29" s="2"/>
-      <x:c r="C29" s="2"/>
-      <x:c r="D29" s="2"/>
-      <x:c r="E29" s="2"/>
-      <x:c r="F29" s="2"/>
-      <x:c r="G29" s="2"/>
-      <x:c r="H29" s="2"/>
-      <x:c r="I29" s="2"/>
-      <x:c r="J29" s="2"/>
-      <x:c r="K29" s="2"/>
+      <x:c r="A29" s="2" t="str">
+        <x:v>DeepSeek V4.1 Flash max</x:v>
+      </x:c>
+      <x:c r="B29" s="12" t="n">
+        <x:f>RANK(C29,$C$21:$C$30,0)</x:f>
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="C29" s="12" t="n">
+        <x:f>H14</x:f>
+        <x:v>176</x:v>
+      </x:c>
+      <x:c r="D29" s="23" t="n">
+        <x:f>I14</x:f>
+        <x:v>58.666666666666664</x:v>
+      </x:c>
+      <x:c r="E29" s="20" t="n">
+        <x:f>J14</x:f>
+        <x:v>1.321</x:v>
+      </x:c>
+      <x:c r="F29" s="23" t="n">
+        <x:f>C29/E29</x:f>
+        <x:v>133.2323996971991</x:v>
+      </x:c>
+      <x:c r="G29" s="23" t="n">
+        <x:f>AVERAGE(I145,I155,I165)</x:f>
+        <x:v>53.333333333333336</x:v>
+      </x:c>
+      <x:c r="H29" s="23" t="n">
+        <x:f>AVERAGE(J145,J155,J165)</x:f>
+        <x:v>65.33333333333333</x:v>
+      </x:c>
+      <x:c r="I29" s="12" t="str">
+        <x:f>IF(COUNTIFS($E$21:$E$30,"&lt;="&amp;E29,$C$21:$C$30,"&gt;="&amp;C29)-COUNTIFS($E$21:$E$30,E29,$C$21:$C$30,C29)&gt;0,"被支配","前沿")</x:f>
+        <x:v>被支配</x:v>
+      </x:c>
+      <x:c r="J29" s="12" t="n">
+        <x:f>K14</x:f>
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="K29" s="12" t="n">
+        <x:f>COUNTIF(B14,"&gt;=80")+COUNTIF(D14,"&gt;=80")+COUNTIF(F14,"&gt;=80")</x:f>
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="L29" s="2"/>
       <x:c r="M29" s="2"/>
       <x:c r="N29" s="2"/>
@@ -4395,20 +5088,50 @@
       <x:c r="U29" s="2"/>
       <x:c r="V29" s="2"/>
     </x:row>
-    <x:row r="30" ht="24" customHeight="1">
-      <x:c r="A30" s="27" t="str">
-        <x:v>五个评分维度的三题均值</x:v>
-      </x:c>
-      <x:c r="B30" s="27"/>
-      <x:c r="C30" s="27"/>
-      <x:c r="D30" s="27"/>
-      <x:c r="E30" s="27"/>
-      <x:c r="F30" s="27"/>
-      <x:c r="G30" s="27"/>
-      <x:c r="H30" s="27"/>
-      <x:c r="I30" s="27"/>
-      <x:c r="J30" s="27"/>
-      <x:c r="K30" s="27"/>
+    <x:row r="30" ht="21" customHeight="1">
+      <x:c r="A30" s="123" t="str">
+        <x:v>Grok 4.7 high</x:v>
+      </x:c>
+      <x:c r="B30" s="124" t="n">
+        <x:f>RANK(C30,$C$21:$C$30,0)</x:f>
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="C30" s="124" t="n">
+        <x:f>H15</x:f>
+        <x:v>169</x:v>
+      </x:c>
+      <x:c r="D30" s="128" t="n">
+        <x:f>I15</x:f>
+        <x:v>56.333333333333336</x:v>
+      </x:c>
+      <x:c r="E30" s="126" t="n">
+        <x:f>J15</x:f>
+        <x:v>14.676</x:v>
+      </x:c>
+      <x:c r="F30" s="128" t="n">
+        <x:f>C30/E30</x:f>
+        <x:v>11.515399291360044</x:v>
+      </x:c>
+      <x:c r="G30" s="128" t="n">
+        <x:f>AVERAGE(I141,I153,I163)</x:f>
+        <x:v>51.333333333333336</x:v>
+      </x:c>
+      <x:c r="H30" s="128" t="n">
+        <x:f>AVERAGE(J141,J153,J163)</x:f>
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="I30" s="124" t="str">
+        <x:f>IF(COUNTIFS($E$21:$E$30,"&lt;="&amp;E30,$C$21:$C$30,"&gt;="&amp;C30)-COUNTIFS($E$21:$E$30,E30,$C$21:$C$30,C30)&gt;0,"被支配","前沿")</x:f>
+        <x:v>被支配</x:v>
+      </x:c>
+      <x:c r="J30" s="124" t="n">
+        <x:f>K15</x:f>
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="K30" s="124" t="n">
+        <x:f>COUNTIF(B15,"&gt;=80")+COUNTIF(D15,"&gt;=80")+COUNTIF(F15,"&gt;=80")</x:f>
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="L30" s="2"/>
       <x:c r="M30" s="2"/>
       <x:c r="N30" s="2" t="str">
@@ -4427,52 +5150,30 @@
       <x:c r="U30" s="2"/>
       <x:c r="V30" s="2"/>
     </x:row>
-    <x:row r="31" ht="35" customHeight="1">
-      <x:c r="A31" s="69" t="str">
-        <x:v>模型配置</x:v>
-      </x:c>
-      <x:c r="B31" s="69" t="str">
-        <x:v>定义 /15</x:v>
-      </x:c>
-      <x:c r="C31" s="69" t="str">
-        <x:v>校准 /30</x:v>
-      </x:c>
-      <x:c r="D31" s="69" t="str">
-        <x:v>验证 /15</x:v>
-      </x:c>
-      <x:c r="E31" s="69" t="str">
-        <x:v>推进 /30</x:v>
-      </x:c>
-      <x:c r="F31" s="69" t="str">
-        <x:v>结论 /10</x:v>
-      </x:c>
-      <x:c r="G31" s="69" t="str">
-        <x:v>均分 /100</x:v>
-      </x:c>
-      <x:c r="H31" s="69" t="str">
-        <x:v>第 1 题</x:v>
-      </x:c>
-      <x:c r="I31" s="69" t="str">
-        <x:v>第 2 题</x:v>
-      </x:c>
-      <x:c r="J31" s="69" t="str">
-        <x:v>第 3 题</x:v>
-      </x:c>
-      <x:c r="K31" s="69" t="str">
-        <x:v>分差范围</x:v>
-      </x:c>
+    <x:row r="31" ht="21" customHeight="1">
+      <x:c r="A31" s="2"/>
+      <x:c r="B31" s="2"/>
+      <x:c r="C31" s="2"/>
+      <x:c r="D31" s="2"/>
+      <x:c r="E31" s="2"/>
+      <x:c r="F31" s="2"/>
+      <x:c r="G31" s="2"/>
+      <x:c r="H31" s="2"/>
+      <x:c r="I31" s="2"/>
+      <x:c r="J31" s="2"/>
+      <x:c r="K31" s="2"/>
       <x:c r="L31" s="2"/>
       <x:c r="M31" s="2"/>
       <x:c r="N31" s="2" t="str">
-        <x:v>GPT-6 Astra high</x:v>
+        <x:v>GPT-6.1 Sol xhigh</x:v>
       </x:c>
       <x:c r="O31" s="2" t="n">
-        <x:f>LOG10('Task 2'!C6)</x:f>
-        <x:v>0.658011396657112</x:v>
+        <x:f>LOG10('Task 2'!C10)</x:f>
+        <x:v>0.0457140589408676</x:v>
       </x:c>
       <x:c r="P31" s="2" t="n">
-        <x:f>'Task 2'!D6</x:f>
-        <x:v>97</x:v>
+        <x:f>'Task 2'!D10</x:f>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="Q31" s="2"/>
       <x:c r="R31" s="2"/>
@@ -4482,61 +5183,31 @@
       <x:c r="V31" s="2"/>
     </x:row>
     <x:row r="32" ht="21" customHeight="1">
-      <x:c r="A32" s="2" t="str">
-        <x:v>GPT-6 Astra high</x:v>
-      </x:c>
-      <x:c r="B32" s="23" t="n">
-        <x:f>AVERAGE(C126,C137,C145)</x:f>
-        <x:v>14.666666666666666</x:v>
-      </x:c>
-      <x:c r="C32" s="23" t="n">
-        <x:f>AVERAGE(D126,D137,D145)</x:f>
-        <x:v>29.333333333333332</x:v>
-      </x:c>
-      <x:c r="D32" s="23" t="n">
-        <x:f>AVERAGE(E126,E137,E145)</x:f>
-        <x:v>13.666666666666666</x:v>
-      </x:c>
-      <x:c r="E32" s="23" t="n">
-        <x:f>AVERAGE(F126,F137,F145)</x:f>
-        <x:v>28.333333333333332</x:v>
-      </x:c>
-      <x:c r="F32" s="23" t="n">
-        <x:f>AVERAGE(G126,G137,G145)</x:f>
-        <x:v>9.666666666666666</x:v>
-      </x:c>
-      <x:c r="G32" s="23" t="n">
-        <x:f>SUM(B32:F32)</x:f>
-        <x:v>95.66666666666667</x:v>
-      </x:c>
-      <x:c r="H32" s="12" t="n">
-        <x:f>B6</x:f>
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="I32" s="12" t="n">
-        <x:f>D6</x:f>
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="J32" s="12" t="n">
-        <x:f>F6</x:f>
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="K32" s="12" t="n">
-        <x:f>MAX(H32:J32)-MIN(H32:J32)</x:f>
-        <x:v>6</x:v>
-      </x:c>
+      <x:c r="A32" s="129" t="str">
+        <x:v>评阅范围是三题判断范围端点的均值，非统计置信区间；前沿以中心分数判定。总分 / USD 仅为辅助指标。</x:v>
+      </x:c>
+      <x:c r="B32" s="129"/>
+      <x:c r="C32" s="129"/>
+      <x:c r="D32" s="129"/>
+      <x:c r="E32" s="129"/>
+      <x:c r="F32" s="129"/>
+      <x:c r="G32" s="129"/>
+      <x:c r="H32" s="129"/>
+      <x:c r="I32" s="129"/>
+      <x:c r="J32" s="129"/>
+      <x:c r="K32" s="129"/>
       <x:c r="L32" s="2"/>
       <x:c r="M32" s="2"/>
       <x:c r="N32" s="2" t="str">
-        <x:v>GPT-6 Sol max</x:v>
+        <x:v>GPT-6.1 Sol max</x:v>
       </x:c>
       <x:c r="O32" s="2" t="n">
-        <x:f>LOG10('Task 2'!C4)</x:f>
-        <x:v>0.258637282724076</x:v>
+        <x:f>LOG10('Task 2'!C11)</x:f>
+        <x:v>0.0569048513364726</x:v>
       </x:c>
       <x:c r="P32" s="2" t="n">
-        <x:f>'Task 2'!D4</x:f>
-        <x:v>94</x:v>
+        <x:f>'Task 2'!D11</x:f>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="Q32" s="2"/>
       <x:c r="R32" s="2"/>
@@ -4546,61 +5217,29 @@
       <x:c r="V32" s="2"/>
     </x:row>
     <x:row r="33" ht="21" customHeight="1">
-      <x:c r="A33" s="70" t="str">
-        <x:v>GPT-6 Sol max</x:v>
-      </x:c>
-      <x:c r="B33" s="76" t="n">
-        <x:f>AVERAGE(C130,C135,C143)</x:f>
-        <x:v>14.666666666666666</x:v>
-      </x:c>
-      <x:c r="C33" s="76" t="n">
-        <x:f>AVERAGE(D130,D135,D143)</x:f>
-        <x:v>29.333333333333332</x:v>
-      </x:c>
-      <x:c r="D33" s="76" t="n">
-        <x:f>AVERAGE(E130,E135,E143)</x:f>
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="E33" s="76" t="n">
-        <x:f>AVERAGE(F130,F135,F143)</x:f>
-        <x:v>27.333333333333332</x:v>
-      </x:c>
-      <x:c r="F33" s="76" t="n">
-        <x:f>AVERAGE(G130,G135,G143)</x:f>
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="G33" s="76" t="n">
-        <x:f>SUM(B33:F33)</x:f>
-        <x:v>94.33333333333333</x:v>
-      </x:c>
-      <x:c r="H33" s="71" t="n">
-        <x:f>B7</x:f>
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="I33" s="71" t="n">
-        <x:f>D7</x:f>
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="J33" s="71" t="n">
-        <x:f>F7</x:f>
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="K33" s="71" t="n">
-        <x:f>MAX(H33:J33)-MIN(H33:J33)</x:f>
-        <x:v>1</x:v>
-      </x:c>
+      <x:c r="A33" s="2"/>
+      <x:c r="B33" s="2"/>
+      <x:c r="C33" s="2"/>
+      <x:c r="D33" s="2"/>
+      <x:c r="E33" s="2"/>
+      <x:c r="F33" s="2"/>
+      <x:c r="G33" s="2"/>
+      <x:c r="H33" s="2"/>
+      <x:c r="I33" s="2"/>
+      <x:c r="J33" s="2"/>
+      <x:c r="K33" s="2"/>
       <x:c r="L33" s="2"/>
       <x:c r="M33" s="2"/>
       <x:c r="N33" s="2" t="str">
-        <x:v>Opus 5.5 xhigh</x:v>
+        <x:v>GPT-6 Astra high</x:v>
       </x:c>
       <x:c r="O33" s="2" t="n">
-        <x:f>LOG10('Task 2'!C8)</x:f>
-        <x:v>1.09096307659573</x:v>
+        <x:f>LOG10('Task 2'!C6)</x:f>
+        <x:v>0.658011396657112</x:v>
       </x:c>
       <x:c r="P33" s="2" t="n">
-        <x:f>'Task 2'!D8</x:f>
-        <x:v>93</x:v>
+        <x:f>'Task 2'!D6</x:f>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="Q33" s="2"/>
       <x:c r="R33" s="2"/>
@@ -4609,62 +5248,32 @@
       <x:c r="U33" s="2"/>
       <x:c r="V33" s="2"/>
     </x:row>
-    <x:row r="34" ht="21" customHeight="1">
-      <x:c r="A34" s="2" t="str">
-        <x:v>Opus 5.5 xhigh</x:v>
-      </x:c>
-      <x:c r="B34" s="23" t="n">
-        <x:f>AVERAGE(C129,C139,C147)</x:f>
-        <x:v>13.666666666666666</x:v>
-      </x:c>
-      <x:c r="C34" s="23" t="n">
-        <x:f>AVERAGE(D129,D139,D147)</x:f>
-        <x:v>28.333333333333332</x:v>
-      </x:c>
-      <x:c r="D34" s="23" t="n">
-        <x:f>AVERAGE(E129,E139,E147)</x:f>
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="E34" s="23" t="n">
-        <x:f>AVERAGE(F129,F139,F147)</x:f>
-        <x:v>25.666666666666668</x:v>
-      </x:c>
-      <x:c r="F34" s="23" t="n">
-        <x:f>AVERAGE(G129,G139,G147)</x:f>
-        <x:v>6.333333333333333</x:v>
-      </x:c>
-      <x:c r="G34" s="23" t="n">
-        <x:f>SUM(B34:F34)</x:f>
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="H34" s="12" t="n">
-        <x:f>B8</x:f>
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="I34" s="12" t="n">
-        <x:f>D8</x:f>
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="J34" s="12" t="n">
-        <x:f>F8</x:f>
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="K34" s="12" t="n">
-        <x:f>MAX(H34:J34)-MIN(H34:J34)</x:f>
-        <x:v>12</x:v>
-      </x:c>
+    <x:row r="34" ht="24" customHeight="1">
+      <x:c r="A34" s="27" t="str">
+        <x:v>五个评分维度的三题均值</x:v>
+      </x:c>
+      <x:c r="B34" s="27"/>
+      <x:c r="C34" s="27"/>
+      <x:c r="D34" s="27"/>
+      <x:c r="E34" s="27"/>
+      <x:c r="F34" s="27"/>
+      <x:c r="G34" s="27"/>
+      <x:c r="H34" s="27"/>
+      <x:c r="I34" s="27"/>
+      <x:c r="J34" s="27"/>
+      <x:c r="K34" s="27"/>
       <x:c r="L34" s="2"/>
       <x:c r="M34" s="2"/>
       <x:c r="N34" s="2" t="str">
-        <x:v>GPT-6 Sol xhigh</x:v>
+        <x:v>GPT-6 Sol max</x:v>
       </x:c>
       <x:c r="O34" s="2" t="n">
-        <x:f>LOG10('Task 2'!C5)</x:f>
-        <x:v>0.33344727449675</x:v>
+        <x:f>LOG10('Task 2'!C4)</x:f>
+        <x:v>0.258637282724076</x:v>
       </x:c>
       <x:c r="P34" s="2" t="n">
-        <x:f>'Task 2'!D5</x:f>
-        <x:v>92</x:v>
+        <x:f>'Task 2'!D4</x:f>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="Q34" s="2"/>
       <x:c r="R34" s="2"/>
@@ -4673,62 +5282,52 @@
       <x:c r="U34" s="2"/>
       <x:c r="V34" s="2"/>
     </x:row>
-    <x:row r="35" ht="21" customHeight="1">
-      <x:c r="A35" s="70" t="str">
-        <x:v>GPT-6 Sol xhigh</x:v>
-      </x:c>
-      <x:c r="B35" s="76" t="n">
-        <x:f>AVERAGE(C127,C136,C144)</x:f>
-        <x:v>14.666666666666666</x:v>
-      </x:c>
-      <x:c r="C35" s="76" t="n">
-        <x:f>AVERAGE(D127,D136,D144)</x:f>
-        <x:v>26.333333333333332</x:v>
-      </x:c>
-      <x:c r="D35" s="76" t="n">
-        <x:f>AVERAGE(E127,E136,E144)</x:f>
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="E35" s="76" t="n">
-        <x:f>AVERAGE(F127,F136,F144)</x:f>
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="F35" s="76" t="n">
-        <x:f>AVERAGE(G127,G136,G144)</x:f>
-        <x:v>8.666666666666666</x:v>
-      </x:c>
-      <x:c r="G35" s="76" t="n">
-        <x:f>SUM(B35:F35)</x:f>
-        <x:v>78.66666666666667</x:v>
-      </x:c>
-      <x:c r="H35" s="71" t="n">
-        <x:f>B9</x:f>
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="I35" s="71" t="n">
-        <x:f>D9</x:f>
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="J35" s="71" t="n">
-        <x:f>F9</x:f>
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="K35" s="71" t="n">
-        <x:f>MAX(H35:J35)-MIN(H35:J35)</x:f>
-        <x:v>38</x:v>
+    <x:row r="35" ht="35" customHeight="1">
+      <x:c r="A35" s="120" t="str">
+        <x:v>模型配置</x:v>
+      </x:c>
+      <x:c r="B35" s="120" t="str">
+        <x:v>定义 /15</x:v>
+      </x:c>
+      <x:c r="C35" s="120" t="str">
+        <x:v>校准 /30</x:v>
+      </x:c>
+      <x:c r="D35" s="120" t="str">
+        <x:v>验证 /15</x:v>
+      </x:c>
+      <x:c r="E35" s="120" t="str">
+        <x:v>推进 /30</x:v>
+      </x:c>
+      <x:c r="F35" s="120" t="str">
+        <x:v>结论 /10</x:v>
+      </x:c>
+      <x:c r="G35" s="120" t="str">
+        <x:v>均分 /100</x:v>
+      </x:c>
+      <x:c r="H35" s="120" t="str">
+        <x:v>第 1 题</x:v>
+      </x:c>
+      <x:c r="I35" s="120" t="str">
+        <x:v>第 2 题</x:v>
+      </x:c>
+      <x:c r="J35" s="120" t="str">
+        <x:v>第 3 题</x:v>
+      </x:c>
+      <x:c r="K35" s="120" t="str">
+        <x:v>分差范围</x:v>
       </x:c>
       <x:c r="L35" s="2"/>
       <x:c r="M35" s="2"/>
       <x:c r="N35" s="2" t="str">
-        <x:v>GPT-5.6 Sol xhigh</x:v>
+        <x:v>Opus 5.5 xhigh</x:v>
       </x:c>
       <x:c r="O35" s="2" t="n">
-        <x:f>LOG10('Task 2'!C2)</x:f>
-        <x:v>0.441380884916511</x:v>
+        <x:f>LOG10('Task 2'!C8)</x:f>
+        <x:v>1.09096307659573</x:v>
       </x:c>
       <x:c r="P35" s="2" t="n">
-        <x:f>'Task 2'!D2</x:f>
-        <x:v>87</x:v>
+        <x:f>'Task 2'!D8</x:f>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="Q35" s="2"/>
       <x:c r="R35" s="2"/>
@@ -4739,60 +5338,60 @@
     </x:row>
     <x:row r="36" ht="21" customHeight="1">
       <x:c r="A36" s="2" t="str">
-        <x:v>GPT-5.6 Sol xhigh</x:v>
+        <x:v>GPT-6.1 Sol max</x:v>
       </x:c>
       <x:c r="B36" s="23" t="n">
-        <x:f>AVERAGE(C125,C133,C141)</x:f>
-        <x:v>14</x:v>
+        <x:f>AVERAGE(C147,C157,C167)</x:f>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C36" s="23" t="n">
-        <x:f>AVERAGE(D125,D133,D141)</x:f>
-        <x:v>25</x:v>
+        <x:f>AVERAGE(D147,D157,D167)</x:f>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D36" s="23" t="n">
-        <x:f>AVERAGE(E125,E133,E141)</x:f>
-        <x:v>10.333333333333334</x:v>
+        <x:f>AVERAGE(E147,E157,E167)</x:f>
+        <x:v>13.666666666666666</x:v>
       </x:c>
       <x:c r="E36" s="23" t="n">
-        <x:f>AVERAGE(F125,F133,F141)</x:f>
-        <x:v>18.333333333333332</x:v>
+        <x:f>AVERAGE(F147,F157,F167)</x:f>
+        <x:v>29.333333333333332</x:v>
       </x:c>
       <x:c r="F36" s="23" t="n">
-        <x:f>AVERAGE(G125,G133,G141)</x:f>
-        <x:v>7.666666666666667</x:v>
+        <x:f>AVERAGE(G147,G157,G167)</x:f>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="G36" s="23" t="n">
         <x:f>SUM(B36:F36)</x:f>
-        <x:v>75.33333333333334</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="H36" s="12" t="n">
-        <x:f>B10</x:f>
-        <x:v>57</x:v>
+        <x:f>B6</x:f>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="I36" s="12" t="n">
-        <x:f>D10</x:f>
-        <x:v>87</x:v>
+        <x:f>D6</x:f>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="J36" s="12" t="n">
-        <x:f>F10</x:f>
-        <x:v>82</x:v>
+        <x:f>F6</x:f>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="K36" s="12" t="n">
         <x:f>MAX(H36:J36)-MIN(H36:J36)</x:f>
-        <x:v>30</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="L36" s="2"/>
       <x:c r="M36" s="2"/>
       <x:c r="N36" s="2" t="str">
-        <x:v>GPT-6 Luna max</x:v>
+        <x:v>GPT-6 Sol xhigh</x:v>
       </x:c>
       <x:c r="O36" s="2" t="n">
-        <x:f>LOG10('Task 2'!C3)</x:f>
-        <x:v>-0.844663962534938</x:v>
+        <x:f>LOG10('Task 2'!C5)</x:f>
+        <x:v>0.33344727449675</x:v>
       </x:c>
       <x:c r="P36" s="2" t="n">
-        <x:f>'Task 2'!D3</x:f>
-        <x:v>86</x:v>
+        <x:f>'Task 2'!D5</x:f>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="Q36" s="2"/>
       <x:c r="R36" s="2"/>
@@ -4802,61 +5401,61 @@
       <x:c r="V36" s="2"/>
     </x:row>
     <x:row r="37" ht="21" customHeight="1">
-      <x:c r="A37" s="70" t="str">
-        <x:v>GPT-6 Luna max</x:v>
-      </x:c>
-      <x:c r="B37" s="76" t="n">
-        <x:f>AVERAGE(C131,C134,C142)</x:f>
-        <x:v>14.666666666666666</x:v>
-      </x:c>
-      <x:c r="C37" s="76" t="n">
-        <x:f>AVERAGE(D131,D134,D142)</x:f>
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="D37" s="76" t="n">
-        <x:f>AVERAGE(E131,E134,E142)</x:f>
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="E37" s="76" t="n">
-        <x:f>AVERAGE(F131,F134,F142)</x:f>
-        <x:v>14.666666666666666</x:v>
-      </x:c>
-      <x:c r="F37" s="76" t="n">
-        <x:f>AVERAGE(G131,G134,G142)</x:f>
-        <x:v>8.333333333333334</x:v>
-      </x:c>
-      <x:c r="G37" s="76" t="n">
+      <x:c r="A37" s="121" t="str">
+        <x:v>GPT-6.1 Sol xhigh</x:v>
+      </x:c>
+      <x:c r="B37" s="127" t="n">
+        <x:f>AVERAGE(C146,C156,C166)</x:f>
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C37" s="127" t="n">
+        <x:f>AVERAGE(D146,D156,D166)</x:f>
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="D37" s="127" t="n">
+        <x:f>AVERAGE(E146,E156,E166)</x:f>
+        <x:v>13.333333333333334</x:v>
+      </x:c>
+      <x:c r="E37" s="127" t="n">
+        <x:f>AVERAGE(F146,F156,F166)</x:f>
+        <x:v>28.666666666666668</x:v>
+      </x:c>
+      <x:c r="F37" s="127" t="n">
+        <x:f>AVERAGE(G146,G156,G166)</x:f>
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="G37" s="127" t="n">
         <x:f>SUM(B37:F37)</x:f>
-        <x:v>71.66666666666666</x:v>
-      </x:c>
-      <x:c r="H37" s="71" t="n">
-        <x:f>B11</x:f>
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="I37" s="71" t="n">
-        <x:f>D11</x:f>
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="J37" s="71" t="n">
-        <x:f>F11</x:f>
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="K37" s="71" t="n">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="H37" s="122" t="n">
+        <x:f>B7</x:f>
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="I37" s="122" t="n">
+        <x:f>D7</x:f>
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="J37" s="122" t="n">
+        <x:f>F7</x:f>
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="K37" s="122" t="n">
         <x:f>MAX(H37:J37)-MIN(H37:J37)</x:f>
-        <x:v>33</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="L37" s="2"/>
       <x:c r="M37" s="2"/>
       <x:c r="N37" s="2" t="str">
-        <x:v>DeepSeek V4.1 Flash max</x:v>
+        <x:v>GPT-5.6 Sol xhigh</x:v>
       </x:c>
       <x:c r="O37" s="2" t="n">
-        <x:f>LOG10('Task 2'!C9)</x:f>
-        <x:v>-0.366531544420413</x:v>
+        <x:f>LOG10('Task 2'!C2)</x:f>
+        <x:v>0.441380884916511</x:v>
       </x:c>
       <x:c r="P37" s="2" t="n">
-        <x:f>'Task 2'!D9</x:f>
-        <x:v>75</x:v>
+        <x:f>'Task 2'!D2</x:f>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="Q37" s="2"/>
       <x:c r="R37" s="2"/>
@@ -4867,60 +5466,60 @@
     </x:row>
     <x:row r="38" ht="21" customHeight="1">
       <x:c r="A38" s="2" t="str">
-        <x:v>DeepSeek V4.1 Flash max</x:v>
+        <x:v>GPT-6 Astra high</x:v>
       </x:c>
       <x:c r="B38" s="23" t="n">
-        <x:f>AVERAGE(C132,C140,C148)</x:f>
-        <x:v>12.333333333333334</x:v>
+        <x:f>AVERAGE(C139,C152,C162)</x:f>
+        <x:v>14.666666666666666</x:v>
       </x:c>
       <x:c r="C38" s="23" t="n">
-        <x:f>AVERAGE(D132,D140,D148)</x:f>
-        <x:v>22.666666666666668</x:v>
+        <x:f>AVERAGE(D139,D152,D162)</x:f>
+        <x:v>29.333333333333332</x:v>
       </x:c>
       <x:c r="D38" s="23" t="n">
-        <x:f>AVERAGE(E132,E140,E148)</x:f>
-        <x:v>8</x:v>
+        <x:f>AVERAGE(E139,E152,E162)</x:f>
+        <x:v>13.666666666666666</x:v>
       </x:c>
       <x:c r="E38" s="23" t="n">
-        <x:f>AVERAGE(F132,F140,F148)</x:f>
-        <x:v>11.666666666666666</x:v>
+        <x:f>AVERAGE(F139,F152,F162)</x:f>
+        <x:v>28.333333333333332</x:v>
       </x:c>
       <x:c r="F38" s="23" t="n">
-        <x:f>AVERAGE(G132,G140,G148)</x:f>
-        <x:v>4</x:v>
+        <x:f>AVERAGE(G139,G152,G162)</x:f>
+        <x:v>9.666666666666666</x:v>
       </x:c>
       <x:c r="G38" s="23" t="n">
         <x:f>SUM(B38:F38)</x:f>
-        <x:v>58.666666666666664</x:v>
+        <x:v>95.66666666666667</x:v>
       </x:c>
       <x:c r="H38" s="12" t="n">
-        <x:f>B12</x:f>
-        <x:v>47</x:v>
+        <x:f>B8</x:f>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="I38" s="12" t="n">
-        <x:f>D12</x:f>
-        <x:v>75</x:v>
+        <x:f>D8</x:f>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="J38" s="12" t="n">
-        <x:f>F12</x:f>
-        <x:v>54</x:v>
+        <x:f>F8</x:f>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="K38" s="12" t="n">
         <x:f>MAX(H38:J38)-MIN(H38:J38)</x:f>
-        <x:v>28</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="L38" s="2"/>
       <x:c r="M38" s="2"/>
       <x:c r="N38" s="2" t="str">
-        <x:v>Grok 4.7 high</x:v>
+        <x:v>GPT-6 Luna max</x:v>
       </x:c>
       <x:c r="O38" s="2" t="n">
-        <x:f>LOG10('Task 2'!C7)</x:f>
-        <x:v>0.630834517828051</x:v>
+        <x:f>LOG10('Task 2'!C3)</x:f>
+        <x:v>-0.844663962534938</x:v>
       </x:c>
       <x:c r="P38" s="2" t="n">
-        <x:f>'Task 2'!D7</x:f>
-        <x:v>69</x:v>
+        <x:f>'Task 2'!D3</x:f>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="Q38" s="2"/>
       <x:c r="R38" s="2"/>
@@ -4930,54 +5529,62 @@
       <x:c r="V38" s="2"/>
     </x:row>
     <x:row r="39" ht="21" customHeight="1">
-      <x:c r="A39" s="72" t="str">
-        <x:v>Grok 4.7 high</x:v>
-      </x:c>
-      <x:c r="B39" s="77" t="n">
-        <x:f>AVERAGE(C128,C138,C146)</x:f>
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C39" s="77" t="n">
-        <x:f>AVERAGE(D128,D138,D146)</x:f>
-        <x:v>19.666666666666668</x:v>
-      </x:c>
-      <x:c r="D39" s="77" t="n">
-        <x:f>AVERAGE(E128,E138,E146)</x:f>
-        <x:v>8.333333333333334</x:v>
-      </x:c>
-      <x:c r="E39" s="77" t="n">
-        <x:f>AVERAGE(F128,F138,F146)</x:f>
-        <x:v>10.666666666666666</x:v>
-      </x:c>
-      <x:c r="F39" s="77" t="n">
-        <x:f>AVERAGE(G128,G138,G146)</x:f>
-        <x:v>5.666666666666667</x:v>
-      </x:c>
-      <x:c r="G39" s="77" t="n">
+      <x:c r="A39" s="121" t="str">
+        <x:v>GPT-6 Sol max</x:v>
+      </x:c>
+      <x:c r="B39" s="127" t="n">
+        <x:f>AVERAGE(C143,C150,C160)</x:f>
+        <x:v>14.666666666666666</x:v>
+      </x:c>
+      <x:c r="C39" s="127" t="n">
+        <x:f>AVERAGE(D143,D150,D160)</x:f>
+        <x:v>29.333333333333332</x:v>
+      </x:c>
+      <x:c r="D39" s="127" t="n">
+        <x:f>AVERAGE(E143,E150,E160)</x:f>
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E39" s="127" t="n">
+        <x:f>AVERAGE(F143,F150,F160)</x:f>
+        <x:v>27.333333333333332</x:v>
+      </x:c>
+      <x:c r="F39" s="127" t="n">
+        <x:f>AVERAGE(G143,G150,G160)</x:f>
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="G39" s="127" t="n">
         <x:f>SUM(B39:F39)</x:f>
-        <x:v>56.33333333333333</x:v>
-      </x:c>
-      <x:c r="H39" s="73" t="n">
-        <x:f>B13</x:f>
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="I39" s="73" t="n">
-        <x:f>D13</x:f>
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="J39" s="73" t="n">
-        <x:f>F13</x:f>
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="K39" s="73" t="n">
+        <x:v>94.33333333333333</x:v>
+      </x:c>
+      <x:c r="H39" s="122" t="n">
+        <x:f>B9</x:f>
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="I39" s="122" t="n">
+        <x:f>D9</x:f>
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="J39" s="122" t="n">
+        <x:f>F9</x:f>
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="K39" s="122" t="n">
         <x:f>MAX(H39:J39)-MIN(H39:J39)</x:f>
-        <x:v>40</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="L39" s="2"/>
       <x:c r="M39" s="2"/>
-      <x:c r="N39" s="2"/>
-      <x:c r="O39" s="2"/>
-      <x:c r="P39" s="2"/>
+      <x:c r="N39" s="2" t="str">
+        <x:v>DeepSeek V4.1 Flash max</x:v>
+      </x:c>
+      <x:c r="O39" s="2" t="n">
+        <x:f>LOG10('Task 2'!C9)</x:f>
+        <x:v>-0.366531544420413</x:v>
+      </x:c>
+      <x:c r="P39" s="2" t="n">
+        <x:f>'Task 2'!D9</x:f>
+        <x:v>75</x:v>
+      </x:c>
       <x:c r="Q39" s="2"/>
       <x:c r="R39" s="2"/>
       <x:c r="S39" s="2"/>
@@ -4986,22 +5593,62 @@
       <x:c r="V39" s="2"/>
     </x:row>
     <x:row r="40" ht="21" customHeight="1">
-      <x:c r="A40" s="2"/>
-      <x:c r="B40" s="2"/>
-      <x:c r="C40" s="2"/>
-      <x:c r="D40" s="2"/>
-      <x:c r="E40" s="2"/>
-      <x:c r="F40" s="2"/>
-      <x:c r="G40" s="2"/>
-      <x:c r="H40" s="2"/>
-      <x:c r="I40" s="2"/>
-      <x:c r="J40" s="2"/>
-      <x:c r="K40" s="2"/>
+      <x:c r="A40" s="2" t="str">
+        <x:v>Opus 5.5 xhigh</x:v>
+      </x:c>
+      <x:c r="B40" s="23" t="n">
+        <x:f>AVERAGE(C142,C154,C164)</x:f>
+        <x:v>13.666666666666666</x:v>
+      </x:c>
+      <x:c r="C40" s="23" t="n">
+        <x:f>AVERAGE(D142,D154,D164)</x:f>
+        <x:v>28.333333333333332</x:v>
+      </x:c>
+      <x:c r="D40" s="23" t="n">
+        <x:f>AVERAGE(E142,E154,E164)</x:f>
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E40" s="23" t="n">
+        <x:f>AVERAGE(F142,F154,F164)</x:f>
+        <x:v>25.666666666666668</x:v>
+      </x:c>
+      <x:c r="F40" s="23" t="n">
+        <x:f>AVERAGE(G142,G154,G164)</x:f>
+        <x:v>6.333333333333333</x:v>
+      </x:c>
+      <x:c r="G40" s="23" t="n">
+        <x:f>SUM(B40:F40)</x:f>
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="H40" s="12" t="n">
+        <x:f>B10</x:f>
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="I40" s="12" t="n">
+        <x:f>D10</x:f>
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="J40" s="12" t="n">
+        <x:f>F10</x:f>
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="K40" s="12" t="n">
+        <x:f>MAX(H40:J40)-MIN(H40:J40)</x:f>
+        <x:v>12</x:v>
+      </x:c>
       <x:c r="L40" s="2"/>
       <x:c r="M40" s="2"/>
-      <x:c r="N40" s="2"/>
-      <x:c r="O40" s="2"/>
-      <x:c r="P40" s="2"/>
+      <x:c r="N40" s="2" t="str">
+        <x:v>Grok 4.7 high</x:v>
+      </x:c>
+      <x:c r="O40" s="2" t="n">
+        <x:f>LOG10('Task 2'!C7)</x:f>
+        <x:v>0.630834517828051</x:v>
+      </x:c>
+      <x:c r="P40" s="2" t="n">
+        <x:f>'Task 2'!D7</x:f>
+        <x:v>69</x:v>
+      </x:c>
       <x:c r="Q40" s="2"/>
       <x:c r="R40" s="2"/>
       <x:c r="S40" s="2"/>
@@ -5009,18 +5656,50 @@
       <x:c r="U40" s="2"/>
       <x:c r="V40" s="2"/>
     </x:row>
-    <x:row r="41" ht="17.25" customHeight="1">
-      <x:c r="A41" s="2"/>
-      <x:c r="B41" s="2"/>
-      <x:c r="C41" s="2"/>
-      <x:c r="D41" s="2"/>
-      <x:c r="E41" s="2"/>
-      <x:c r="F41" s="2"/>
-      <x:c r="G41" s="2"/>
-      <x:c r="H41" s="2"/>
-      <x:c r="I41" s="2"/>
-      <x:c r="J41" s="2"/>
-      <x:c r="K41" s="2"/>
+    <x:row r="41" ht="21" customHeight="1">
+      <x:c r="A41" s="121" t="str">
+        <x:v>GPT-6 Sol xhigh</x:v>
+      </x:c>
+      <x:c r="B41" s="127" t="n">
+        <x:f>AVERAGE(C140,C151,C161)</x:f>
+        <x:v>14.666666666666666</x:v>
+      </x:c>
+      <x:c r="C41" s="127" t="n">
+        <x:f>AVERAGE(D140,D151,D161)</x:f>
+        <x:v>26.333333333333332</x:v>
+      </x:c>
+      <x:c r="D41" s="127" t="n">
+        <x:f>AVERAGE(E140,E151,E161)</x:f>
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E41" s="127" t="n">
+        <x:f>AVERAGE(F140,F151,F161)</x:f>
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="F41" s="127" t="n">
+        <x:f>AVERAGE(G140,G151,G161)</x:f>
+        <x:v>8.666666666666666</x:v>
+      </x:c>
+      <x:c r="G41" s="127" t="n">
+        <x:f>SUM(B41:F41)</x:f>
+        <x:v>78.66666666666667</x:v>
+      </x:c>
+      <x:c r="H41" s="122" t="n">
+        <x:f>B11</x:f>
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="I41" s="122" t="n">
+        <x:f>D11</x:f>
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="J41" s="122" t="n">
+        <x:f>F11</x:f>
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="K41" s="122" t="n">
+        <x:f>MAX(H41:J41)-MIN(H41:J41)</x:f>
+        <x:v>38</x:v>
+      </x:c>
       <x:c r="L41" s="2"/>
       <x:c r="M41" s="2"/>
       <x:c r="N41" s="2"/>
@@ -5033,18 +5712,50 @@
       <x:c r="U41" s="2"/>
       <x:c r="V41" s="2"/>
     </x:row>
-    <x:row r="42" ht="17.25" customHeight="1">
-      <x:c r="A42" s="2"/>
-      <x:c r="B42" s="2"/>
-      <x:c r="C42" s="2"/>
-      <x:c r="D42" s="2"/>
-      <x:c r="E42" s="2"/>
-      <x:c r="F42" s="2"/>
-      <x:c r="G42" s="2"/>
-      <x:c r="H42" s="2"/>
-      <x:c r="I42" s="2"/>
-      <x:c r="J42" s="2"/>
-      <x:c r="K42" s="2"/>
+    <x:row r="42" ht="21" customHeight="1">
+      <x:c r="A42" s="2" t="str">
+        <x:v>GPT-5.6 Sol xhigh</x:v>
+      </x:c>
+      <x:c r="B42" s="23" t="n">
+        <x:f>AVERAGE(C138,C148,C158)</x:f>
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C42" s="23" t="n">
+        <x:f>AVERAGE(D138,D148,D158)</x:f>
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="D42" s="23" t="n">
+        <x:f>AVERAGE(E138,E148,E158)</x:f>
+        <x:v>10.333333333333334</x:v>
+      </x:c>
+      <x:c r="E42" s="23" t="n">
+        <x:f>AVERAGE(F138,F148,F158)</x:f>
+        <x:v>18.333333333333332</x:v>
+      </x:c>
+      <x:c r="F42" s="23" t="n">
+        <x:f>AVERAGE(G138,G148,G158)</x:f>
+        <x:v>7.666666666666667</x:v>
+      </x:c>
+      <x:c r="G42" s="23" t="n">
+        <x:f>SUM(B42:F42)</x:f>
+        <x:v>75.33333333333334</x:v>
+      </x:c>
+      <x:c r="H42" s="12" t="n">
+        <x:f>B12</x:f>
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="I42" s="12" t="n">
+        <x:f>D12</x:f>
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="J42" s="12" t="n">
+        <x:f>F12</x:f>
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="K42" s="12" t="n">
+        <x:f>MAX(H42:J42)-MIN(H42:J42)</x:f>
+        <x:v>30</x:v>
+      </x:c>
       <x:c r="L42" s="2"/>
       <x:c r="M42" s="2"/>
       <x:c r="N42" s="2" t="str">
@@ -5063,30 +5774,62 @@
       <x:c r="U42" s="2"/>
       <x:c r="V42" s="2"/>
     </x:row>
-    <x:row r="43" ht="17.25" customHeight="1">
-      <x:c r="A43" s="2"/>
-      <x:c r="B43" s="2"/>
-      <x:c r="C43" s="2"/>
-      <x:c r="D43" s="2"/>
-      <x:c r="E43" s="2"/>
-      <x:c r="F43" s="2"/>
-      <x:c r="G43" s="2"/>
-      <x:c r="H43" s="2"/>
-      <x:c r="I43" s="2"/>
-      <x:c r="J43" s="2"/>
-      <x:c r="K43" s="2"/>
+    <x:row r="43" ht="21" customHeight="1">
+      <x:c r="A43" s="121" t="str">
+        <x:v>GPT-6 Luna max</x:v>
+      </x:c>
+      <x:c r="B43" s="127" t="n">
+        <x:f>AVERAGE(C144,C149,C159)</x:f>
+        <x:v>14.666666666666666</x:v>
+      </x:c>
+      <x:c r="C43" s="127" t="n">
+        <x:f>AVERAGE(D144,D149,D159)</x:f>
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="D43" s="127" t="n">
+        <x:f>AVERAGE(E144,E149,E159)</x:f>
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="E43" s="127" t="n">
+        <x:f>AVERAGE(F144,F149,F159)</x:f>
+        <x:v>14.666666666666666</x:v>
+      </x:c>
+      <x:c r="F43" s="127" t="n">
+        <x:f>AVERAGE(G144,G149,G159)</x:f>
+        <x:v>8.333333333333334</x:v>
+      </x:c>
+      <x:c r="G43" s="127" t="n">
+        <x:f>SUM(B43:F43)</x:f>
+        <x:v>71.66666666666666</x:v>
+      </x:c>
+      <x:c r="H43" s="122" t="n">
+        <x:f>B13</x:f>
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="I43" s="122" t="n">
+        <x:f>D13</x:f>
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="J43" s="122" t="n">
+        <x:f>F13</x:f>
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="K43" s="122" t="n">
+        <x:f>MAX(H43:J43)-MIN(H43:J43)</x:f>
+        <x:v>33</x:v>
+      </x:c>
       <x:c r="L43" s="2"/>
       <x:c r="M43" s="2"/>
       <x:c r="N43" s="2" t="str">
-        <x:v>GPT-6 Astra high</x:v>
+        <x:v>GPT-6.1 Sol max</x:v>
       </x:c>
       <x:c r="O43" s="2" t="n">
-        <x:f>LOG10('Task 3'!C6)</x:f>
-        <x:v>0.623869268350302</x:v>
+        <x:f>LOG10('Task 3'!C11)</x:f>
+        <x:v>0.215108581053093</x:v>
       </x:c>
       <x:c r="P43" s="2" t="n">
-        <x:f>'Task 3'!D6</x:f>
-        <x:v>98</x:v>
+        <x:f>'Task 3'!D11</x:f>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="Q43" s="2"/>
       <x:c r="R43" s="2"/>
@@ -5095,30 +5838,62 @@
       <x:c r="U43" s="2"/>
       <x:c r="V43" s="2"/>
     </x:row>
-    <x:row r="44" ht="17.25" customHeight="1">
-      <x:c r="A44" s="2"/>
-      <x:c r="B44" s="2"/>
-      <x:c r="C44" s="2"/>
-      <x:c r="D44" s="2"/>
-      <x:c r="E44" s="2"/>
-      <x:c r="F44" s="2"/>
-      <x:c r="G44" s="2"/>
-      <x:c r="H44" s="2"/>
-      <x:c r="I44" s="2"/>
-      <x:c r="J44" s="2"/>
-      <x:c r="K44" s="2"/>
+    <x:row r="44" ht="21" customHeight="1">
+      <x:c r="A44" s="2" t="str">
+        <x:v>DeepSeek V4.1 Flash max</x:v>
+      </x:c>
+      <x:c r="B44" s="23" t="n">
+        <x:f>AVERAGE(C145,C155,C165)</x:f>
+        <x:v>12.333333333333334</x:v>
+      </x:c>
+      <x:c r="C44" s="23" t="n">
+        <x:f>AVERAGE(D145,D155,D165)</x:f>
+        <x:v>22.666666666666668</x:v>
+      </x:c>
+      <x:c r="D44" s="23" t="n">
+        <x:f>AVERAGE(E145,E155,E165)</x:f>
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="E44" s="23" t="n">
+        <x:f>AVERAGE(F145,F155,F165)</x:f>
+        <x:v>11.666666666666666</x:v>
+      </x:c>
+      <x:c r="F44" s="23" t="n">
+        <x:f>AVERAGE(G145,G155,G165)</x:f>
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="G44" s="23" t="n">
+        <x:f>SUM(B44:F44)</x:f>
+        <x:v>58.666666666666664</x:v>
+      </x:c>
+      <x:c r="H44" s="12" t="n">
+        <x:f>B14</x:f>
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="I44" s="12" t="n">
+        <x:f>D14</x:f>
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="J44" s="12" t="n">
+        <x:f>F14</x:f>
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="K44" s="12" t="n">
+        <x:f>MAX(H44:J44)-MIN(H44:J44)</x:f>
+        <x:v>28</x:v>
+      </x:c>
       <x:c r="L44" s="2"/>
       <x:c r="M44" s="2"/>
       <x:c r="N44" s="2" t="str">
-        <x:v>GPT-6 Sol max</x:v>
+        <x:v>GPT-6 Astra high</x:v>
       </x:c>
       <x:c r="O44" s="2" t="n">
-        <x:f>LOG10('Task 3'!C4)</x:f>
-        <x:v>0.3654879848909</x:v>
+        <x:f>LOG10('Task 3'!C6)</x:f>
+        <x:v>0.623869268350302</x:v>
       </x:c>
       <x:c r="P44" s="2" t="n">
-        <x:f>'Task 3'!D4</x:f>
-        <x:v>95</x:v>
+        <x:f>'Task 3'!D6</x:f>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="Q44" s="2"/>
       <x:c r="R44" s="2"/>
@@ -5127,30 +5902,62 @@
       <x:c r="U44" s="2"/>
       <x:c r="V44" s="2"/>
     </x:row>
-    <x:row r="45" ht="17.25" customHeight="1">
-      <x:c r="A45" s="2"/>
-      <x:c r="B45" s="2"/>
-      <x:c r="C45" s="2"/>
-      <x:c r="D45" s="2"/>
-      <x:c r="E45" s="2"/>
-      <x:c r="F45" s="2"/>
-      <x:c r="G45" s="2"/>
-      <x:c r="H45" s="2"/>
-      <x:c r="I45" s="2"/>
-      <x:c r="J45" s="2"/>
-      <x:c r="K45" s="2"/>
+    <x:row r="45" ht="21" customHeight="1">
+      <x:c r="A45" s="123" t="str">
+        <x:v>Grok 4.7 high</x:v>
+      </x:c>
+      <x:c r="B45" s="128" t="n">
+        <x:f>AVERAGE(C141,C153,C163)</x:f>
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="C45" s="128" t="n">
+        <x:f>AVERAGE(D141,D153,D163)</x:f>
+        <x:v>19.666666666666668</x:v>
+      </x:c>
+      <x:c r="D45" s="128" t="n">
+        <x:f>AVERAGE(E141,E153,E163)</x:f>
+        <x:v>8.333333333333334</x:v>
+      </x:c>
+      <x:c r="E45" s="128" t="n">
+        <x:f>AVERAGE(F141,F153,F163)</x:f>
+        <x:v>10.666666666666666</x:v>
+      </x:c>
+      <x:c r="F45" s="128" t="n">
+        <x:f>AVERAGE(G141,G153,G163)</x:f>
+        <x:v>5.666666666666667</x:v>
+      </x:c>
+      <x:c r="G45" s="128" t="n">
+        <x:f>SUM(B45:F45)</x:f>
+        <x:v>56.33333333333333</x:v>
+      </x:c>
+      <x:c r="H45" s="124" t="n">
+        <x:f>B15</x:f>
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="I45" s="124" t="n">
+        <x:f>D15</x:f>
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="J45" s="124" t="n">
+        <x:f>F15</x:f>
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="K45" s="124" t="n">
+        <x:f>MAX(H45:J45)-MIN(H45:J45)</x:f>
+        <x:v>40</x:v>
+      </x:c>
       <x:c r="L45" s="2"/>
       <x:c r="M45" s="2"/>
       <x:c r="N45" s="2" t="str">
-        <x:v>GPT-6 Sol xhigh</x:v>
+        <x:v>GPT-6.1 Sol xhigh</x:v>
       </x:c>
       <x:c r="O45" s="2" t="n">
-        <x:f>LOG10('Task 3'!C5)</x:f>
-        <x:v>0.215637563435062</x:v>
+        <x:f>LOG10('Task 3'!C10)</x:f>
+        <x:v>0.137037454789513</x:v>
       </x:c>
       <x:c r="P45" s="2" t="n">
-        <x:f>'Task 3'!D5</x:f>
-        <x:v>90</x:v>
+        <x:f>'Task 3'!D10</x:f>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="Q45" s="2"/>
       <x:c r="R45" s="2"/>
@@ -5159,7 +5966,7 @@
       <x:c r="U45" s="2"/>
       <x:c r="V45" s="2"/>
     </x:row>
-    <x:row r="46" ht="17.25" customHeight="1">
+    <x:row r="46" ht="21" customHeight="1">
       <x:c r="A46" s="2"/>
       <x:c r="B46" s="2"/>
       <x:c r="C46" s="2"/>
@@ -5174,15 +5981,15 @@
       <x:c r="L46" s="2"/>
       <x:c r="M46" s="2"/>
       <x:c r="N46" s="2" t="str">
-        <x:v>GPT-5.6 Sol xhigh</x:v>
+        <x:v>GPT-6 Sol max</x:v>
       </x:c>
       <x:c r="O46" s="2" t="n">
-        <x:f>LOG10('Task 3'!C2)</x:f>
-        <x:v>1.14488541828714</x:v>
+        <x:f>LOG10('Task 3'!C4)</x:f>
+        <x:v>0.3654879848909</x:v>
       </x:c>
       <x:c r="P46" s="2" t="n">
-        <x:f>'Task 3'!D2</x:f>
-        <x:v>82</x:v>
+        <x:f>'Task 3'!D4</x:f>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="Q46" s="2"/>
       <x:c r="R46" s="2"/>
@@ -5206,15 +6013,15 @@
       <x:c r="L47" s="2"/>
       <x:c r="M47" s="2"/>
       <x:c r="N47" s="2" t="str">
-        <x:v>Opus 5.5 xhigh</x:v>
+        <x:v>GPT-6 Sol xhigh</x:v>
       </x:c>
       <x:c r="O47" s="2" t="n">
-        <x:f>LOG10('Task 3'!C8)</x:f>
-        <x:v>1.15787967438915</x:v>
+        <x:f>LOG10('Task 3'!C5)</x:f>
+        <x:v>0.215637563435062</x:v>
       </x:c>
       <x:c r="P47" s="2" t="n">
-        <x:f>'Task 3'!D8</x:f>
-        <x:v>81</x:v>
+        <x:f>'Task 3'!D5</x:f>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="Q47" s="2"/>
       <x:c r="R47" s="2"/>
@@ -5238,15 +6045,15 @@
       <x:c r="L48" s="2"/>
       <x:c r="M48" s="2"/>
       <x:c r="N48" s="2" t="str">
-        <x:v>GPT-6 Luna max</x:v>
+        <x:v>GPT-5.6 Sol xhigh</x:v>
       </x:c>
       <x:c r="O48" s="2" t="n">
-        <x:f>LOG10('Task 3'!C3)</x:f>
-        <x:v>-0.844663962534938</x:v>
+        <x:f>LOG10('Task 3'!C2)</x:f>
+        <x:v>1.14488541828714</x:v>
       </x:c>
       <x:c r="P48" s="2" t="n">
-        <x:f>'Task 3'!D3</x:f>
-        <x:v>76</x:v>
+        <x:f>'Task 3'!D2</x:f>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="Q48" s="2"/>
       <x:c r="R48" s="2"/>
@@ -5270,15 +6077,15 @@
       <x:c r="L49" s="2"/>
       <x:c r="M49" s="2"/>
       <x:c r="N49" s="2" t="str">
-        <x:v>Grok 4.7 high</x:v>
+        <x:v>Opus 5.5 xhigh</x:v>
       </x:c>
       <x:c r="O49" s="2" t="n">
-        <x:f>LOG10('Task 3'!C7)</x:f>
-        <x:v>0.769967801329442</x:v>
+        <x:f>LOG10('Task 3'!C8)</x:f>
+        <x:v>1.15787967438915</x:v>
       </x:c>
       <x:c r="P49" s="2" t="n">
-        <x:f>'Task 3'!D7</x:f>
-        <x:v>70</x:v>
+        <x:f>'Task 3'!D8</x:f>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="Q49" s="2"/>
       <x:c r="R49" s="2"/>
@@ -5302,15 +6109,15 @@
       <x:c r="L50" s="2"/>
       <x:c r="M50" s="2"/>
       <x:c r="N50" s="2" t="str">
-        <x:v>DeepSeek V4.1 Flash max</x:v>
+        <x:v>GPT-6 Luna max</x:v>
       </x:c>
       <x:c r="O50" s="2" t="n">
-        <x:f>LOG10('Task 3'!C9)</x:f>
-        <x:v>-0.321481620959886</x:v>
+        <x:f>LOG10('Task 3'!C3)</x:f>
+        <x:v>-0.844663962534938</x:v>
       </x:c>
       <x:c r="P50" s="2" t="n">
-        <x:f>'Task 3'!D9</x:f>
-        <x:v>54</x:v>
+        <x:f>'Task 3'!D3</x:f>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="Q50" s="2"/>
       <x:c r="R50" s="2"/>
@@ -5333,9 +6140,17 @@
       <x:c r="K51" s="2"/>
       <x:c r="L51" s="2"/>
       <x:c r="M51" s="2"/>
-      <x:c r="N51" s="2"/>
-      <x:c r="O51" s="2"/>
-      <x:c r="P51" s="2"/>
+      <x:c r="N51" s="2" t="str">
+        <x:v>Grok 4.7 high</x:v>
+      </x:c>
+      <x:c r="O51" s="2" t="n">
+        <x:f>LOG10('Task 3'!C7)</x:f>
+        <x:v>0.769967801329442</x:v>
+      </x:c>
+      <x:c r="P51" s="2" t="n">
+        <x:f>'Task 3'!D7</x:f>
+        <x:v>70</x:v>
+      </x:c>
       <x:c r="Q51" s="2"/>
       <x:c r="R51" s="2"/>
       <x:c r="S51" s="2"/>
@@ -5357,9 +6172,17 @@
       <x:c r="K52" s="2"/>
       <x:c r="L52" s="2"/>
       <x:c r="M52" s="2"/>
-      <x:c r="N52" s="2"/>
-      <x:c r="O52" s="2"/>
-      <x:c r="P52" s="2"/>
+      <x:c r="N52" s="2" t="str">
+        <x:v>DeepSeek V4.1 Flash max</x:v>
+      </x:c>
+      <x:c r="O52" s="2" t="n">
+        <x:f>LOG10('Task 3'!C9)</x:f>
+        <x:v>-0.321481620959886</x:v>
+      </x:c>
+      <x:c r="P52" s="2" t="n">
+        <x:f>'Task 3'!D9</x:f>
+        <x:v>54</x:v>
+      </x:c>
       <x:c r="Q52" s="2"/>
       <x:c r="R52" s="2"/>
       <x:c r="S52" s="2"/>
@@ -6207,20 +7030,18 @@
       <x:c r="U87" s="2"/>
       <x:c r="V87" s="2"/>
     </x:row>
-    <x:row r="88" ht="24" customHeight="1">
-      <x:c r="A88" s="27" t="str">
-        <x:v>事后按题选型：512 种组合中的代表方案</x:v>
-      </x:c>
-      <x:c r="B88" s="27"/>
-      <x:c r="C88" s="27"/>
-      <x:c r="D88" s="27"/>
-      <x:c r="E88" s="27"/>
-      <x:c r="F88" s="27"/>
-      <x:c r="G88" s="27"/>
-      <x:c r="H88" s="27"/>
-      <x:c r="I88" s="27"/>
-      <x:c r="J88" s="27"/>
-      <x:c r="K88" s="27"/>
+    <x:row r="88" ht="17.25" customHeight="1">
+      <x:c r="A88" s="2"/>
+      <x:c r="B88" s="2"/>
+      <x:c r="C88" s="2"/>
+      <x:c r="D88" s="2"/>
+      <x:c r="E88" s="2"/>
+      <x:c r="F88" s="2"/>
+      <x:c r="G88" s="2"/>
+      <x:c r="H88" s="2"/>
+      <x:c r="I88" s="2"/>
+      <x:c r="J88" s="2"/>
+      <x:c r="K88" s="2"/>
       <x:c r="L88" s="2"/>
       <x:c r="M88" s="2"/>
       <x:c r="N88" s="2"/>
@@ -6233,7 +7054,7 @@
       <x:c r="U88" s="2"/>
       <x:c r="V88" s="2"/>
     </x:row>
-    <x:row r="89" ht="21" customHeight="1">
+    <x:row r="89" ht="17.25" customHeight="1">
       <x:c r="A89" s="2"/>
       <x:c r="B89" s="2"/>
       <x:c r="C89" s="2"/>
@@ -6257,40 +7078,18 @@
       <x:c r="U89" s="2"/>
       <x:c r="V89" s="2"/>
     </x:row>
-    <x:row r="90" ht="35" customHeight="1">
-      <x:c r="A90" s="69" t="str">
-        <x:v>选择方案</x:v>
-      </x:c>
-      <x:c r="B90" s="69" t="str">
-        <x:v>总分 /300</x:v>
-      </x:c>
-      <x:c r="C90" s="69" t="str">
-        <x:v>均分 /100</x:v>
-      </x:c>
-      <x:c r="D90" s="69" t="str">
-        <x:v>总成本 USD</x:v>
-      </x:c>
-      <x:c r="E90" s="69" t="str">
-        <x:v>题 1 分</x:v>
-      </x:c>
-      <x:c r="F90" s="69" t="str">
-        <x:v>题 2 分</x:v>
-      </x:c>
-      <x:c r="G90" s="69" t="str">
-        <x:v>题 3 分</x:v>
-      </x:c>
-      <x:c r="H90" s="69" t="str">
-        <x:v>题 1 USD</x:v>
-      </x:c>
-      <x:c r="I90" s="69" t="str">
-        <x:v>题 2 USD</x:v>
-      </x:c>
-      <x:c r="J90" s="69" t="str">
-        <x:v>题 3 USD</x:v>
-      </x:c>
-      <x:c r="K90" s="69" t="str">
-        <x:v>回答编号</x:v>
-      </x:c>
+    <x:row r="90" ht="17.25" customHeight="1">
+      <x:c r="A90" s="2"/>
+      <x:c r="B90" s="2"/>
+      <x:c r="C90" s="2"/>
+      <x:c r="D90" s="2"/>
+      <x:c r="E90" s="2"/>
+      <x:c r="F90" s="2"/>
+      <x:c r="G90" s="2"/>
+      <x:c r="H90" s="2"/>
+      <x:c r="I90" s="2"/>
+      <x:c r="J90" s="2"/>
+      <x:c r="K90" s="2"/>
       <x:c r="L90" s="2"/>
       <x:c r="M90" s="2"/>
       <x:c r="N90" s="2"/>
@@ -6303,49 +7102,18 @@
       <x:c r="U90" s="2"/>
       <x:c r="V90" s="2"/>
     </x:row>
-    <x:row r="91" ht="31.5" customHeight="1">
-      <x:c r="A91" s="31" t="str">
-        <x:v>三题均用 Luna max</x:v>
-      </x:c>
-      <x:c r="B91" s="12" t="n">
-        <x:f>SUM(E91:G91)</x:f>
-        <x:v>215</x:v>
-      </x:c>
-      <x:c r="C91" s="23" t="n">
-        <x:f>B91/3</x:f>
-        <x:v>71.66666666666667</x:v>
-      </x:c>
-      <x:c r="D91" s="20" t="n">
-        <x:f>SUM(H91:J91)</x:f>
-        <x:v>0.46399999999999997</x:v>
-      </x:c>
-      <x:c r="E91" s="12" t="n">
-        <x:f>'Task 1'!D8</x:f>
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="F91" s="12" t="n">
-        <x:f>'Task 2'!D3</x:f>
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="G91" s="12" t="n">
-        <x:f>'Task 3'!D3</x:f>
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="H91" s="20" t="n">
-        <x:f>'Task 1'!C8</x:f>
-        <x:v>0.178</x:v>
-      </x:c>
-      <x:c r="I91" s="20" t="n">
-        <x:f>'Task 2'!C3</x:f>
-        <x:v>0.143</x:v>
-      </x:c>
-      <x:c r="J91" s="20" t="n">
-        <x:f>'Task 3'!C3</x:f>
-        <x:v>0.143</x:v>
-      </x:c>
-      <x:c r="K91" s="61" t="str">
-        <x:v>s_1c / 2b / 3b</x:v>
-      </x:c>
+    <x:row r="91" ht="17.25" customHeight="1">
+      <x:c r="A91" s="2"/>
+      <x:c r="B91" s="2"/>
+      <x:c r="C91" s="2"/>
+      <x:c r="D91" s="2"/>
+      <x:c r="E91" s="2"/>
+      <x:c r="F91" s="2"/>
+      <x:c r="G91" s="2"/>
+      <x:c r="H91" s="2"/>
+      <x:c r="I91" s="2"/>
+      <x:c r="J91" s="2"/>
+      <x:c r="K91" s="2"/>
       <x:c r="L91" s="2"/>
       <x:c r="M91" s="2"/>
       <x:c r="N91" s="2"/>
@@ -6358,49 +7126,18 @@
       <x:c r="U91" s="2"/>
       <x:c r="V91" s="2"/>
     </x:row>
-    <x:row r="92" ht="31.5" customHeight="1">
-      <x:c r="A92" s="78" t="str">
-        <x:v>每题至少 75 分：最低成本</x:v>
-      </x:c>
-      <x:c r="B92" s="71" t="n">
-        <x:f>SUM(E92:G92)</x:f>
-        <x:v>256</x:v>
-      </x:c>
-      <x:c r="C92" s="76" t="n">
-        <x:f>B92/3</x:f>
-        <x:v>85.33333333333333</x:v>
-      </x:c>
-      <x:c r="D92" s="74" t="n">
-        <x:f>SUM(H92:J92)</x:f>
-        <x:v>4.404</x:v>
-      </x:c>
-      <x:c r="E92" s="71" t="n">
-        <x:f>'Task 1'!D7</x:f>
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="F92" s="71" t="n">
-        <x:f>'Task 2'!D3</x:f>
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="G92" s="71" t="n">
-        <x:f>'Task 3'!D3</x:f>
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="H92" s="74" t="n">
-        <x:f>'Task 1'!C7</x:f>
-        <x:v>4.118</x:v>
-      </x:c>
-      <x:c r="I92" s="74" t="n">
-        <x:f>'Task 2'!C3</x:f>
-        <x:v>0.143</x:v>
-      </x:c>
-      <x:c r="J92" s="74" t="n">
-        <x:f>'Task 3'!C3</x:f>
-        <x:v>0.143</x:v>
-      </x:c>
-      <x:c r="K92" s="80" t="str">
-        <x:v>s_1b / 2b / 3b</x:v>
-      </x:c>
+    <x:row r="92" ht="17.25" customHeight="1">
+      <x:c r="A92" s="2"/>
+      <x:c r="B92" s="2"/>
+      <x:c r="C92" s="2"/>
+      <x:c r="D92" s="2"/>
+      <x:c r="E92" s="2"/>
+      <x:c r="F92" s="2"/>
+      <x:c r="G92" s="2"/>
+      <x:c r="H92" s="2"/>
+      <x:c r="I92" s="2"/>
+      <x:c r="J92" s="2"/>
+      <x:c r="K92" s="2"/>
       <x:c r="L92" s="2"/>
       <x:c r="M92" s="2"/>
       <x:c r="N92" s="2"/>
@@ -6413,49 +7150,18 @@
       <x:c r="U92" s="2"/>
       <x:c r="V92" s="2"/>
     </x:row>
-    <x:row r="93" ht="31.5" customHeight="1">
-      <x:c r="A93" s="31" t="str">
-        <x:v>每题至少 80 分：最低成本</x:v>
-      </x:c>
-      <x:c r="B93" s="12" t="n">
-        <x:f>SUM(E93:G93)</x:f>
-        <x:v>270</x:v>
-      </x:c>
-      <x:c r="C93" s="23" t="n">
-        <x:f>B93/3</x:f>
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="D93" s="20" t="n">
-        <x:f>SUM(H93:J93)</x:f>
-        <x:v>5.904</x:v>
-      </x:c>
-      <x:c r="E93" s="12" t="n">
-        <x:f>'Task 1'!D7</x:f>
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="F93" s="12" t="n">
-        <x:f>'Task 2'!D3</x:f>
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="G93" s="12" t="n">
-        <x:f>'Task 3'!D5</x:f>
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="H93" s="20" t="n">
-        <x:f>'Task 1'!C7</x:f>
-        <x:v>4.118</x:v>
-      </x:c>
-      <x:c r="I93" s="20" t="n">
-        <x:f>'Task 2'!C3</x:f>
-        <x:v>0.143</x:v>
-      </x:c>
-      <x:c r="J93" s="20" t="n">
-        <x:f>'Task 3'!C5</x:f>
-        <x:v>1.643</x:v>
-      </x:c>
-      <x:c r="K93" s="61" t="str">
-        <x:v>s_1b / 2b / 3d</x:v>
-      </x:c>
+    <x:row r="93" ht="21" customHeight="1">
+      <x:c r="A93" s="2"/>
+      <x:c r="B93" s="2"/>
+      <x:c r="C93" s="2"/>
+      <x:c r="D93" s="2"/>
+      <x:c r="E93" s="2"/>
+      <x:c r="F93" s="2"/>
+      <x:c r="G93" s="2"/>
+      <x:c r="H93" s="2"/>
+      <x:c r="I93" s="2"/>
+      <x:c r="J93" s="2"/>
+      <x:c r="K93" s="2"/>
       <x:c r="L93" s="2"/>
       <x:c r="M93" s="2"/>
       <x:c r="N93" s="2"/>
@@ -6468,49 +7174,20 @@
       <x:c r="U93" s="2"/>
       <x:c r="V93" s="2"/>
     </x:row>
-    <x:row r="94" ht="31.5" customHeight="1">
-      <x:c r="A94" s="78" t="str">
-        <x:v>每题至少 90 分：最低成本</x:v>
-      </x:c>
-      <x:c r="B94" s="71" t="n">
-        <x:f>SUM(E94:G94)</x:f>
-        <x:v>278</x:v>
-      </x:c>
-      <x:c r="C94" s="76" t="n">
-        <x:f>B94/3</x:f>
-        <x:v>92.66666666666667</x:v>
-      </x:c>
-      <x:c r="D94" s="74" t="n">
-        <x:f>SUM(H94:J94)</x:f>
-        <x:v>7.575</x:v>
-      </x:c>
-      <x:c r="E94" s="71" t="n">
-        <x:f>'Task 1'!D7</x:f>
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="F94" s="71" t="n">
-        <x:f>'Task 2'!D4</x:f>
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="G94" s="71" t="n">
-        <x:f>'Task 3'!D5</x:f>
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="H94" s="74" t="n">
-        <x:f>'Task 1'!C7</x:f>
-        <x:v>4.118</x:v>
-      </x:c>
-      <x:c r="I94" s="74" t="n">
-        <x:f>'Task 2'!C4</x:f>
-        <x:v>1.814</x:v>
-      </x:c>
-      <x:c r="J94" s="74" t="n">
-        <x:f>'Task 3'!C5</x:f>
-        <x:v>1.643</x:v>
-      </x:c>
-      <x:c r="K94" s="80" t="str">
-        <x:v>s_1b / 2c / 3d</x:v>
-      </x:c>
+    <x:row r="94" ht="24" customHeight="1">
+      <x:c r="A94" s="27" t="str">
+        <x:v>事后按题选型：1000 种组合中的代表方案</x:v>
+      </x:c>
+      <x:c r="B94" s="27"/>
+      <x:c r="C94" s="27"/>
+      <x:c r="D94" s="27"/>
+      <x:c r="E94" s="27"/>
+      <x:c r="F94" s="27"/>
+      <x:c r="G94" s="27"/>
+      <x:c r="H94" s="27"/>
+      <x:c r="I94" s="27"/>
+      <x:c r="J94" s="27"/>
+      <x:c r="K94" s="27"/>
       <x:c r="L94" s="2"/>
       <x:c r="M94" s="2"/>
       <x:c r="N94" s="2"/>
@@ -6523,49 +7200,18 @@
       <x:c r="U94" s="2"/>
       <x:c r="V94" s="2"/>
     </x:row>
-    <x:row r="95" ht="31.5" customHeight="1">
-      <x:c r="A95" s="31" t="str">
-        <x:v>三题均用 Sol max</x:v>
-      </x:c>
-      <x:c r="B95" s="12" t="n">
-        <x:f>SUM(E95:G95)</x:f>
-        <x:v>283</x:v>
-      </x:c>
-      <x:c r="C95" s="23" t="n">
-        <x:f>B95/3</x:f>
-        <x:v>94.33333333333333</x:v>
-      </x:c>
-      <x:c r="D95" s="20" t="n">
-        <x:f>SUM(H95:J95)</x:f>
-        <x:v>8.252</x:v>
-      </x:c>
-      <x:c r="E95" s="12" t="n">
-        <x:f>'Task 1'!D7</x:f>
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="F95" s="12" t="n">
-        <x:f>'Task 2'!D4</x:f>
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="G95" s="12" t="n">
-        <x:f>'Task 3'!D4</x:f>
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="H95" s="20" t="n">
-        <x:f>'Task 1'!C7</x:f>
-        <x:v>4.118</x:v>
-      </x:c>
-      <x:c r="I95" s="20" t="n">
-        <x:f>'Task 2'!C4</x:f>
-        <x:v>1.814</x:v>
-      </x:c>
-      <x:c r="J95" s="20" t="n">
-        <x:f>'Task 3'!C4</x:f>
-        <x:v>2.32</x:v>
-      </x:c>
-      <x:c r="K95" s="61" t="str">
-        <x:v>s_1b / 2c / 3c</x:v>
-      </x:c>
+    <x:row r="95" ht="21" customHeight="1">
+      <x:c r="A95" s="2"/>
+      <x:c r="B95" s="2"/>
+      <x:c r="C95" s="2"/>
+      <x:c r="D95" s="2"/>
+      <x:c r="E95" s="2"/>
+      <x:c r="F95" s="2"/>
+      <x:c r="G95" s="2"/>
+      <x:c r="H95" s="2"/>
+      <x:c r="I95" s="2"/>
+      <x:c r="J95" s="2"/>
+      <x:c r="K95" s="2"/>
       <x:c r="L95" s="2"/>
       <x:c r="M95" s="2"/>
       <x:c r="N95" s="2"/>
@@ -6578,48 +7224,39 @@
       <x:c r="U95" s="2"/>
       <x:c r="V95" s="2"/>
     </x:row>
-    <x:row r="96" ht="31.5" customHeight="1">
-      <x:c r="A96" s="79" t="str">
-        <x:v>逐题最高分组合</x:v>
-      </x:c>
-      <x:c r="B96" s="73" t="n">
-        <x:f>SUM(E96:G96)</x:f>
-        <x:v>289</x:v>
-      </x:c>
-      <x:c r="C96" s="77" t="n">
-        <x:f>B96/3</x:f>
-        <x:v>96.33333333333333</x:v>
-      </x:c>
-      <x:c r="D96" s="75" t="n">
-        <x:f>SUM(H96:J96)</x:f>
-        <x:v>12.873999999999999</x:v>
-      </x:c>
-      <x:c r="E96" s="73" t="n">
-        <x:f>'Task 1'!D7</x:f>
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="F96" s="73" t="n">
-        <x:f>'Task 2'!D6</x:f>
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="G96" s="73" t="n">
-        <x:f>'Task 3'!D6</x:f>
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="H96" s="75" t="n">
-        <x:f>'Task 1'!C7</x:f>
-        <x:v>4.118</x:v>
-      </x:c>
-      <x:c r="I96" s="75" t="n">
-        <x:f>'Task 2'!C6</x:f>
-        <x:v>4.55</x:v>
-      </x:c>
-      <x:c r="J96" s="75" t="n">
-        <x:f>'Task 3'!C6</x:f>
-        <x:v>4.206</x:v>
-      </x:c>
-      <x:c r="K96" s="81" t="str">
-        <x:v>s_1b / 2e / 3e</x:v>
+    <x:row r="96" ht="35" customHeight="1">
+      <x:c r="A96" s="120" t="str">
+        <x:v>选择方案</x:v>
+      </x:c>
+      <x:c r="B96" s="120" t="str">
+        <x:v>总分 /300</x:v>
+      </x:c>
+      <x:c r="C96" s="120" t="str">
+        <x:v>均分 /100</x:v>
+      </x:c>
+      <x:c r="D96" s="120" t="str">
+        <x:v>总成本 USD</x:v>
+      </x:c>
+      <x:c r="E96" s="120" t="str">
+        <x:v>题 1 分</x:v>
+      </x:c>
+      <x:c r="F96" s="120" t="str">
+        <x:v>题 2 分</x:v>
+      </x:c>
+      <x:c r="G96" s="120" t="str">
+        <x:v>题 3 分</x:v>
+      </x:c>
+      <x:c r="H96" s="120" t="str">
+        <x:v>题 1 USD</x:v>
+      </x:c>
+      <x:c r="I96" s="120" t="str">
+        <x:v>题 2 USD</x:v>
+      </x:c>
+      <x:c r="J96" s="120" t="str">
+        <x:v>题 3 USD</x:v>
+      </x:c>
+      <x:c r="K96" s="120" t="str">
+        <x:v>回答编号</x:v>
       </x:c>
       <x:c r="L96" s="2"/>
       <x:c r="M96" s="2"/>
@@ -6633,18 +7270,49 @@
       <x:c r="U96" s="2"/>
       <x:c r="V96" s="2"/>
     </x:row>
-    <x:row r="97" ht="21" customHeight="1">
-      <x:c r="A97" s="2"/>
-      <x:c r="B97" s="2"/>
-      <x:c r="C97" s="2"/>
-      <x:c r="D97" s="2"/>
-      <x:c r="E97" s="2"/>
-      <x:c r="F97" s="2"/>
-      <x:c r="G97" s="2"/>
-      <x:c r="H97" s="2"/>
-      <x:c r="I97" s="2"/>
-      <x:c r="J97" s="2"/>
-      <x:c r="K97" s="2"/>
+    <x:row r="97" ht="33" customHeight="1">
+      <x:c r="A97" s="31" t="str">
+        <x:v>三题均用 Luna max</x:v>
+      </x:c>
+      <x:c r="B97" s="12" t="n">
+        <x:f>SUM(E97:G97)</x:f>
+        <x:v>215</x:v>
+      </x:c>
+      <x:c r="C97" s="23" t="n">
+        <x:f>B97/3</x:f>
+        <x:v>71.66666666666667</x:v>
+      </x:c>
+      <x:c r="D97" s="20" t="n">
+        <x:f>SUM(H97:J97)</x:f>
+        <x:v>0.46399999999999997</x:v>
+      </x:c>
+      <x:c r="E97" s="12" t="n">
+        <x:f>'Task 1'!D8</x:f>
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="F97" s="12" t="n">
+        <x:f>'Task 2'!D3</x:f>
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="G97" s="12" t="n">
+        <x:f>'Task 3'!D3</x:f>
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="H97" s="20" t="n">
+        <x:f>'Task 1'!C8</x:f>
+        <x:v>0.178</x:v>
+      </x:c>
+      <x:c r="I97" s="20" t="n">
+        <x:f>'Task 2'!C3</x:f>
+        <x:v>0.143</x:v>
+      </x:c>
+      <x:c r="J97" s="20" t="n">
+        <x:f>'Task 3'!C3</x:f>
+        <x:v>0.143</x:v>
+      </x:c>
+      <x:c r="K97" s="61" t="str">
+        <x:v>s_1c / 2b / 3b</x:v>
+      </x:c>
       <x:c r="L97" s="2"/>
       <x:c r="M97" s="2"/>
       <x:c r="N97" s="2"/>
@@ -6657,20 +7325,49 @@
       <x:c r="U97" s="2"/>
       <x:c r="V97" s="2"/>
     </x:row>
-    <x:row r="98" ht="21" customHeight="1">
-      <x:c r="A98" s="4" t="str">
-        <x:v>组合利用本次已知得分选题，不代表未来新题可预先取得同样效果；完整选型名称见分析报告。</x:v>
-      </x:c>
-      <x:c r="B98" s="4"/>
-      <x:c r="C98" s="4"/>
-      <x:c r="D98" s="4"/>
-      <x:c r="E98" s="4"/>
-      <x:c r="F98" s="4"/>
-      <x:c r="G98" s="4"/>
-      <x:c r="H98" s="4"/>
-      <x:c r="I98" s="4"/>
-      <x:c r="J98" s="4"/>
-      <x:c r="K98" s="4"/>
+    <x:row r="98" ht="33" customHeight="1">
+      <x:c r="A98" s="130" t="str">
+        <x:v>每题至少 75 分：最低成本</x:v>
+      </x:c>
+      <x:c r="B98" s="122" t="n">
+        <x:f>SUM(E98:G98)</x:f>
+        <x:v>257</x:v>
+      </x:c>
+      <x:c r="C98" s="127" t="n">
+        <x:f>B98/3</x:f>
+        <x:v>85.66666666666667</x:v>
+      </x:c>
+      <x:c r="D98" s="125" t="n">
+        <x:f>SUM(H98:J98)</x:f>
+        <x:v>1.8980000000000001</x:v>
+      </x:c>
+      <x:c r="E98" s="122" t="n">
+        <x:f>'Task 1'!D10</x:f>
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="F98" s="122" t="n">
+        <x:f>'Task 2'!D3</x:f>
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="G98" s="122" t="n">
+        <x:f>'Task 3'!D3</x:f>
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="H98" s="125" t="n">
+        <x:f>'Task 1'!C10</x:f>
+        <x:v>1.612</x:v>
+      </x:c>
+      <x:c r="I98" s="125" t="n">
+        <x:f>'Task 2'!C3</x:f>
+        <x:v>0.143</x:v>
+      </x:c>
+      <x:c r="J98" s="125" t="n">
+        <x:f>'Task 3'!C3</x:f>
+        <x:v>0.143</x:v>
+      </x:c>
+      <x:c r="K98" s="132" t="str">
+        <x:v>s2_1a / 2b / 3b</x:v>
+      </x:c>
       <x:c r="L98" s="2"/>
       <x:c r="M98" s="2"/>
       <x:c r="N98" s="2"/>
@@ -6683,18 +7380,49 @@
       <x:c r="U98" s="2"/>
       <x:c r="V98" s="2"/>
     </x:row>
-    <x:row r="99" ht="21" customHeight="1">
-      <x:c r="A99" s="2"/>
-      <x:c r="B99" s="2"/>
-      <x:c r="C99" s="2"/>
-      <x:c r="D99" s="2"/>
-      <x:c r="E99" s="2"/>
-      <x:c r="F99" s="2"/>
-      <x:c r="G99" s="2"/>
-      <x:c r="H99" s="2"/>
-      <x:c r="I99" s="2"/>
-      <x:c r="J99" s="2"/>
-      <x:c r="K99" s="2"/>
+    <x:row r="99" ht="33" customHeight="1">
+      <x:c r="A99" s="31" t="str">
+        <x:v>每题至少 80 分：最低成本</x:v>
+      </x:c>
+      <x:c r="B99" s="12" t="n">
+        <x:f>SUM(E99:G99)</x:f>
+        <x:v>279</x:v>
+      </x:c>
+      <x:c r="C99" s="23" t="n">
+        <x:f>B99/3</x:f>
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="D99" s="20" t="n">
+        <x:f>SUM(H99:J99)</x:f>
+        <x:v>3.1260000000000003</x:v>
+      </x:c>
+      <x:c r="E99" s="12" t="n">
+        <x:f>'Task 1'!D10</x:f>
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="F99" s="12" t="n">
+        <x:f>'Task 2'!D3</x:f>
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="G99" s="12" t="n">
+        <x:f>'Task 3'!D10</x:f>
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="H99" s="20" t="n">
+        <x:f>'Task 1'!C10</x:f>
+        <x:v>1.612</x:v>
+      </x:c>
+      <x:c r="I99" s="20" t="n">
+        <x:f>'Task 2'!C3</x:f>
+        <x:v>0.143</x:v>
+      </x:c>
+      <x:c r="J99" s="20" t="n">
+        <x:f>'Task 3'!C10</x:f>
+        <x:v>1.371</x:v>
+      </x:c>
+      <x:c r="K99" s="61" t="str">
+        <x:v>s2_1a / 2b / s2_3a</x:v>
+      </x:c>
       <x:c r="L99" s="2"/>
       <x:c r="M99" s="2"/>
       <x:c r="N99" s="2"/>
@@ -6707,20 +7435,49 @@
       <x:c r="U99" s="2"/>
       <x:c r="V99" s="2"/>
     </x:row>
-    <x:row r="100" ht="24" customHeight="1">
-      <x:c r="A100" s="27" t="str">
-        <x:v>统一模型配置的边际成本</x:v>
-      </x:c>
-      <x:c r="B100" s="27"/>
-      <x:c r="C100" s="27"/>
-      <x:c r="D100" s="27"/>
-      <x:c r="E100" s="27"/>
-      <x:c r="F100" s="27"/>
-      <x:c r="G100" s="27"/>
-      <x:c r="H100" s="27"/>
-      <x:c r="I100" s="27"/>
-      <x:c r="J100" s="27"/>
-      <x:c r="K100" s="27"/>
+    <x:row r="100" ht="33" customHeight="1">
+      <x:c r="A100" s="130" t="str">
+        <x:v>每题至少 90 分：最低成本</x:v>
+      </x:c>
+      <x:c r="B100" s="122" t="n">
+        <x:f>SUM(E100:G100)</x:f>
+        <x:v>291</x:v>
+      </x:c>
+      <x:c r="C100" s="127" t="n">
+        <x:f>B100/3</x:f>
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="D100" s="125" t="n">
+        <x:f>SUM(H100:J100)</x:f>
+        <x:v>4.093999999999999</x:v>
+      </x:c>
+      <x:c r="E100" s="122" t="n">
+        <x:f>'Task 1'!D10</x:f>
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="F100" s="122" t="n">
+        <x:f>'Task 2'!D10</x:f>
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="G100" s="122" t="n">
+        <x:f>'Task 3'!D10</x:f>
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="H100" s="125" t="n">
+        <x:f>'Task 1'!C10</x:f>
+        <x:v>1.612</x:v>
+      </x:c>
+      <x:c r="I100" s="125" t="n">
+        <x:f>'Task 2'!C10</x:f>
+        <x:v>1.111</x:v>
+      </x:c>
+      <x:c r="J100" s="125" t="n">
+        <x:f>'Task 3'!C10</x:f>
+        <x:v>1.371</x:v>
+      </x:c>
+      <x:c r="K100" s="132" t="str">
+        <x:v>s2_1a / s2_2a / s2_3a</x:v>
+      </x:c>
       <x:c r="L100" s="2"/>
       <x:c r="M100" s="2"/>
       <x:c r="N100" s="2"/>
@@ -6733,18 +7490,49 @@
       <x:c r="U100" s="2"/>
       <x:c r="V100" s="2"/>
     </x:row>
-    <x:row r="101" ht="21" customHeight="1">
-      <x:c r="A101" s="2"/>
-      <x:c r="B101" s="2"/>
-      <x:c r="C101" s="2"/>
-      <x:c r="D101" s="2"/>
-      <x:c r="E101" s="2"/>
-      <x:c r="F101" s="2"/>
-      <x:c r="G101" s="2"/>
-      <x:c r="H101" s="2"/>
-      <x:c r="I101" s="2"/>
-      <x:c r="J101" s="2"/>
-      <x:c r="K101" s="2"/>
+    <x:row r="101" ht="33" customHeight="1">
+      <x:c r="A101" s="31" t="str">
+        <x:v>每题至少 95 分：最低成本</x:v>
+      </x:c>
+      <x:c r="B101" s="12" t="n">
+        <x:f>SUM(E101:G101)</x:f>
+        <x:v>291</x:v>
+      </x:c>
+      <x:c r="C101" s="23" t="n">
+        <x:f>B101/3</x:f>
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="D101" s="20" t="n">
+        <x:f>SUM(H101:J101)</x:f>
+        <x:v>4.093999999999999</x:v>
+      </x:c>
+      <x:c r="E101" s="12" t="n">
+        <x:f>'Task 1'!D10</x:f>
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="F101" s="12" t="n">
+        <x:f>'Task 2'!D10</x:f>
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="G101" s="12" t="n">
+        <x:f>'Task 3'!D10</x:f>
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="H101" s="20" t="n">
+        <x:f>'Task 1'!C10</x:f>
+        <x:v>1.612</x:v>
+      </x:c>
+      <x:c r="I101" s="20" t="n">
+        <x:f>'Task 2'!C10</x:f>
+        <x:v>1.111</x:v>
+      </x:c>
+      <x:c r="J101" s="20" t="n">
+        <x:f>'Task 3'!C10</x:f>
+        <x:v>1.371</x:v>
+      </x:c>
+      <x:c r="K101" s="61" t="str">
+        <x:v>s2_1a / s2_2a / s2_3a</x:v>
+      </x:c>
       <x:c r="L101" s="2"/>
       <x:c r="M101" s="2"/>
       <x:c r="N101" s="2"/>
@@ -6757,34 +7545,49 @@
       <x:c r="U101" s="2"/>
       <x:c r="V101" s="2"/>
     </x:row>
-    <x:row r="102" ht="35" customHeight="1">
-      <x:c r="A102" s="69" t="str">
-        <x:v>比较（全部三题）</x:v>
-      </x:c>
-      <x:c r="B102" s="69" t="str">
-        <x:v>总分增量</x:v>
-      </x:c>
-      <x:c r="C102" s="69" t="str">
-        <x:v>均分增量</x:v>
-      </x:c>
-      <x:c r="D102" s="69" t="str">
-        <x:v>美元增量</x:v>
-      </x:c>
-      <x:c r="E102" s="69" t="str">
-        <x:v>成本变化率</x:v>
-      </x:c>
-      <x:c r="F102" s="69" t="str">
-        <x:v>USD /分</x:v>
-      </x:c>
-      <x:c r="G102" s="69" t="str">
-        <x:v>前者总成本</x:v>
-      </x:c>
-      <x:c r="H102" s="69" t="str">
-        <x:v>后者总成本</x:v>
-      </x:c>
-      <x:c r="I102" s="2"/>
-      <x:c r="J102" s="2"/>
-      <x:c r="K102" s="2"/>
+    <x:row r="102" ht="33" customHeight="1">
+      <x:c r="A102" s="130" t="str">
+        <x:v>三题均用 6.1 Sol xhigh</x:v>
+      </x:c>
+      <x:c r="B102" s="122" t="n">
+        <x:f>SUM(E102:G102)</x:f>
+        <x:v>291</x:v>
+      </x:c>
+      <x:c r="C102" s="127" t="n">
+        <x:f>B102/3</x:f>
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="D102" s="125" t="n">
+        <x:f>SUM(H102:J102)</x:f>
+        <x:v>4.093999999999999</x:v>
+      </x:c>
+      <x:c r="E102" s="122" t="n">
+        <x:f>'Task 1'!D10</x:f>
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="F102" s="122" t="n">
+        <x:f>'Task 2'!D10</x:f>
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="G102" s="122" t="n">
+        <x:f>'Task 3'!D10</x:f>
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="H102" s="125" t="n">
+        <x:f>'Task 1'!C10</x:f>
+        <x:v>1.612</x:v>
+      </x:c>
+      <x:c r="I102" s="125" t="n">
+        <x:f>'Task 2'!C10</x:f>
+        <x:v>1.111</x:v>
+      </x:c>
+      <x:c r="J102" s="125" t="n">
+        <x:f>'Task 3'!C10</x:f>
+        <x:v>1.371</x:v>
+      </x:c>
+      <x:c r="K102" s="132" t="str">
+        <x:v>s2_1a / s2_2a / s2_3a</x:v>
+      </x:c>
       <x:c r="L102" s="2"/>
       <x:c r="M102" s="2"/>
       <x:c r="N102" s="2"/>
@@ -6797,41 +7600,49 @@
       <x:c r="U102" s="2"/>
       <x:c r="V102" s="2"/>
     </x:row>
-    <x:row r="103" ht="21" customHeight="1">
-      <x:c r="A103" s="2" t="str">
-        <x:v>Sol xhigh 相对 Luna max</x:v>
+    <x:row r="103" ht="33" customHeight="1">
+      <x:c r="A103" s="31" t="str">
+        <x:v>三题均用 6.1 Sol max</x:v>
       </x:c>
       <x:c r="B103" s="12" t="n">
-        <x:f>C22-C24</x:f>
-        <x:v>21</x:v>
+        <x:f>SUM(E103:G103)</x:f>
+        <x:v>294</x:v>
       </x:c>
       <x:c r="C103" s="23" t="n">
-        <x:f>D22-D24</x:f>
-        <x:v>7</x:v>
+        <x:f>B103/3</x:f>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D103" s="20" t="n">
-        <x:f>E22-E24</x:f>
-        <x:v>5.720000000000001</x:v>
-      </x:c>
-      <x:c r="E103" s="38" t="n">
-        <x:f>D103/E24</x:f>
-        <x:v>12.327586206896553</x:v>
-      </x:c>
-      <x:c r="F103" s="20" t="n">
-        <x:f>D103/B103</x:f>
-        <x:v>0.2723809523809524</x:v>
-      </x:c>
-      <x:c r="G103" s="20" t="n">
-        <x:f>E22</x:f>
-        <x:v>6.184</x:v>
+        <x:f>SUM(H103:J103)</x:f>
+        <x:v>4.576</x:v>
+      </x:c>
+      <x:c r="E103" s="12" t="n">
+        <x:f>'Task 1'!D11</x:f>
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="F103" s="12" t="n">
+        <x:f>'Task 2'!D11</x:f>
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="G103" s="12" t="n">
+        <x:f>'Task 3'!D11</x:f>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="H103" s="20" t="n">
-        <x:f>E24</x:f>
-        <x:v>0.46399999999999997</x:v>
-      </x:c>
-      <x:c r="I103" s="2"/>
-      <x:c r="J103" s="2"/>
-      <x:c r="K103" s="2"/>
+        <x:f>'Task 1'!C11</x:f>
+        <x:v>1.795</x:v>
+      </x:c>
+      <x:c r="I103" s="20" t="n">
+        <x:f>'Task 2'!C11</x:f>
+        <x:v>1.14</x:v>
+      </x:c>
+      <x:c r="J103" s="20" t="n">
+        <x:f>'Task 3'!C11</x:f>
+        <x:v>1.641</x:v>
+      </x:c>
+      <x:c r="K103" s="61" t="str">
+        <x:v>s2_1b / s2_2b / s2_3b</x:v>
+      </x:c>
       <x:c r="L103" s="2"/>
       <x:c r="M103" s="2"/>
       <x:c r="N103" s="2"/>
@@ -6844,41 +7655,49 @@
       <x:c r="U103" s="2"/>
       <x:c r="V103" s="2"/>
     </x:row>
-    <x:row r="104" ht="21" customHeight="1">
-      <x:c r="A104" s="70" t="str">
-        <x:v>Sol max 相对 Sol xhigh</x:v>
-      </x:c>
-      <x:c r="B104" s="71" t="n">
-        <x:f>C20-C22</x:f>
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="C104" s="76" t="n">
-        <x:f>D20-D22</x:f>
-        <x:v>15.666666666666657</x:v>
-      </x:c>
-      <x:c r="D104" s="74" t="n">
-        <x:f>E20-E22</x:f>
-        <x:v>2.0680000000000005</x:v>
-      </x:c>
-      <x:c r="E104" s="82" t="n">
-        <x:f>D104/E22</x:f>
-        <x:v>0.33441138421733513</x:v>
-      </x:c>
-      <x:c r="F104" s="74" t="n">
-        <x:f>D104/B104</x:f>
-        <x:v>0.04400000000000001</x:v>
-      </x:c>
-      <x:c r="G104" s="74" t="n">
-        <x:f>E20</x:f>
-        <x:v>8.252</x:v>
-      </x:c>
-      <x:c r="H104" s="74" t="n">
-        <x:f>E22</x:f>
-        <x:v>6.184</x:v>
-      </x:c>
-      <x:c r="I104" s="2"/>
-      <x:c r="J104" s="2"/>
-      <x:c r="K104" s="2"/>
+    <x:row r="104" ht="33" customHeight="1">
+      <x:c r="A104" s="131" t="str">
+        <x:v>逐题最高分：最低成本</x:v>
+      </x:c>
+      <x:c r="B104" s="124" t="n">
+        <x:f>SUM(E104:G104)</x:f>
+        <x:v>294</x:v>
+      </x:c>
+      <x:c r="C104" s="128" t="n">
+        <x:f>B104/3</x:f>
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="D104" s="126" t="n">
+        <x:f>SUM(H104:J104)</x:f>
+        <x:v>4.547</x:v>
+      </x:c>
+      <x:c r="E104" s="124" t="n">
+        <x:f>'Task 1'!D11</x:f>
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="F104" s="124" t="n">
+        <x:f>'Task 2'!D10</x:f>
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="G104" s="124" t="n">
+        <x:f>'Task 3'!D11</x:f>
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="H104" s="126" t="n">
+        <x:f>'Task 1'!C11</x:f>
+        <x:v>1.795</x:v>
+      </x:c>
+      <x:c r="I104" s="126" t="n">
+        <x:f>'Task 2'!C10</x:f>
+        <x:v>1.111</x:v>
+      </x:c>
+      <x:c r="J104" s="126" t="n">
+        <x:f>'Task 3'!C11</x:f>
+        <x:v>1.641</x:v>
+      </x:c>
+      <x:c r="K104" s="133" t="str">
+        <x:v>s2_1b / s2_2a / s2_3b</x:v>
+      </x:c>
       <x:c r="L104" s="2"/>
       <x:c r="M104" s="2"/>
       <x:c r="N104" s="2"/>
@@ -6892,37 +7711,14 @@
       <x:c r="V104" s="2"/>
     </x:row>
     <x:row r="105" ht="21" customHeight="1">
-      <x:c r="A105" s="15" t="str">
-        <x:v>Astra high 相对 Sol max</x:v>
-      </x:c>
-      <x:c r="B105" s="16" t="n">
-        <x:f>C19-C20</x:f>
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C105" s="25" t="n">
-        <x:f>D19-D20</x:f>
-        <x:v>1.3333333333333428</x:v>
-      </x:c>
-      <x:c r="D105" s="22" t="n">
-        <x:f>E19-E20</x:f>
-        <x:v>6.118</x:v>
-      </x:c>
-      <x:c r="E105" s="65" t="n">
-        <x:f>D105/E20</x:f>
-        <x:v>0.7413960252060107</x:v>
-      </x:c>
-      <x:c r="F105" s="22" t="n">
-        <x:f>D105/B105</x:f>
-        <x:v>1.5295</x:v>
-      </x:c>
-      <x:c r="G105" s="22" t="n">
-        <x:f>E19</x:f>
-        <x:v>14.370000000000001</x:v>
-      </x:c>
-      <x:c r="H105" s="22" t="n">
-        <x:f>E20</x:f>
-        <x:v>8.252</x:v>
-      </x:c>
+      <x:c r="A105" s="2"/>
+      <x:c r="B105" s="2"/>
+      <x:c r="C105" s="2"/>
+      <x:c r="D105" s="2"/>
+      <x:c r="E105" s="2"/>
+      <x:c r="F105" s="2"/>
+      <x:c r="G105" s="2"/>
+      <x:c r="H105" s="2"/>
       <x:c r="I105" s="2"/>
       <x:c r="J105" s="2"/>
       <x:c r="K105" s="2"/>
@@ -6939,17 +7735,19 @@
       <x:c r="V105" s="2"/>
     </x:row>
     <x:row r="106" ht="21" customHeight="1">
-      <x:c r="A106" s="2"/>
-      <x:c r="B106" s="2"/>
-      <x:c r="C106" s="2"/>
-      <x:c r="D106" s="2"/>
-      <x:c r="E106" s="2"/>
-      <x:c r="F106" s="2"/>
-      <x:c r="G106" s="2"/>
-      <x:c r="H106" s="2"/>
-      <x:c r="I106" s="2"/>
-      <x:c r="J106" s="2"/>
-      <x:c r="K106" s="2"/>
+      <x:c r="A106" s="4" t="str">
+        <x:v>组合依据本次已知得分作事后选择，不能外推为未来新题的预期效果；完整模型名称见分析报告。</x:v>
+      </x:c>
+      <x:c r="B106" s="4"/>
+      <x:c r="C106" s="4"/>
+      <x:c r="D106" s="4"/>
+      <x:c r="E106" s="4"/>
+      <x:c r="F106" s="4"/>
+      <x:c r="G106" s="4"/>
+      <x:c r="H106" s="4"/>
+      <x:c r="I106" s="4"/>
+      <x:c r="J106" s="4"/>
+      <x:c r="K106" s="4"/>
       <x:c r="L106" s="2"/>
       <x:c r="M106" s="2"/>
       <x:c r="N106" s="2"/>
@@ -6988,7 +7786,7 @@
     </x:row>
     <x:row r="108" ht="24" customHeight="1">
       <x:c r="A108" s="27" t="str">
-        <x:v>统计口径与数据来源</x:v>
+        <x:v>统一模型配置的边际成本</x:v>
       </x:c>
       <x:c r="B108" s="27"/>
       <x:c r="C108" s="27"/>
@@ -7036,20 +7834,34 @@
       <x:c r="U109" s="2"/>
       <x:c r="V109" s="2"/>
     </x:row>
-    <x:row r="110" ht="21" customHeight="1">
-      <x:c r="A110" s="4" t="str">
-        <x:v>评分沿用原始及 Supplement 已完成评阅：定义 15、校准 30、验证 15、推进 30、结论校准 10。</x:v>
-      </x:c>
-      <x:c r="B110" s="4"/>
-      <x:c r="C110" s="4"/>
-      <x:c r="D110" s="4"/>
-      <x:c r="E110" s="4"/>
-      <x:c r="F110" s="4"/>
-      <x:c r="G110" s="4"/>
-      <x:c r="H110" s="4"/>
-      <x:c r="I110" s="4"/>
-      <x:c r="J110" s="4"/>
-      <x:c r="K110" s="4"/>
+    <x:row r="110" ht="35" customHeight="1">
+      <x:c r="A110" s="120" t="str">
+        <x:v>比较（全部三题）</x:v>
+      </x:c>
+      <x:c r="B110" s="120" t="str">
+        <x:v>总分增量</x:v>
+      </x:c>
+      <x:c r="C110" s="120" t="str">
+        <x:v>均分增量</x:v>
+      </x:c>
+      <x:c r="D110" s="120" t="str">
+        <x:v>美元增量</x:v>
+      </x:c>
+      <x:c r="E110" s="120" t="str">
+        <x:v>成本变化率</x:v>
+      </x:c>
+      <x:c r="F110" s="120" t="str">
+        <x:v>USD /分</x:v>
+      </x:c>
+      <x:c r="G110" s="120" t="str">
+        <x:v>前者总成本</x:v>
+      </x:c>
+      <x:c r="H110" s="120" t="str">
+        <x:v>后者总成本</x:v>
+      </x:c>
+      <x:c r="I110" s="2"/>
+      <x:c r="J110" s="2"/>
+      <x:c r="K110" s="2"/>
       <x:c r="L110" s="2"/>
       <x:c r="M110" s="2"/>
       <x:c r="N110" s="2"/>
@@ -7062,20 +7874,41 @@
       <x:c r="U110" s="2"/>
       <x:c r="V110" s="2"/>
     </x:row>
-    <x:row r="111" ht="21" customHeight="1">
-      <x:c r="A111" s="4" t="str">
-        <x:v>身份与新增成本来自用户本轮映射；原有费用保留。三份 Opus 补充报告替换其对应回答，成本不重复计入。</x:v>
-      </x:c>
-      <x:c r="B111" s="4"/>
-      <x:c r="C111" s="4"/>
-      <x:c r="D111" s="4"/>
-      <x:c r="E111" s="4"/>
-      <x:c r="F111" s="4"/>
-      <x:c r="G111" s="4"/>
-      <x:c r="H111" s="4"/>
-      <x:c r="I111" s="4"/>
-      <x:c r="J111" s="4"/>
-      <x:c r="K111" s="4"/>
+    <x:row r="111" ht="28.5" customHeight="1">
+      <x:c r="A111" s="31" t="str">
+        <x:v>6.1 max 相对 6.1 xhigh</x:v>
+      </x:c>
+      <x:c r="B111" s="12" t="n">
+        <x:f>C21-C22</x:f>
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C111" s="23" t="n">
+        <x:f>D21-D22</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D111" s="20" t="n">
+        <x:f>E21-E22</x:f>
+        <x:v>0.4820000000000002</x:v>
+      </x:c>
+      <x:c r="E111" s="38" t="n">
+        <x:f>D111/E22</x:f>
+        <x:v>0.11773326819736206</x:v>
+      </x:c>
+      <x:c r="F111" s="20" t="n">
+        <x:f>D111/B111</x:f>
+        <x:v>0.16066666666666674</x:v>
+      </x:c>
+      <x:c r="G111" s="20" t="n">
+        <x:f>E21</x:f>
+        <x:v>4.576</x:v>
+      </x:c>
+      <x:c r="H111" s="20" t="n">
+        <x:f>E22</x:f>
+        <x:v>4.093999999999999</x:v>
+      </x:c>
+      <x:c r="I111" s="2"/>
+      <x:c r="J111" s="2"/>
+      <x:c r="K111" s="2"/>
       <x:c r="L111" s="2"/>
       <x:c r="M111" s="2"/>
       <x:c r="N111" s="2"/>
@@ -7088,20 +7921,41 @@
       <x:c r="U111" s="2"/>
       <x:c r="V111" s="2"/>
     </x:row>
-    <x:row r="112" ht="21" customHeight="1">
-      <x:c r="A112" s="4" t="str">
-        <x:v>每个配置均有三题，均分采用等权；模型排名、均分与合计成本由 Task 1–3 的单元格公式计算。</x:v>
-      </x:c>
-      <x:c r="B112" s="4"/>
-      <x:c r="C112" s="4"/>
-      <x:c r="D112" s="4"/>
-      <x:c r="E112" s="4"/>
-      <x:c r="F112" s="4"/>
-      <x:c r="G112" s="4"/>
-      <x:c r="H112" s="4"/>
-      <x:c r="I112" s="4"/>
-      <x:c r="J112" s="4"/>
-      <x:c r="K112" s="4"/>
+    <x:row r="112" ht="28.5" customHeight="1">
+      <x:c r="A112" s="130" t="str">
+        <x:v>6.1 xhigh 相对 6 Sol max</x:v>
+      </x:c>
+      <x:c r="B112" s="122" t="n">
+        <x:f>C22-C24</x:f>
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C112" s="127" t="n">
+        <x:f>D22-D24</x:f>
+        <x:v>2.6666666666666714</x:v>
+      </x:c>
+      <x:c r="D112" s="125" t="n">
+        <x:f>E22-E24</x:f>
+        <x:v>-4.158000000000001</x:v>
+      </x:c>
+      <x:c r="E112" s="134" t="n">
+        <x:f>D112/E24</x:f>
+        <x:v>-0.5038778477944742</x:v>
+      </x:c>
+      <x:c r="F112" s="125" t="n">
+        <x:f>D112/B112</x:f>
+        <x:v>-0.5197500000000002</x:v>
+      </x:c>
+      <x:c r="G112" s="125" t="n">
+        <x:f>E22</x:f>
+        <x:v>4.093999999999999</x:v>
+      </x:c>
+      <x:c r="H112" s="125" t="n">
+        <x:f>E24</x:f>
+        <x:v>8.252</x:v>
+      </x:c>
+      <x:c r="I112" s="2"/>
+      <x:c r="J112" s="2"/>
+      <x:c r="K112" s="2"/>
       <x:c r="L112" s="2"/>
       <x:c r="M112" s="2"/>
       <x:c r="N112" s="2"/>
@@ -7114,20 +7968,41 @@
       <x:c r="U112" s="2"/>
       <x:c r="V112" s="2"/>
     </x:row>
-    <x:row r="113" ht="21" customHeight="1">
-      <x:c r="A113" s="4" t="str">
-        <x:v>参考：评分明细.json、补充评分明细.json，以及两批 q1/q2/q3_assessment.md；报告保留逐题依据。</x:v>
-      </x:c>
-      <x:c r="B113" s="4"/>
-      <x:c r="C113" s="4"/>
-      <x:c r="D113" s="4"/>
-      <x:c r="E113" s="4"/>
-      <x:c r="F113" s="4"/>
-      <x:c r="G113" s="4"/>
-      <x:c r="H113" s="4"/>
-      <x:c r="I113" s="4"/>
-      <x:c r="J113" s="4"/>
-      <x:c r="K113" s="4"/>
+    <x:row r="113" ht="28.5" customHeight="1">
+      <x:c r="A113" s="31" t="str">
+        <x:v>6.1 max 相对 6 Sol max</x:v>
+      </x:c>
+      <x:c r="B113" s="12" t="n">
+        <x:f>C21-C24</x:f>
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C113" s="23" t="n">
+        <x:f>D21-D24</x:f>
+        <x:v>3.6666666666666714</x:v>
+      </x:c>
+      <x:c r="D113" s="20" t="n">
+        <x:f>E21-E24</x:f>
+        <x:v>-3.676000000000001</x:v>
+      </x:c>
+      <x:c r="E113" s="38" t="n">
+        <x:f>D113/E24</x:f>
+        <x:v>-0.44546776539020855</x:v>
+      </x:c>
+      <x:c r="F113" s="20" t="n">
+        <x:f>D113/B113</x:f>
+        <x:v>-0.3341818181818183</x:v>
+      </x:c>
+      <x:c r="G113" s="20" t="n">
+        <x:f>E21</x:f>
+        <x:v>4.576</x:v>
+      </x:c>
+      <x:c r="H113" s="20" t="n">
+        <x:f>E24</x:f>
+        <x:v>8.252</x:v>
+      </x:c>
+      <x:c r="I113" s="2"/>
+      <x:c r="J113" s="2"/>
+      <x:c r="K113" s="2"/>
       <x:c r="L113" s="2"/>
       <x:c r="M113" s="2"/>
       <x:c r="N113" s="2"/>
@@ -7140,20 +8015,41 @@
       <x:c r="U113" s="2"/>
       <x:c r="V113" s="2"/>
     </x:row>
-    <x:row r="114" ht="21" customHeight="1">
-      <x:c r="A114" s="4" t="str">
-        <x:v>每个模型—题目仅一个样本。Opus 采用格式统一后的报告；这里比较最终提交版本，并非完全统一的首轮协议实验。</x:v>
-      </x:c>
-      <x:c r="B114" s="4"/>
-      <x:c r="C114" s="4"/>
-      <x:c r="D114" s="4"/>
-      <x:c r="E114" s="4"/>
-      <x:c r="F114" s="4"/>
-      <x:c r="G114" s="4"/>
-      <x:c r="H114" s="4"/>
-      <x:c r="I114" s="4"/>
-      <x:c r="J114" s="4"/>
-      <x:c r="K114" s="4"/>
+    <x:row r="114" ht="28.5" customHeight="1">
+      <x:c r="A114" s="130" t="str">
+        <x:v>6.1 xhigh 相对 Astra high</x:v>
+      </x:c>
+      <x:c r="B114" s="122" t="n">
+        <x:f>C22-C23</x:f>
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C114" s="127" t="n">
+        <x:f>D22-D23</x:f>
+        <x:v>1.3333333333333286</x:v>
+      </x:c>
+      <x:c r="D114" s="125" t="n">
+        <x:f>E22-E23</x:f>
+        <x:v>-10.276000000000002</x:v>
+      </x:c>
+      <x:c r="E114" s="134" t="n">
+        <x:f>D114/E23</x:f>
+        <x:v>-0.7151009046624913</x:v>
+      </x:c>
+      <x:c r="F114" s="125" t="n">
+        <x:f>D114/B114</x:f>
+        <x:v>-2.5690000000000004</x:v>
+      </x:c>
+      <x:c r="G114" s="125" t="n">
+        <x:f>E22</x:f>
+        <x:v>4.093999999999999</x:v>
+      </x:c>
+      <x:c r="H114" s="125" t="n">
+        <x:f>E23</x:f>
+        <x:v>14.370000000000001</x:v>
+      </x:c>
+      <x:c r="I114" s="2"/>
+      <x:c r="J114" s="2"/>
+      <x:c r="K114" s="2"/>
       <x:c r="L114" s="2"/>
       <x:c r="M114" s="2"/>
       <x:c r="N114" s="2"/>
@@ -7166,20 +8062,41 @@
       <x:c r="U114" s="2"/>
       <x:c r="V114" s="2"/>
     </x:row>
-    <x:row r="115" ht="21" customHeight="1">
-      <x:c r="A115" s="4" t="str">
-        <x:v>成本是用户记录的美元用量；无 token、FLOPs、耗时及重复运行数据，不能推断算力缩放律或总体胜率。</x:v>
-      </x:c>
-      <x:c r="B115" s="4"/>
-      <x:c r="C115" s="4"/>
-      <x:c r="D115" s="4"/>
-      <x:c r="E115" s="4"/>
-      <x:c r="F115" s="4"/>
-      <x:c r="G115" s="4"/>
-      <x:c r="H115" s="4"/>
-      <x:c r="I115" s="4"/>
-      <x:c r="J115" s="4"/>
-      <x:c r="K115" s="4"/>
+    <x:row r="115" ht="28.5" customHeight="1">
+      <x:c r="A115" s="33" t="str">
+        <x:v>6.1 xhigh 相对 Luna max</x:v>
+      </x:c>
+      <x:c r="B115" s="16" t="n">
+        <x:f>C22-C28</x:f>
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="C115" s="25" t="n">
+        <x:f>D22-D28</x:f>
+        <x:v>25.33333333333333</x:v>
+      </x:c>
+      <x:c r="D115" s="22" t="n">
+        <x:f>E22-E28</x:f>
+        <x:v>3.6299999999999994</x:v>
+      </x:c>
+      <x:c r="E115" s="65" t="n">
+        <x:f>D115/E28</x:f>
+        <x:v>7.823275862068965</x:v>
+      </x:c>
+      <x:c r="F115" s="22" t="n">
+        <x:f>D115/B115</x:f>
+        <x:v>0.047763157894736834</x:v>
+      </x:c>
+      <x:c r="G115" s="22" t="n">
+        <x:f>E22</x:f>
+        <x:v>4.093999999999999</x:v>
+      </x:c>
+      <x:c r="H115" s="22" t="n">
+        <x:f>E28</x:f>
+        <x:v>0.46399999999999997</x:v>
+      </x:c>
+      <x:c r="I115" s="2"/>
+      <x:c r="J115" s="2"/>
+      <x:c r="K115" s="2"/>
       <x:c r="L115" s="2"/>
       <x:c r="M115" s="2"/>
       <x:c r="N115" s="2"/>
@@ -7193,19 +8110,17 @@
       <x:c r="V115" s="2"/>
     </x:row>
     <x:row r="116" ht="21" customHeight="1">
-      <x:c r="A116" s="4" t="str">
-        <x:v>成本—得分前沿：不存在成本不高、得分不低且至少一项更优的另一配置；小分差应结合评阅范围理解。</x:v>
-      </x:c>
-      <x:c r="B116" s="4"/>
-      <x:c r="C116" s="4"/>
-      <x:c r="D116" s="4"/>
-      <x:c r="E116" s="4"/>
-      <x:c r="F116" s="4"/>
-      <x:c r="G116" s="4"/>
-      <x:c r="H116" s="4"/>
-      <x:c r="I116" s="4"/>
-      <x:c r="J116" s="4"/>
-      <x:c r="K116" s="4"/>
+      <x:c r="A116" s="2"/>
+      <x:c r="B116" s="2"/>
+      <x:c r="C116" s="2"/>
+      <x:c r="D116" s="2"/>
+      <x:c r="E116" s="2"/>
+      <x:c r="F116" s="2"/>
+      <x:c r="G116" s="2"/>
+      <x:c r="H116" s="2"/>
+      <x:c r="I116" s="2"/>
+      <x:c r="J116" s="2"/>
+      <x:c r="K116" s="2"/>
       <x:c r="L116" s="2"/>
       <x:c r="M116" s="2"/>
       <x:c r="N116" s="2"/>
@@ -7219,19 +8134,17 @@
       <x:c r="V116" s="2"/>
     </x:row>
     <x:row r="117" ht="21" customHeight="1">
-      <x:c r="A117" s="4" t="str">
-        <x:v>图中横轴为 log10(USD)：−1=$0.1，0=$1，1=$10；原生图横坐标为本次成本快照，改动成本后需重绘。</x:v>
-      </x:c>
-      <x:c r="B117" s="4"/>
-      <x:c r="C117" s="4"/>
-      <x:c r="D117" s="4"/>
-      <x:c r="E117" s="4"/>
-      <x:c r="F117" s="4"/>
-      <x:c r="G117" s="4"/>
-      <x:c r="H117" s="4"/>
-      <x:c r="I117" s="4"/>
-      <x:c r="J117" s="4"/>
-      <x:c r="K117" s="4"/>
+      <x:c r="A117" s="2"/>
+      <x:c r="B117" s="2"/>
+      <x:c r="C117" s="2"/>
+      <x:c r="D117" s="2"/>
+      <x:c r="E117" s="2"/>
+      <x:c r="F117" s="2"/>
+      <x:c r="G117" s="2"/>
+      <x:c r="H117" s="2"/>
+      <x:c r="I117" s="2"/>
+      <x:c r="J117" s="2"/>
+      <x:c r="K117" s="2"/>
       <x:c r="L117" s="2"/>
       <x:c r="M117" s="2"/>
       <x:c r="N117" s="2"/>
@@ -7244,20 +8157,20 @@
       <x:c r="U117" s="2"/>
       <x:c r="V117" s="2"/>
     </x:row>
-    <x:row r="118" ht="21" customHeight="1">
-      <x:c r="A118" s="4" t="str">
-        <x:v>误差棒与曲线的完整版本见随附 PNG/SVG；图上标注靠近数据点。前沿连线仅帮助阅读，不作连续性能拟合。</x:v>
-      </x:c>
-      <x:c r="B118" s="4"/>
-      <x:c r="C118" s="4"/>
-      <x:c r="D118" s="4"/>
-      <x:c r="E118" s="4"/>
-      <x:c r="F118" s="4"/>
-      <x:c r="G118" s="4"/>
-      <x:c r="H118" s="4"/>
-      <x:c r="I118" s="4"/>
-      <x:c r="J118" s="4"/>
-      <x:c r="K118" s="4"/>
+    <x:row r="118" ht="24" customHeight="1">
+      <x:c r="A118" s="27" t="str">
+        <x:v>统计口径与数据来源</x:v>
+      </x:c>
+      <x:c r="B118" s="27"/>
+      <x:c r="C118" s="27"/>
+      <x:c r="D118" s="27"/>
+      <x:c r="E118" s="27"/>
+      <x:c r="F118" s="27"/>
+      <x:c r="G118" s="27"/>
+      <x:c r="H118" s="27"/>
+      <x:c r="I118" s="27"/>
+      <x:c r="J118" s="27"/>
+      <x:c r="K118" s="27"/>
       <x:c r="L118" s="2"/>
       <x:c r="M118" s="2"/>
       <x:c r="N118" s="2"/>
@@ -7295,22 +8208,19 @@
       <x:c r="V119" s="2"/>
     </x:row>
     <x:row r="120" ht="21" customHeight="1">
-      <x:c r="A120" s="2" t="str">
-        <x:v>本表 24 项有效结果的记录成本 USD</x:v>
-      </x:c>
-      <x:c r="B120" s="2"/>
-      <x:c r="C120" s="2"/>
-      <x:c r="D120" s="2"/>
-      <x:c r="E120" s="40" t="n">
-        <x:f>SUM('Task 1'!C2:C9,'Task 2'!C2:C9,'Task 3'!C2:C9)</x:f>
-        <x:v>116.842</x:v>
-      </x:c>
-      <x:c r="F120" s="2"/>
-      <x:c r="G120" s="2"/>
-      <x:c r="H120" s="2"/>
-      <x:c r="I120" s="2"/>
-      <x:c r="J120" s="2"/>
-      <x:c r="K120" s="2"/>
+      <x:c r="A120" s="4" t="str">
+        <x:v>评分依据三批已完成评阅：定义 15、校准 30、验证 15、推进 30、结论校准 10；本次只合并身份和用量。</x:v>
+      </x:c>
+      <x:c r="B120" s="4"/>
+      <x:c r="C120" s="4"/>
+      <x:c r="D120" s="4"/>
+      <x:c r="E120" s="4"/>
+      <x:c r="F120" s="4"/>
+      <x:c r="G120" s="4"/>
+      <x:c r="H120" s="4"/>
+      <x:c r="I120" s="4"/>
+      <x:c r="J120" s="4"/>
+      <x:c r="K120" s="4"/>
       <x:c r="L120" s="2"/>
       <x:c r="M120" s="2"/>
       <x:c r="N120" s="2"/>
@@ -7324,17 +8234,19 @@
       <x:c r="V120" s="2"/>
     </x:row>
     <x:row r="121" ht="21" customHeight="1">
-      <x:c r="A121" s="2"/>
-      <x:c r="B121" s="2"/>
-      <x:c r="C121" s="2"/>
-      <x:c r="D121" s="2"/>
-      <x:c r="E121" s="2"/>
-      <x:c r="F121" s="2"/>
-      <x:c r="G121" s="2"/>
-      <x:c r="H121" s="2"/>
-      <x:c r="I121" s="2"/>
-      <x:c r="J121" s="2"/>
-      <x:c r="K121" s="2"/>
+      <x:c r="A121" s="4" t="str">
+        <x:v>新增映射：s2_1a / s2_2a / s2_3a = GPT-6.1 Sol xhigh；s2_1b / s2_2b / s2_3b = GPT-6.1 Sol max。</x:v>
+      </x:c>
+      <x:c r="B121" s="4"/>
+      <x:c r="C121" s="4"/>
+      <x:c r="D121" s="4"/>
+      <x:c r="E121" s="4"/>
+      <x:c r="F121" s="4"/>
+      <x:c r="G121" s="4"/>
+      <x:c r="H121" s="4"/>
+      <x:c r="I121" s="4"/>
+      <x:c r="J121" s="4"/>
+      <x:c r="K121" s="4"/>
       <x:c r="L121" s="2"/>
       <x:c r="M121" s="2"/>
       <x:c r="N121" s="2"/>
@@ -7347,20 +8259,20 @@
       <x:c r="U121" s="2"/>
       <x:c r="V121" s="2"/>
     </x:row>
-    <x:row r="122" ht="24" customHeight="1">
-      <x:c r="A122" s="27" t="str">
-        <x:v>逐份回答：五维评分、评阅范围与溯源</x:v>
-      </x:c>
-      <x:c r="B122" s="27"/>
-      <x:c r="C122" s="27"/>
-      <x:c r="D122" s="27"/>
-      <x:c r="E122" s="27"/>
-      <x:c r="F122" s="27"/>
-      <x:c r="G122" s="27"/>
-      <x:c r="H122" s="27"/>
-      <x:c r="I122" s="27"/>
-      <x:c r="J122" s="27"/>
-      <x:c r="K122" s="27"/>
+    <x:row r="122" ht="21" customHeight="1">
+      <x:c r="A122" s="4" t="str">
+        <x:v>xhigh 三题美元消耗：1.612、1.111、1.371；max：1.795、1.140、1.641。来源：用户 2026-09-30 披露。</x:v>
+      </x:c>
+      <x:c r="B122" s="4"/>
+      <x:c r="C122" s="4"/>
+      <x:c r="D122" s="4"/>
+      <x:c r="E122" s="4"/>
+      <x:c r="F122" s="4"/>
+      <x:c r="G122" s="4"/>
+      <x:c r="H122" s="4"/>
+      <x:c r="I122" s="4"/>
+      <x:c r="J122" s="4"/>
+      <x:c r="K122" s="4"/>
       <x:c r="L122" s="2"/>
       <x:c r="M122" s="2"/>
       <x:c r="N122" s="2"/>
@@ -7374,17 +8286,19 @@
       <x:c r="V122" s="2"/>
     </x:row>
     <x:row r="123" ht="21" customHeight="1">
-      <x:c r="A123" s="2"/>
-      <x:c r="B123" s="2"/>
-      <x:c r="C123" s="2"/>
-      <x:c r="D123" s="2"/>
-      <x:c r="E123" s="2"/>
-      <x:c r="F123" s="2"/>
-      <x:c r="G123" s="2"/>
-      <x:c r="H123" s="2"/>
-      <x:c r="I123" s="2"/>
-      <x:c r="J123" s="2"/>
-      <x:c r="K123" s="2"/>
+      <x:c r="A123" s="4" t="str">
+        <x:v>每个配置均有三题，均分等权。新增六项成本合计 8.670 USD；未提供 token 数，不倒推 token 或 FLOPs。</x:v>
+      </x:c>
+      <x:c r="B123" s="4"/>
+      <x:c r="C123" s="4"/>
+      <x:c r="D123" s="4"/>
+      <x:c r="E123" s="4"/>
+      <x:c r="F123" s="4"/>
+      <x:c r="G123" s="4"/>
+      <x:c r="H123" s="4"/>
+      <x:c r="I123" s="4"/>
+      <x:c r="J123" s="4"/>
+      <x:c r="K123" s="4"/>
       <x:c r="L123" s="2"/>
       <x:c r="M123" s="2"/>
       <x:c r="N123" s="2"/>
@@ -7397,40 +8311,20 @@
       <x:c r="U123" s="2"/>
       <x:c r="V123" s="2"/>
     </x:row>
-    <x:row r="124" ht="35" customHeight="1">
-      <x:c r="A124" s="69" t="str">
-        <x:v>模型配置</x:v>
-      </x:c>
-      <x:c r="B124" s="69" t="str">
-        <x:v>题目</x:v>
-      </x:c>
-      <x:c r="C124" s="69" t="str">
-        <x:v>定义 /15</x:v>
-      </x:c>
-      <x:c r="D124" s="69" t="str">
-        <x:v>校准 /30</x:v>
-      </x:c>
-      <x:c r="E124" s="69" t="str">
-        <x:v>验证 /15</x:v>
-      </x:c>
-      <x:c r="F124" s="69" t="str">
-        <x:v>推进 /30</x:v>
-      </x:c>
-      <x:c r="G124" s="69" t="str">
-        <x:v>结论 /10</x:v>
-      </x:c>
-      <x:c r="H124" s="69" t="str">
-        <x:v>总分 /100</x:v>
-      </x:c>
-      <x:c r="I124" s="69" t="str">
-        <x:v>评阅下限</x:v>
-      </x:c>
-      <x:c r="J124" s="69" t="str">
-        <x:v>评阅上限</x:v>
-      </x:c>
-      <x:c r="K124" s="69" t="str">
-        <x:v>采用编号</x:v>
-      </x:c>
+    <x:row r="124" ht="21" customHeight="1">
+      <x:c r="A124" s="4" t="str">
+        <x:v>Opus 三题采用补充报告评分，成本沿用原记录且各计一次；原始匿名答卷与评阅均保留。</x:v>
+      </x:c>
+      <x:c r="B124" s="4"/>
+      <x:c r="C124" s="4"/>
+      <x:c r="D124" s="4"/>
+      <x:c r="E124" s="4"/>
+      <x:c r="F124" s="4"/>
+      <x:c r="G124" s="4"/>
+      <x:c r="H124" s="4"/>
+      <x:c r="I124" s="4"/>
+      <x:c r="J124" s="4"/>
+      <x:c r="K124" s="4"/>
       <x:c r="L124" s="2"/>
       <x:c r="M124" s="2"/>
       <x:c r="N124" s="2"/>
@@ -7444,40 +8338,19 @@
       <x:c r="V124" s="2"/>
     </x:row>
     <x:row r="125" ht="21" customHeight="1">
-      <x:c r="A125" s="2" t="str">
-        <x:v>GPT-5.6 Sol xhigh</x:v>
-      </x:c>
-      <x:c r="B125" s="12" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C125" s="12" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D125" s="12" t="n">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="E125" s="12" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="F125" s="12" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="G125" s="12" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="H125" s="12" t="n">
-        <x:f>'Task 1'!D2</x:f>
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="I125" s="12" t="n">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="J125" s="12" t="n">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="K125" s="12" t="str">
-        <x:v>1a</x:v>
-      </x:c>
+      <x:c r="A125" s="4" t="str">
+        <x:v>每个模型—题目只有一份采用结果，交互轮次和工具预算未证明严格一致；结论限于本次测试材料。</x:v>
+      </x:c>
+      <x:c r="B125" s="4"/>
+      <x:c r="C125" s="4"/>
+      <x:c r="D125" s="4"/>
+      <x:c r="E125" s="4"/>
+      <x:c r="F125" s="4"/>
+      <x:c r="G125" s="4"/>
+      <x:c r="H125" s="4"/>
+      <x:c r="I125" s="4"/>
+      <x:c r="J125" s="4"/>
+      <x:c r="K125" s="4"/>
       <x:c r="L125" s="2"/>
       <x:c r="M125" s="2"/>
       <x:c r="N125" s="2"/>
@@ -7491,40 +8364,19 @@
       <x:c r="V125" s="2"/>
     </x:row>
     <x:row r="126" ht="21" customHeight="1">
-      <x:c r="A126" s="70" t="str">
-        <x:v>GPT-6 Astra high</x:v>
-      </x:c>
-      <x:c r="B126" s="71" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C126" s="71" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D126" s="71" t="n">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="E126" s="71" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="F126" s="71" t="n">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="G126" s="71" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="H126" s="71" t="n">
-        <x:f>'Task 1'!D3</x:f>
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="I126" s="71" t="n">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="J126" s="71" t="n">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="K126" s="71" t="str">
-        <x:v>1b</x:v>
-      </x:c>
+      <x:c r="A126" s="4" t="str">
+        <x:v>评阅区间非统计置信区间；6.1 max 与 xhigh 的小分差不足以证明稳定的总体能力差异。</x:v>
+      </x:c>
+      <x:c r="B126" s="4"/>
+      <x:c r="C126" s="4"/>
+      <x:c r="D126" s="4"/>
+      <x:c r="E126" s="4"/>
+      <x:c r="F126" s="4"/>
+      <x:c r="G126" s="4"/>
+      <x:c r="H126" s="4"/>
+      <x:c r="I126" s="4"/>
+      <x:c r="J126" s="4"/>
+      <x:c r="K126" s="4"/>
       <x:c r="L126" s="2"/>
       <x:c r="M126" s="2"/>
       <x:c r="N126" s="2"/>
@@ -7538,40 +8390,19 @@
       <x:c r="V126" s="2"/>
     </x:row>
     <x:row r="127" ht="21" customHeight="1">
-      <x:c r="A127" s="2" t="str">
-        <x:v>GPT-6 Sol xhigh</x:v>
-      </x:c>
-      <x:c r="B127" s="12" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C127" s="12" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D127" s="12" t="n">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="E127" s="12" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="F127" s="12" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="G127" s="12" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="H127" s="12" t="n">
-        <x:f>'Task 1'!D4</x:f>
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="I127" s="12" t="n">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="J127" s="12" t="n">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="K127" s="12" t="str">
-        <x:v>1c</x:v>
-      </x:c>
+      <x:c r="A127" s="4" t="str">
+        <x:v>评分按匿名编号开展；部分新增正文费用附录出现型号文字，未据此调分；同族隐性偏好仍可能存在。</x:v>
+      </x:c>
+      <x:c r="B127" s="4"/>
+      <x:c r="C127" s="4"/>
+      <x:c r="D127" s="4"/>
+      <x:c r="E127" s="4"/>
+      <x:c r="F127" s="4"/>
+      <x:c r="G127" s="4"/>
+      <x:c r="H127" s="4"/>
+      <x:c r="I127" s="4"/>
+      <x:c r="J127" s="4"/>
+      <x:c r="K127" s="4"/>
       <x:c r="L127" s="2"/>
       <x:c r="M127" s="2"/>
       <x:c r="N127" s="2"/>
@@ -7585,40 +8416,19 @@
       <x:c r="V127" s="2"/>
     </x:row>
     <x:row r="128" ht="21" customHeight="1">
-      <x:c r="A128" s="70" t="str">
-        <x:v>Grok 4.7 high</x:v>
-      </x:c>
-      <x:c r="B128" s="71" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C128" s="71" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D128" s="71" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="E128" s="71" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="F128" s="71" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="G128" s="71" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="H128" s="71" t="n">
-        <x:f>'Task 1'!D5</x:f>
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="I128" s="71" t="n">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="J128" s="71" t="n">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="K128" s="71" t="str">
-        <x:v>1d</x:v>
-      </x:c>
+      <x:c r="A128" s="4" t="str">
+        <x:v>参考成本沿用参与者记录，不等于订阅实付、推理时间或算力；总分 / USD 不具有科研价值倍数含义。</x:v>
+      </x:c>
+      <x:c r="B128" s="4"/>
+      <x:c r="C128" s="4"/>
+      <x:c r="D128" s="4"/>
+      <x:c r="E128" s="4"/>
+      <x:c r="F128" s="4"/>
+      <x:c r="G128" s="4"/>
+      <x:c r="H128" s="4"/>
+      <x:c r="I128" s="4"/>
+      <x:c r="J128" s="4"/>
+      <x:c r="K128" s="4"/>
       <x:c r="L128" s="2"/>
       <x:c r="M128" s="2"/>
       <x:c r="N128" s="2"/>
@@ -7632,40 +8442,19 @@
       <x:c r="V128" s="2"/>
     </x:row>
     <x:row r="129" ht="21" customHeight="1">
-      <x:c r="A129" s="2" t="str">
-        <x:v>Opus 5.5 xhigh</x:v>
-      </x:c>
-      <x:c r="B129" s="12" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C129" s="12" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D129" s="12" t="n">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="E129" s="12" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="F129" s="12" t="n">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="G129" s="12" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="H129" s="12" t="n">
-        <x:f>'Task 1'!D6</x:f>
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="I129" s="12" t="n">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="J129" s="12" t="n">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="K129" s="12" t="str">
-        <x:v>s_1a</x:v>
-      </x:c>
+      <x:c r="A129" s="4" t="str">
+        <x:v>原生图横轴为 log10(USD) 且采用本次成本快照；编辑费用后应重新生成。PNG/SVG 图含评阅范围。</x:v>
+      </x:c>
+      <x:c r="B129" s="4"/>
+      <x:c r="C129" s="4"/>
+      <x:c r="D129" s="4"/>
+      <x:c r="E129" s="4"/>
+      <x:c r="F129" s="4"/>
+      <x:c r="G129" s="4"/>
+      <x:c r="H129" s="4"/>
+      <x:c r="I129" s="4"/>
+      <x:c r="J129" s="4"/>
+      <x:c r="K129" s="4"/>
       <x:c r="L129" s="2"/>
       <x:c r="M129" s="2"/>
       <x:c r="N129" s="2"/>
@@ -7679,40 +8468,19 @@
       <x:c r="V129" s="2"/>
     </x:row>
     <x:row r="130" ht="21" customHeight="1">
-      <x:c r="A130" s="70" t="str">
-        <x:v>GPT-6 Sol max</x:v>
-      </x:c>
-      <x:c r="B130" s="71" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C130" s="71" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D130" s="71" t="n">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="E130" s="71" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="F130" s="71" t="n">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="G130" s="71" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="H130" s="71" t="n">
-        <x:f>'Task 1'!D7</x:f>
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="I130" s="71" t="n">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="J130" s="71" t="n">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="K130" s="71" t="str">
-        <x:v>s_1b</x:v>
-      </x:c>
+      <x:c r="A130" s="4" t="str">
+        <x:v>来源：评分细则、三批 q1/q2/q3 评阅报告、第二轮补充评分明细，以及参与者确认的费用映射。</x:v>
+      </x:c>
+      <x:c r="B130" s="4"/>
+      <x:c r="C130" s="4"/>
+      <x:c r="D130" s="4"/>
+      <x:c r="E130" s="4"/>
+      <x:c r="F130" s="4"/>
+      <x:c r="G130" s="4"/>
+      <x:c r="H130" s="4"/>
+      <x:c r="I130" s="4"/>
+      <x:c r="J130" s="4"/>
+      <x:c r="K130" s="4"/>
       <x:c r="L130" s="2"/>
       <x:c r="M130" s="2"/>
       <x:c r="N130" s="2"/>
@@ -7726,40 +8494,19 @@
       <x:c r="V130" s="2"/>
     </x:row>
     <x:row r="131" ht="21" customHeight="1">
-      <x:c r="A131" s="2" t="str">
-        <x:v>GPT-6 Luna max</x:v>
-      </x:c>
-      <x:c r="B131" s="12" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C131" s="12" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D131" s="12" t="n">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="E131" s="12" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="F131" s="12" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="G131" s="12" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="H131" s="12" t="n">
-        <x:f>'Task 1'!D8</x:f>
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="I131" s="12" t="n">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="J131" s="12" t="n">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="K131" s="12" t="str">
-        <x:v>s_1c</x:v>
-      </x:c>
+      <x:c r="A131" s="4" t="str">
+        <x:v>项目与来源：https://github.com/Zhen-WushuiLingchun/math_physics_ai_benchmark_v1</x:v>
+      </x:c>
+      <x:c r="B131" s="4"/>
+      <x:c r="C131" s="4"/>
+      <x:c r="D131" s="4"/>
+      <x:c r="E131" s="4"/>
+      <x:c r="F131" s="4"/>
+      <x:c r="G131" s="4"/>
+      <x:c r="H131" s="4"/>
+      <x:c r="I131" s="4"/>
+      <x:c r="J131" s="4"/>
+      <x:c r="K131" s="4"/>
       <x:c r="L131" s="2"/>
       <x:c r="M131" s="2"/>
       <x:c r="N131" s="2"/>
@@ -7773,40 +8520,17 @@
       <x:c r="V131" s="2"/>
     </x:row>
     <x:row r="132" ht="21" customHeight="1">
-      <x:c r="A132" s="70" t="str">
-        <x:v>DeepSeek V4.1 Flash max</x:v>
-      </x:c>
-      <x:c r="B132" s="71" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C132" s="71" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D132" s="71" t="n">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="E132" s="71" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="F132" s="71" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="G132" s="71" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="H132" s="71" t="n">
-        <x:f>'Task 1'!D9</x:f>
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="I132" s="71" t="n">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="J132" s="71" t="n">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="K132" s="71" t="str">
-        <x:v>s_1d</x:v>
-      </x:c>
+      <x:c r="A132" s="2"/>
+      <x:c r="B132" s="2"/>
+      <x:c r="C132" s="2"/>
+      <x:c r="D132" s="2"/>
+      <x:c r="E132" s="2"/>
+      <x:c r="F132" s="2"/>
+      <x:c r="G132" s="2"/>
+      <x:c r="H132" s="2"/>
+      <x:c r="I132" s="2"/>
+      <x:c r="J132" s="2"/>
+      <x:c r="K132" s="2"/>
       <x:c r="L132" s="2"/>
       <x:c r="M132" s="2"/>
       <x:c r="N132" s="2"/>
@@ -7821,39 +8545,21 @@
     </x:row>
     <x:row r="133" ht="21" customHeight="1">
       <x:c r="A133" s="2" t="str">
-        <x:v>GPT-5.6 Sol xhigh</x:v>
-      </x:c>
-      <x:c r="B133" s="12" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C133" s="12" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="D133" s="12" t="n">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="E133" s="12" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="F133" s="12" t="n">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="G133" s="12" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="H133" s="12" t="n">
-        <x:f>'Task 2'!D2</x:f>
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="I133" s="12" t="n">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="J133" s="12" t="n">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="K133" s="12" t="str">
-        <x:v>2a</x:v>
-      </x:c>
+        <x:v>本表 30 项采用结果的记录成本 USD</x:v>
+      </x:c>
+      <x:c r="B133" s="2"/>
+      <x:c r="C133" s="2"/>
+      <x:c r="D133" s="2"/>
+      <x:c r="E133" s="40" t="n">
+        <x:f>SUM('Task 1'!C2:C11,'Task 2'!C2:C11,'Task 3'!C2:C11)</x:f>
+        <x:v>125.51200000000001</x:v>
+      </x:c>
+      <x:c r="F133" s="2"/>
+      <x:c r="G133" s="2"/>
+      <x:c r="H133" s="2"/>
+      <x:c r="I133" s="2"/>
+      <x:c r="J133" s="2"/>
+      <x:c r="K133" s="2"/>
       <x:c r="L133" s="2"/>
       <x:c r="M133" s="2"/>
       <x:c r="N133" s="2"/>
@@ -7867,40 +8573,17 @@
       <x:c r="V133" s="2"/>
     </x:row>
     <x:row r="134" ht="21" customHeight="1">
-      <x:c r="A134" s="70" t="str">
-        <x:v>GPT-6 Luna max</x:v>
-      </x:c>
-      <x:c r="B134" s="71" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C134" s="71" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="D134" s="71" t="n">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="E134" s="71" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="F134" s="71" t="n">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="G134" s="71" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="H134" s="71" t="n">
-        <x:f>'Task 2'!D3</x:f>
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="I134" s="71" t="n">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="J134" s="71" t="n">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="K134" s="71" t="str">
-        <x:v>2b</x:v>
-      </x:c>
+      <x:c r="A134" s="2"/>
+      <x:c r="B134" s="2"/>
+      <x:c r="C134" s="2"/>
+      <x:c r="D134" s="2"/>
+      <x:c r="E134" s="2"/>
+      <x:c r="F134" s="2"/>
+      <x:c r="G134" s="2"/>
+      <x:c r="H134" s="2"/>
+      <x:c r="I134" s="2"/>
+      <x:c r="J134" s="2"/>
+      <x:c r="K134" s="2"/>
       <x:c r="L134" s="2"/>
       <x:c r="M134" s="2"/>
       <x:c r="N134" s="2"/>
@@ -7913,41 +8596,20 @@
       <x:c r="U134" s="2"/>
       <x:c r="V134" s="2"/>
     </x:row>
-    <x:row r="135" ht="21" customHeight="1">
-      <x:c r="A135" s="2" t="str">
-        <x:v>GPT-6 Sol max</x:v>
-      </x:c>
-      <x:c r="B135" s="12" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C135" s="12" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="D135" s="12" t="n">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="E135" s="12" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F135" s="12" t="n">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="G135" s="12" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="H135" s="12" t="n">
-        <x:f>'Task 2'!D4</x:f>
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="I135" s="12" t="n">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="J135" s="12" t="n">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="K135" s="12" t="str">
-        <x:v>2c</x:v>
-      </x:c>
+    <x:row r="135" ht="24" customHeight="1">
+      <x:c r="A135" s="27" t="str">
+        <x:v>逐份回答：五维评分、评阅范围与溯源</x:v>
+      </x:c>
+      <x:c r="B135" s="27"/>
+      <x:c r="C135" s="27"/>
+      <x:c r="D135" s="27"/>
+      <x:c r="E135" s="27"/>
+      <x:c r="F135" s="27"/>
+      <x:c r="G135" s="27"/>
+      <x:c r="H135" s="27"/>
+      <x:c r="I135" s="27"/>
+      <x:c r="J135" s="27"/>
+      <x:c r="K135" s="27"/>
       <x:c r="L135" s="2"/>
       <x:c r="M135" s="2"/>
       <x:c r="N135" s="2"/>
@@ -7961,40 +8623,17 @@
       <x:c r="V135" s="2"/>
     </x:row>
     <x:row r="136" ht="21" customHeight="1">
-      <x:c r="A136" s="70" t="str">
-        <x:v>GPT-6 Sol xhigh</x:v>
-      </x:c>
-      <x:c r="B136" s="71" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C136" s="71" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="D136" s="71" t="n">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="E136" s="71" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="F136" s="71" t="n">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="G136" s="71" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="H136" s="71" t="n">
-        <x:f>'Task 2'!D5</x:f>
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="I136" s="71" t="n">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="J136" s="71" t="n">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="K136" s="71" t="str">
-        <x:v>2d</x:v>
-      </x:c>
+      <x:c r="A136" s="2"/>
+      <x:c r="B136" s="2"/>
+      <x:c r="C136" s="2"/>
+      <x:c r="D136" s="2"/>
+      <x:c r="E136" s="2"/>
+      <x:c r="F136" s="2"/>
+      <x:c r="G136" s="2"/>
+      <x:c r="H136" s="2"/>
+      <x:c r="I136" s="2"/>
+      <x:c r="J136" s="2"/>
+      <x:c r="K136" s="2"/>
       <x:c r="L136" s="2"/>
       <x:c r="M136" s="2"/>
       <x:c r="N136" s="2"/>
@@ -8007,40 +8646,39 @@
       <x:c r="U136" s="2"/>
       <x:c r="V136" s="2"/>
     </x:row>
-    <x:row r="137" ht="21" customHeight="1">
-      <x:c r="A137" s="2" t="str">
-        <x:v>GPT-6 Astra high</x:v>
-      </x:c>
-      <x:c r="B137" s="12" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C137" s="12" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="D137" s="12" t="n">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="E137" s="12" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F137" s="12" t="n">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="G137" s="12" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="H137" s="12" t="n">
-        <x:f>'Task 2'!D6</x:f>
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="I137" s="12" t="n">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="J137" s="12" t="n">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="K137" s="12" t="str">
-        <x:v>2e</x:v>
+    <x:row r="137" ht="35" customHeight="1">
+      <x:c r="A137" s="120" t="str">
+        <x:v>模型配置</x:v>
+      </x:c>
+      <x:c r="B137" s="120" t="str">
+        <x:v>题目</x:v>
+      </x:c>
+      <x:c r="C137" s="120" t="str">
+        <x:v>定义 /15</x:v>
+      </x:c>
+      <x:c r="D137" s="120" t="str">
+        <x:v>校准 /30</x:v>
+      </x:c>
+      <x:c r="E137" s="120" t="str">
+        <x:v>验证 /15</x:v>
+      </x:c>
+      <x:c r="F137" s="120" t="str">
+        <x:v>推进 /30</x:v>
+      </x:c>
+      <x:c r="G137" s="120" t="str">
+        <x:v>结论 /10</x:v>
+      </x:c>
+      <x:c r="H137" s="120" t="str">
+        <x:v>总分 /100</x:v>
+      </x:c>
+      <x:c r="I137" s="120" t="str">
+        <x:v>评阅下限</x:v>
+      </x:c>
+      <x:c r="J137" s="120" t="str">
+        <x:v>评阅上限</x:v>
+      </x:c>
+      <x:c r="K137" s="120" t="str">
+        <x:v>采用编号</x:v>
       </x:c>
       <x:c r="L137" s="2"/>
       <x:c r="M137" s="2"/>
@@ -8055,39 +8693,39 @@
       <x:c r="V137" s="2"/>
     </x:row>
     <x:row r="138" ht="21" customHeight="1">
-      <x:c r="A138" s="70" t="str">
-        <x:v>Grok 4.7 high</x:v>
-      </x:c>
-      <x:c r="B138" s="71" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C138" s="71" t="n">
+      <x:c r="A138" s="2" t="str">
+        <x:v>GPT-5.6 Sol xhigh</x:v>
+      </x:c>
+      <x:c r="B138" s="12" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C138" s="12" t="n">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="D138" s="71" t="n">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="E138" s="71" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="F138" s="71" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="G138" s="71" t="n">
+      <x:c r="D138" s="12" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="E138" s="12" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="F138" s="12" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="G138" s="12" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="H138" s="71" t="n">
-        <x:f>'Task 2'!D7</x:f>
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="I138" s="71" t="n">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="J138" s="71" t="n">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="K138" s="71" t="str">
-        <x:v>2f</x:v>
+      <x:c r="H138" s="12" t="n">
+        <x:f>'Task 1'!D2</x:f>
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="I138" s="12" t="n">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="J138" s="12" t="n">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="K138" s="12" t="str">
+        <x:v>1a</x:v>
       </x:c>
       <x:c r="L138" s="2"/>
       <x:c r="M138" s="2"/>
@@ -8102,39 +8740,39 @@
       <x:c r="V138" s="2"/>
     </x:row>
     <x:row r="139" ht="21" customHeight="1">
-      <x:c r="A139" s="2" t="str">
-        <x:v>Opus 5.5 xhigh</x:v>
-      </x:c>
-      <x:c r="B139" s="12" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C139" s="12" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="D139" s="12" t="n">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="E139" s="12" t="n">
+      <x:c r="A139" s="121" t="str">
+        <x:v>GPT-6 Astra high</x:v>
+      </x:c>
+      <x:c r="B139" s="122" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C139" s="122" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="D139" s="122" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E139" s="122" t="n">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="F139" s="12" t="n">
+      <x:c r="F139" s="122" t="n">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="G139" s="12" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="H139" s="12" t="n">
-        <x:f>'Task 2'!D8</x:f>
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="I139" s="12" t="n">
+      <x:c r="G139" s="122" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="H139" s="122" t="n">
+        <x:f>'Task 1'!D3</x:f>
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="I139" s="122" t="n">
         <x:v>88</x:v>
       </x:c>
-      <x:c r="J139" s="12" t="n">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="K139" s="12" t="str">
-        <x:v>s_2a</x:v>
+      <x:c r="J139" s="122" t="n">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="K139" s="122" t="str">
+        <x:v>1b</x:v>
       </x:c>
       <x:c r="L139" s="2"/>
       <x:c r="M139" s="2"/>
@@ -8149,39 +8787,39 @@
       <x:c r="V139" s="2"/>
     </x:row>
     <x:row r="140" ht="21" customHeight="1">
-      <x:c r="A140" s="70" t="str">
-        <x:v>DeepSeek V4.1 Flash max</x:v>
-      </x:c>
-      <x:c r="B140" s="71" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C140" s="71" t="n">
+      <x:c r="A140" s="2" t="str">
+        <x:v>GPT-6 Sol xhigh</x:v>
+      </x:c>
+      <x:c r="B140" s="12" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C140" s="12" t="n">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="D140" s="71" t="n">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="E140" s="71" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="F140" s="71" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="G140" s="71" t="n">
+      <x:c r="D140" s="12" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="E140" s="12" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F140" s="12" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="G140" s="12" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="H140" s="71" t="n">
-        <x:f>'Task 2'!D9</x:f>
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="I140" s="71" t="n">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="J140" s="71" t="n">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="K140" s="71" t="str">
-        <x:v>s_2b</x:v>
+      <x:c r="H140" s="12" t="n">
+        <x:f>'Task 1'!D4</x:f>
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="I140" s="12" t="n">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="J140" s="12" t="n">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="K140" s="12" t="str">
+        <x:v>1c</x:v>
       </x:c>
       <x:c r="L140" s="2"/>
       <x:c r="M140" s="2"/>
@@ -8196,39 +8834,39 @@
       <x:c r="V140" s="2"/>
     </x:row>
     <x:row r="141" ht="21" customHeight="1">
-      <x:c r="A141" s="2" t="str">
-        <x:v>GPT-5.6 Sol xhigh</x:v>
-      </x:c>
-      <x:c r="B141" s="12" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C141" s="12" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D141" s="12" t="n">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="E141" s="12" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="F141" s="12" t="n">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="G141" s="12" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="H141" s="12" t="n">
-        <x:f>'Task 3'!D2</x:f>
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="I141" s="12" t="n">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="J141" s="12" t="n">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="K141" s="12" t="str">
-        <x:v>3a</x:v>
+      <x:c r="A141" s="121" t="str">
+        <x:v>Grok 4.7 high</x:v>
+      </x:c>
+      <x:c r="B141" s="122" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C141" s="122" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D141" s="122" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="E141" s="122" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="F141" s="122" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G141" s="122" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="H141" s="122" t="n">
+        <x:f>'Task 1'!D5</x:f>
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="I141" s="122" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="J141" s="122" t="n">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="K141" s="122" t="str">
+        <x:v>1d</x:v>
       </x:c>
       <x:c r="L141" s="2"/>
       <x:c r="M141" s="2"/>
@@ -8243,39 +8881,39 @@
       <x:c r="V141" s="2"/>
     </x:row>
     <x:row r="142" ht="21" customHeight="1">
-      <x:c r="A142" s="70" t="str">
-        <x:v>GPT-6 Luna max</x:v>
-      </x:c>
-      <x:c r="B142" s="71" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C142" s="71" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="D142" s="71" t="n">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="E142" s="71" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="F142" s="71" t="n">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="G142" s="71" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="H142" s="71" t="n">
-        <x:f>'Task 3'!D3</x:f>
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="I142" s="71" t="n">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="J142" s="71" t="n">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="K142" s="71" t="str">
-        <x:v>3b</x:v>
+      <x:c r="A142" s="2" t="str">
+        <x:v>Opus 5.5 xhigh</x:v>
+      </x:c>
+      <x:c r="B142" s="12" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C142" s="12" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="D142" s="12" t="n">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E142" s="12" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="F142" s="12" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="G142" s="12" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="H142" s="12" t="n">
+        <x:f>'Task 1'!D6</x:f>
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="I142" s="12" t="n">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="J142" s="12" t="n">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="K142" s="12" t="str">
+        <x:v>s_1a</x:v>
       </x:c>
       <x:c r="L142" s="2"/>
       <x:c r="M142" s="2"/>
@@ -8290,39 +8928,39 @@
       <x:c r="V142" s="2"/>
     </x:row>
     <x:row r="143" ht="21" customHeight="1">
-      <x:c r="A143" s="2" t="str">
+      <x:c r="A143" s="121" t="str">
         <x:v>GPT-6 Sol max</x:v>
       </x:c>
-      <x:c r="B143" s="12" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C143" s="12" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="D143" s="12" t="n">
+      <x:c r="B143" s="122" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C143" s="122" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="D143" s="122" t="n">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="E143" s="12" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="F143" s="12" t="n">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="G143" s="12" t="n">
+      <x:c r="E143" s="122" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="F143" s="122" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="G143" s="122" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="H143" s="12" t="n">
-        <x:f>'Task 3'!D4</x:f>
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="I143" s="12" t="n">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="J143" s="12" t="n">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="K143" s="12" t="str">
-        <x:v>3c</x:v>
+      <x:c r="H143" s="122" t="n">
+        <x:f>'Task 1'!D7</x:f>
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="I143" s="122" t="n">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="J143" s="122" t="n">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="K143" s="122" t="str">
+        <x:v>s_1b</x:v>
       </x:c>
       <x:c r="L143" s="2"/>
       <x:c r="M143" s="2"/>
@@ -8337,39 +8975,39 @@
       <x:c r="V143" s="2"/>
     </x:row>
     <x:row r="144" ht="21" customHeight="1">
-      <x:c r="A144" s="70" t="str">
-        <x:v>GPT-6 Sol xhigh</x:v>
-      </x:c>
-      <x:c r="B144" s="71" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C144" s="71" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="D144" s="71" t="n">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="E144" s="71" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="F144" s="71" t="n">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="G144" s="71" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="H144" s="71" t="n">
-        <x:f>'Task 3'!D5</x:f>
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="I144" s="71" t="n">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="J144" s="71" t="n">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="K144" s="71" t="str">
-        <x:v>3d</x:v>
+      <x:c r="A144" s="2" t="str">
+        <x:v>GPT-6 Luna max</x:v>
+      </x:c>
+      <x:c r="B144" s="12" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C144" s="12" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="D144" s="12" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="E144" s="12" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F144" s="12" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="G144" s="12" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="H144" s="12" t="n">
+        <x:f>'Task 1'!D8</x:f>
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="I144" s="12" t="n">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="J144" s="12" t="n">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="K144" s="12" t="str">
+        <x:v>s_1c</x:v>
       </x:c>
       <x:c r="L144" s="2"/>
       <x:c r="M144" s="2"/>
@@ -8384,39 +9022,39 @@
       <x:c r="V144" s="2"/>
     </x:row>
     <x:row r="145" ht="21" customHeight="1">
-      <x:c r="A145" s="2" t="str">
-        <x:v>GPT-6 Astra high</x:v>
-      </x:c>
-      <x:c r="B145" s="12" t="n">
+      <x:c r="A145" s="121" t="str">
+        <x:v>DeepSeek V4.1 Flash max</x:v>
+      </x:c>
+      <x:c r="B145" s="122" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C145" s="122" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="D145" s="122" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="E145" s="122" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F145" s="122" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="G145" s="122" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C145" s="12" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="D145" s="12" t="n">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="E145" s="12" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F145" s="12" t="n">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="G145" s="12" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="H145" s="12" t="n">
-        <x:f>'Task 3'!D6</x:f>
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="I145" s="12" t="n">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="J145" s="12" t="n">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="K145" s="12" t="str">
-        <x:v>3e</x:v>
+      <x:c r="H145" s="122" t="n">
+        <x:f>'Task 1'!D9</x:f>
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="I145" s="122" t="n">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="J145" s="122" t="n">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="K145" s="122" t="str">
+        <x:v>s_1d</x:v>
       </x:c>
       <x:c r="L145" s="2"/>
       <x:c r="M145" s="2"/>
@@ -8431,39 +9069,39 @@
       <x:c r="V145" s="2"/>
     </x:row>
     <x:row r="146" ht="21" customHeight="1">
-      <x:c r="A146" s="70" t="str">
-        <x:v>Grok 4.7 high</x:v>
-      </x:c>
-      <x:c r="B146" s="71" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C146" s="71" t="n">
+      <x:c r="A146" s="2" t="str">
+        <x:v>GPT-6.1 Sol xhigh</x:v>
+      </x:c>
+      <x:c r="B146" s="12" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C146" s="12" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D146" s="12" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="E146" s="12" t="n">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="D146" s="71" t="n">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="E146" s="71" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="F146" s="71" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="G146" s="71" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="H146" s="71" t="n">
-        <x:f>'Task 3'!D7</x:f>
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="I146" s="71" t="n">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="J146" s="71" t="n">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="K146" s="71" t="str">
-        <x:v>3f</x:v>
+      <x:c r="F146" s="12" t="n">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="G146" s="12" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="H146" s="12" t="n">
+        <x:f>'Task 1'!D10</x:f>
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="I146" s="12" t="n">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="J146" s="12" t="n">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="K146" s="12" t="str">
+        <x:v>s2_1a</x:v>
       </x:c>
       <x:c r="L146" s="2"/>
       <x:c r="M146" s="2"/>
@@ -8478,39 +9116,39 @@
       <x:c r="V146" s="2"/>
     </x:row>
     <x:row r="147" ht="21" customHeight="1">
-      <x:c r="A147" s="2" t="str">
-        <x:v>Opus 5.5 xhigh</x:v>
-      </x:c>
-      <x:c r="B147" s="12" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C147" s="12" t="n">
+      <x:c r="A147" s="121" t="str">
+        <x:v>GPT-6.1 Sol max</x:v>
+      </x:c>
+      <x:c r="B147" s="122" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C147" s="122" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D147" s="122" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="E147" s="122" t="n">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="D147" s="12" t="n">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="E147" s="12" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F147" s="12" t="n">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="G147" s="12" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="H147" s="12" t="n">
-        <x:f>'Task 3'!D8</x:f>
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="I147" s="12" t="n">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="J147" s="12" t="n">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="K147" s="12" t="str">
-        <x:v>s_3a</x:v>
+      <x:c r="F147" s="122" t="n">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="G147" s="122" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="H147" s="122" t="n">
+        <x:f>'Task 1'!D11</x:f>
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="I147" s="122" t="n">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="J147" s="122" t="n">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="K147" s="122" t="str">
+        <x:v>s2_1b</x:v>
       </x:c>
       <x:c r="L147" s="2"/>
       <x:c r="M147" s="2"/>
@@ -8525,39 +9163,39 @@
       <x:c r="V147" s="2"/>
     </x:row>
     <x:row r="148" ht="21" customHeight="1">
-      <x:c r="A148" s="72" t="str">
-        <x:v>DeepSeek V4.1 Flash max</x:v>
-      </x:c>
-      <x:c r="B148" s="73" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C148" s="73" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D148" s="73" t="n">
+      <x:c r="A148" s="2" t="str">
+        <x:v>GPT-5.6 Sol xhigh</x:v>
+      </x:c>
+      <x:c r="B148" s="12" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C148" s="12" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D148" s="12" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="E148" s="12" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="F148" s="12" t="n">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="E148" s="73" t="n">
+      <x:c r="G148" s="12" t="n">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="F148" s="73" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="G148" s="73" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="H148" s="73" t="n">
-        <x:f>'Task 3'!D9</x:f>
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="I148" s="73" t="n">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="J148" s="73" t="n">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="K148" s="73" t="str">
-        <x:v>s_3b</x:v>
+      <x:c r="H148" s="12" t="n">
+        <x:f>'Task 2'!D2</x:f>
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="I148" s="12" t="n">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="J148" s="12" t="n">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="K148" s="12" t="str">
+        <x:v>2a</x:v>
       </x:c>
       <x:c r="L148" s="2"/>
       <x:c r="M148" s="2"/>
@@ -8572,17 +9210,40 @@
       <x:c r="V148" s="2"/>
     </x:row>
     <x:row r="149" ht="21" customHeight="1">
-      <x:c r="A149" s="2"/>
-      <x:c r="B149" s="2"/>
-      <x:c r="C149" s="2"/>
-      <x:c r="D149" s="2"/>
-      <x:c r="E149" s="2"/>
-      <x:c r="F149" s="2"/>
-      <x:c r="G149" s="2"/>
-      <x:c r="H149" s="2"/>
-      <x:c r="I149" s="2"/>
-      <x:c r="J149" s="2"/>
-      <x:c r="K149" s="2"/>
+      <x:c r="A149" s="121" t="str">
+        <x:v>GPT-6 Luna max</x:v>
+      </x:c>
+      <x:c r="B149" s="122" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C149" s="122" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D149" s="122" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="E149" s="122" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="F149" s="122" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="G149" s="122" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="H149" s="122" t="n">
+        <x:f>'Task 2'!D3</x:f>
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="I149" s="122" t="n">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="J149" s="122" t="n">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="K149" s="122" t="str">
+        <x:v>2b</x:v>
+      </x:c>
       <x:c r="L149" s="2"/>
       <x:c r="M149" s="2"/>
       <x:c r="N149" s="2"/>
@@ -8596,17 +9257,40 @@
       <x:c r="V149" s="2"/>
     </x:row>
     <x:row r="150" ht="21" customHeight="1">
-      <x:c r="A150" s="2"/>
-      <x:c r="B150" s="2"/>
-      <x:c r="C150" s="2"/>
-      <x:c r="D150" s="2"/>
-      <x:c r="E150" s="2"/>
-      <x:c r="F150" s="2"/>
-      <x:c r="G150" s="2"/>
-      <x:c r="H150" s="2"/>
-      <x:c r="I150" s="2"/>
-      <x:c r="J150" s="2"/>
-      <x:c r="K150" s="2"/>
+      <x:c r="A150" s="2" t="str">
+        <x:v>GPT-6 Sol max</x:v>
+      </x:c>
+      <x:c r="B150" s="12" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C150" s="12" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D150" s="12" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="E150" s="12" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F150" s="12" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="G150" s="12" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="H150" s="12" t="n">
+        <x:f>'Task 2'!D4</x:f>
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="I150" s="12" t="n">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="J150" s="12" t="n">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="K150" s="12" t="str">
+        <x:v>2c</x:v>
+      </x:c>
       <x:c r="L150" s="2"/>
       <x:c r="M150" s="2"/>
       <x:c r="N150" s="2"/>
@@ -8619,20 +9303,41 @@
       <x:c r="U150" s="2"/>
       <x:c r="V150" s="2"/>
     </x:row>
-    <x:row r="151" ht="24" customHeight="1">
-      <x:c r="A151" s="27" t="str">
-        <x:v>本次完整样本的模型评价</x:v>
-      </x:c>
-      <x:c r="B151" s="27"/>
-      <x:c r="C151" s="27"/>
-      <x:c r="D151" s="27"/>
-      <x:c r="E151" s="27"/>
-      <x:c r="F151" s="27"/>
-      <x:c r="G151" s="27"/>
-      <x:c r="H151" s="27"/>
-      <x:c r="I151" s="27"/>
-      <x:c r="J151" s="27"/>
-      <x:c r="K151" s="27"/>
+    <x:row r="151" ht="21" customHeight="1">
+      <x:c r="A151" s="121" t="str">
+        <x:v>GPT-6 Sol xhigh</x:v>
+      </x:c>
+      <x:c r="B151" s="122" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C151" s="122" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D151" s="122" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="E151" s="122" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="F151" s="122" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="G151" s="122" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="H151" s="122" t="n">
+        <x:f>'Task 2'!D5</x:f>
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="I151" s="122" t="n">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="J151" s="122" t="n">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="K151" s="122" t="str">
+        <x:v>2d</x:v>
+      </x:c>
       <x:c r="L151" s="2"/>
       <x:c r="M151" s="2"/>
       <x:c r="N151" s="2"/>
@@ -8646,17 +9351,40 @@
       <x:c r="V151" s="2"/>
     </x:row>
     <x:row r="152" ht="21" customHeight="1">
-      <x:c r="A152" s="2"/>
-      <x:c r="B152" s="2"/>
-      <x:c r="C152" s="2"/>
-      <x:c r="D152" s="2"/>
-      <x:c r="E152" s="2"/>
-      <x:c r="F152" s="2"/>
-      <x:c r="G152" s="2"/>
-      <x:c r="H152" s="2"/>
-      <x:c r="I152" s="2"/>
-      <x:c r="J152" s="2"/>
-      <x:c r="K152" s="2"/>
+      <x:c r="A152" s="2" t="str">
+        <x:v>GPT-6 Astra high</x:v>
+      </x:c>
+      <x:c r="B152" s="12" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C152" s="12" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D152" s="12" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="E152" s="12" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F152" s="12" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="G152" s="12" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="H152" s="12" t="n">
+        <x:f>'Task 2'!D6</x:f>
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="I152" s="12" t="n">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="J152" s="12" t="n">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="K152" s="12" t="str">
+        <x:v>2e</x:v>
+      </x:c>
       <x:c r="L152" s="2"/>
       <x:c r="M152" s="2"/>
       <x:c r="N152" s="2"/>
@@ -8670,19 +9398,40 @@
       <x:c r="V152" s="2"/>
     </x:row>
     <x:row r="153" ht="21" customHeight="1">
-      <x:c r="A153" s="4" t="str">
-        <x:v>GPT-6 Astra high：总分 287、均分 95.67；三题均强，临界窗反向界与全时间统一稳定性界最突出。</x:v>
-      </x:c>
-      <x:c r="B153" s="4"/>
-      <x:c r="C153" s="4"/>
-      <x:c r="D153" s="4"/>
-      <x:c r="E153" s="4"/>
-      <x:c r="F153" s="4"/>
-      <x:c r="G153" s="4"/>
-      <x:c r="H153" s="4"/>
-      <x:c r="I153" s="4"/>
-      <x:c r="J153" s="4"/>
-      <x:c r="K153" s="4"/>
+      <x:c r="A153" s="121" t="str">
+        <x:v>Grok 4.7 high</x:v>
+      </x:c>
+      <x:c r="B153" s="122" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C153" s="122" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="D153" s="122" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="E153" s="122" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="F153" s="122" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="G153" s="122" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="H153" s="122" t="n">
+        <x:f>'Task 2'!D7</x:f>
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="I153" s="122" t="n">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="J153" s="122" t="n">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="K153" s="122" t="str">
+        <x:v>2f</x:v>
+      </x:c>
       <x:c r="L153" s="2"/>
       <x:c r="M153" s="2"/>
       <x:c r="N153" s="2"/>
@@ -8696,19 +9445,40 @@
       <x:c r="V153" s="2"/>
     </x:row>
     <x:row r="154" ht="21" customHeight="1">
-      <x:c r="A154" s="4" t="str">
-        <x:v>GPT-6 Sol max：总分 283、均分 94.33；题 1 最高，三题均 ≥94，成本比 Astra 低 42.6%。</x:v>
-      </x:c>
-      <x:c r="B154" s="4"/>
-      <x:c r="C154" s="4"/>
-      <x:c r="D154" s="4"/>
-      <x:c r="E154" s="4"/>
-      <x:c r="F154" s="4"/>
-      <x:c r="G154" s="4"/>
-      <x:c r="H154" s="4"/>
-      <x:c r="I154" s="4"/>
-      <x:c r="J154" s="4"/>
-      <x:c r="K154" s="4"/>
+      <x:c r="A154" s="2" t="str">
+        <x:v>Opus 5.5 xhigh</x:v>
+      </x:c>
+      <x:c r="B154" s="12" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C154" s="12" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D154" s="12" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="E154" s="12" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="F154" s="12" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="G154" s="12" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="H154" s="12" t="n">
+        <x:f>'Task 2'!D8</x:f>
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="I154" s="12" t="n">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="J154" s="12" t="n">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="K154" s="12" t="str">
+        <x:v>s_2a</x:v>
+      </x:c>
       <x:c r="L154" s="2"/>
       <x:c r="M154" s="2"/>
       <x:c r="N154" s="2"/>
@@ -8722,19 +9492,40 @@
       <x:c r="V154" s="2"/>
     </x:row>
     <x:row r="155" ht="21" customHeight="1">
-      <x:c r="A155" s="4" t="str">
-        <x:v>Opus 5.5 xhigh：总分 261、均分 87.00；有价值的解析归约，部分一般化与最优指数主张缺少充分证明。</x:v>
-      </x:c>
-      <x:c r="B155" s="4"/>
-      <x:c r="C155" s="4"/>
-      <x:c r="D155" s="4"/>
-      <x:c r="E155" s="4"/>
-      <x:c r="F155" s="4"/>
-      <x:c r="G155" s="4"/>
-      <x:c r="H155" s="4"/>
-      <x:c r="I155" s="4"/>
-      <x:c r="J155" s="4"/>
-      <x:c r="K155" s="4"/>
+      <x:c r="A155" s="121" t="str">
+        <x:v>DeepSeek V4.1 Flash max</x:v>
+      </x:c>
+      <x:c r="B155" s="122" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C155" s="122" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="D155" s="122" t="n">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E155" s="122" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="F155" s="122" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G155" s="122" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="H155" s="122" t="n">
+        <x:f>'Task 2'!D9</x:f>
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="I155" s="122" t="n">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="J155" s="122" t="n">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="K155" s="122" t="str">
+        <x:v>s_2b</x:v>
+      </x:c>
       <x:c r="L155" s="2"/>
       <x:c r="M155" s="2"/>
       <x:c r="N155" s="2"/>
@@ -8748,19 +9539,40 @@
       <x:c r="V155" s="2"/>
     </x:row>
     <x:row r="156" ht="21" customHeight="1">
-      <x:c r="A156" s="4" t="str">
-        <x:v>GPT-6 Sol xhigh：总分 236、均分 78.67；题 2/3 较强，题 1 的关键输入错号进入不可解性证书。</x:v>
-      </x:c>
-      <x:c r="B156" s="4"/>
-      <x:c r="C156" s="4"/>
-      <x:c r="D156" s="4"/>
-      <x:c r="E156" s="4"/>
-      <x:c r="F156" s="4"/>
-      <x:c r="G156" s="4"/>
-      <x:c r="H156" s="4"/>
-      <x:c r="I156" s="4"/>
-      <x:c r="J156" s="4"/>
-      <x:c r="K156" s="4"/>
+      <x:c r="A156" s="2" t="str">
+        <x:v>GPT-6.1 Sol xhigh</x:v>
+      </x:c>
+      <x:c r="B156" s="12" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C156" s="12" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D156" s="12" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="E156" s="12" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F156" s="12" t="n">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="G156" s="12" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="H156" s="12" t="n">
+        <x:f>'Task 2'!D10</x:f>
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="I156" s="12" t="n">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="J156" s="12" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="K156" s="12" t="str">
+        <x:v>s2_2a</x:v>
+      </x:c>
       <x:c r="L156" s="2"/>
       <x:c r="M156" s="2"/>
       <x:c r="N156" s="2"/>
@@ -8774,19 +9586,40 @@
       <x:c r="V156" s="2"/>
     </x:row>
     <x:row r="157" ht="21" customHeight="1">
-      <x:c r="A157" s="4" t="str">
-        <x:v>GPT-5.6 Sol xhigh：总分 226、均分 75.33；基础计算与归约有价值，题 1 目标错配和题 3 低频缺口明显。</x:v>
-      </x:c>
-      <x:c r="B157" s="4"/>
-      <x:c r="C157" s="4"/>
-      <x:c r="D157" s="4"/>
-      <x:c r="E157" s="4"/>
-      <x:c r="F157" s="4"/>
-      <x:c r="G157" s="4"/>
-      <x:c r="H157" s="4"/>
-      <x:c r="I157" s="4"/>
-      <x:c r="J157" s="4"/>
-      <x:c r="K157" s="4"/>
+      <x:c r="A157" s="121" t="str">
+        <x:v>GPT-6.1 Sol max</x:v>
+      </x:c>
+      <x:c r="B157" s="122" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C157" s="122" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D157" s="122" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="E157" s="122" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F157" s="122" t="n">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="G157" s="122" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="H157" s="122" t="n">
+        <x:f>'Task 2'!D11</x:f>
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="I157" s="122" t="n">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="J157" s="122" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="K157" s="122" t="str">
+        <x:v>s2_2b</x:v>
+      </x:c>
       <x:c r="L157" s="2"/>
       <x:c r="M157" s="2"/>
       <x:c r="N157" s="2"/>
@@ -8800,19 +9633,40 @@
       <x:c r="V157" s="2"/>
     </x:row>
     <x:row r="158" ht="21" customHeight="1">
-      <x:c r="A158" s="4" t="str">
-        <x:v>GPT-6 Luna max：总分 215、均分 71.67，三题合计 $0.464；低成本优势明显，题 1 核心证书失效。</x:v>
-      </x:c>
-      <x:c r="B158" s="4"/>
-      <x:c r="C158" s="4"/>
-      <x:c r="D158" s="4"/>
-      <x:c r="E158" s="4"/>
-      <x:c r="F158" s="4"/>
-      <x:c r="G158" s="4"/>
-      <x:c r="H158" s="4"/>
-      <x:c r="I158" s="4"/>
-      <x:c r="J158" s="4"/>
-      <x:c r="K158" s="4"/>
+      <x:c r="A158" s="2" t="str">
+        <x:v>GPT-5.6 Sol xhigh</x:v>
+      </x:c>
+      <x:c r="B158" s="12" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C158" s="12" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="D158" s="12" t="n">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E158" s="12" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="F158" s="12" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="G158" s="12" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="H158" s="12" t="n">
+        <x:f>'Task 3'!D2</x:f>
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="I158" s="12" t="n">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="J158" s="12" t="n">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="K158" s="12" t="str">
+        <x:v>3a</x:v>
+      </x:c>
       <x:c r="L158" s="2"/>
       <x:c r="M158" s="2"/>
       <x:c r="N158" s="2"/>
@@ -8826,19 +9680,40 @@
       <x:c r="V158" s="2"/>
     </x:row>
     <x:row r="159" ht="21" customHeight="1">
-      <x:c r="A159" s="4" t="str">
-        <x:v>DeepSeek V4.1 Flash max：总分 176、均分 58.67；部分结构正确，关键输入、推论与统一性验证不足。</x:v>
-      </x:c>
-      <x:c r="B159" s="4"/>
-      <x:c r="C159" s="4"/>
-      <x:c r="D159" s="4"/>
-      <x:c r="E159" s="4"/>
-      <x:c r="F159" s="4"/>
-      <x:c r="G159" s="4"/>
-      <x:c r="H159" s="4"/>
-      <x:c r="I159" s="4"/>
-      <x:c r="J159" s="4"/>
-      <x:c r="K159" s="4"/>
+      <x:c r="A159" s="121" t="str">
+        <x:v>GPT-6 Luna max</x:v>
+      </x:c>
+      <x:c r="B159" s="122" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C159" s="122" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D159" s="122" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="E159" s="122" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="F159" s="122" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="G159" s="122" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="H159" s="122" t="n">
+        <x:f>'Task 3'!D3</x:f>
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="I159" s="122" t="n">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="J159" s="122" t="n">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="K159" s="122" t="str">
+        <x:v>3b</x:v>
+      </x:c>
       <x:c r="L159" s="2"/>
       <x:c r="M159" s="2"/>
       <x:c r="N159" s="2"/>
@@ -8852,19 +9727,40 @@
       <x:c r="V159" s="2"/>
     </x:row>
     <x:row r="160" ht="21" customHeight="1">
-      <x:c r="A160" s="4" t="str">
-        <x:v>Grok 4.7 high：总分 169、均分 56.33；有局部正确结果，树级相位和恢复基线等校准错误限制结论。</x:v>
-      </x:c>
-      <x:c r="B160" s="4"/>
-      <x:c r="C160" s="4"/>
-      <x:c r="D160" s="4"/>
-      <x:c r="E160" s="4"/>
-      <x:c r="F160" s="4"/>
-      <x:c r="G160" s="4"/>
-      <x:c r="H160" s="4"/>
-      <x:c r="I160" s="4"/>
-      <x:c r="J160" s="4"/>
-      <x:c r="K160" s="4"/>
+      <x:c r="A160" s="2" t="str">
+        <x:v>GPT-6 Sol max</x:v>
+      </x:c>
+      <x:c r="B160" s="12" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C160" s="12" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D160" s="12" t="n">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="E160" s="12" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="F160" s="12" t="n">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="G160" s="12" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="H160" s="12" t="n">
+        <x:f>'Task 3'!D4</x:f>
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="I160" s="12" t="n">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="J160" s="12" t="n">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="K160" s="12" t="str">
+        <x:v>3c</x:v>
+      </x:c>
       <x:c r="L160" s="2"/>
       <x:c r="M160" s="2"/>
       <x:c r="N160" s="2"/>
@@ -8878,17 +9774,40 @@
       <x:c r="V160" s="2"/>
     </x:row>
     <x:row r="161" ht="21" customHeight="1">
-      <x:c r="A161" s="2"/>
-      <x:c r="B161" s="2"/>
-      <x:c r="C161" s="2"/>
-      <x:c r="D161" s="2"/>
-      <x:c r="E161" s="2"/>
-      <x:c r="F161" s="2"/>
-      <x:c r="G161" s="2"/>
-      <x:c r="H161" s="2"/>
-      <x:c r="I161" s="2"/>
-      <x:c r="J161" s="2"/>
-      <x:c r="K161" s="2"/>
+      <x:c r="A161" s="121" t="str">
+        <x:v>GPT-6 Sol xhigh</x:v>
+      </x:c>
+      <x:c r="B161" s="122" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C161" s="122" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D161" s="122" t="n">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="E161" s="122" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="F161" s="122" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="G161" s="122" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="H161" s="122" t="n">
+        <x:f>'Task 3'!D5</x:f>
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="I161" s="122" t="n">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="J161" s="122" t="n">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="K161" s="122" t="str">
+        <x:v>3d</x:v>
+      </x:c>
       <x:c r="L161" s="2"/>
       <x:c r="M161" s="2"/>
       <x:c r="N161" s="2"/>
@@ -8902,17 +9821,40 @@
       <x:c r="V161" s="2"/>
     </x:row>
     <x:row r="162" ht="21" customHeight="1">
-      <x:c r="A162" s="2"/>
-      <x:c r="B162" s="2"/>
-      <x:c r="C162" s="2"/>
-      <x:c r="D162" s="2"/>
-      <x:c r="E162" s="2"/>
-      <x:c r="F162" s="2"/>
-      <x:c r="G162" s="2"/>
-      <x:c r="H162" s="2"/>
-      <x:c r="I162" s="2"/>
-      <x:c r="J162" s="2"/>
-      <x:c r="K162" s="2"/>
+      <x:c r="A162" s="2" t="str">
+        <x:v>GPT-6 Astra high</x:v>
+      </x:c>
+      <x:c r="B162" s="12" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C162" s="12" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D162" s="12" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="E162" s="12" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F162" s="12" t="n">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="G162" s="12" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="H162" s="12" t="n">
+        <x:f>'Task 3'!D6</x:f>
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="I162" s="12" t="n">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="J162" s="12" t="n">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="K162" s="12" t="str">
+        <x:v>3e</x:v>
+      </x:c>
       <x:c r="L162" s="2"/>
       <x:c r="M162" s="2"/>
       <x:c r="N162" s="2"/>
@@ -8926,17 +9868,40 @@
       <x:c r="V162" s="2"/>
     </x:row>
     <x:row r="163" ht="21" customHeight="1">
-      <x:c r="A163" s="2"/>
-      <x:c r="B163" s="2"/>
-      <x:c r="C163" s="2"/>
-      <x:c r="D163" s="2"/>
-      <x:c r="E163" s="2"/>
-      <x:c r="F163" s="2"/>
-      <x:c r="G163" s="2"/>
-      <x:c r="H163" s="2"/>
-      <x:c r="I163" s="2"/>
-      <x:c r="J163" s="2"/>
-      <x:c r="K163" s="2"/>
+      <x:c r="A163" s="121" t="str">
+        <x:v>Grok 4.7 high</x:v>
+      </x:c>
+      <x:c r="B163" s="122" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C163" s="122" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="D163" s="122" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="E163" s="122" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="F163" s="122" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="G163" s="122" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="H163" s="122" t="n">
+        <x:f>'Task 3'!D7</x:f>
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="I163" s="122" t="n">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="J163" s="122" t="n">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="K163" s="122" t="str">
+        <x:v>3f</x:v>
+      </x:c>
       <x:c r="L163" s="2"/>
       <x:c r="M163" s="2"/>
       <x:c r="N163" s="2"/>
@@ -8950,17 +9915,40 @@
       <x:c r="V163" s="2"/>
     </x:row>
     <x:row r="164" ht="21" customHeight="1">
-      <x:c r="A164" s="2"/>
-      <x:c r="B164" s="2"/>
-      <x:c r="C164" s="2"/>
-      <x:c r="D164" s="2"/>
-      <x:c r="E164" s="2"/>
-      <x:c r="F164" s="2"/>
-      <x:c r="G164" s="2"/>
-      <x:c r="H164" s="2"/>
-      <x:c r="I164" s="2"/>
-      <x:c r="J164" s="2"/>
-      <x:c r="K164" s="2"/>
+      <x:c r="A164" s="2" t="str">
+        <x:v>Opus 5.5 xhigh</x:v>
+      </x:c>
+      <x:c r="B164" s="12" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C164" s="12" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="D164" s="12" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E164" s="12" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F164" s="12" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="G164" s="12" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="H164" s="12" t="n">
+        <x:f>'Task 3'!D8</x:f>
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="I164" s="12" t="n">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="J164" s="12" t="n">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="K164" s="12" t="str">
+        <x:v>s_3a</x:v>
+      </x:c>
       <x:c r="L164" s="2"/>
       <x:c r="M164" s="2"/>
       <x:c r="N164" s="2"/>
@@ -8974,17 +9962,40 @@
       <x:c r="V164" s="2"/>
     </x:row>
     <x:row r="165" ht="21" customHeight="1">
-      <x:c r="A165" s="2"/>
-      <x:c r="B165" s="2"/>
-      <x:c r="C165" s="2"/>
-      <x:c r="D165" s="2"/>
-      <x:c r="E165" s="2"/>
-      <x:c r="F165" s="2"/>
-      <x:c r="G165" s="2"/>
-      <x:c r="H165" s="2"/>
-      <x:c r="I165" s="2"/>
-      <x:c r="J165" s="2"/>
-      <x:c r="K165" s="2"/>
+      <x:c r="A165" s="121" t="str">
+        <x:v>DeepSeek V4.1 Flash max</x:v>
+      </x:c>
+      <x:c r="B165" s="122" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C165" s="122" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D165" s="122" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="E165" s="122" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="F165" s="122" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="G165" s="122" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H165" s="122" t="n">
+        <x:f>'Task 3'!D9</x:f>
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="I165" s="122" t="n">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="J165" s="122" t="n">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="K165" s="122" t="str">
+        <x:v>s_3b</x:v>
+      </x:c>
       <x:c r="L165" s="2"/>
       <x:c r="M165" s="2"/>
       <x:c r="N165" s="2"/>
@@ -8998,17 +10009,40 @@
       <x:c r="V165" s="2"/>
     </x:row>
     <x:row r="166" ht="21" customHeight="1">
-      <x:c r="A166" s="2"/>
-      <x:c r="B166" s="2"/>
-      <x:c r="C166" s="2"/>
-      <x:c r="D166" s="2"/>
-      <x:c r="E166" s="2"/>
-      <x:c r="F166" s="2"/>
-      <x:c r="G166" s="2"/>
-      <x:c r="H166" s="2"/>
-      <x:c r="I166" s="2"/>
-      <x:c r="J166" s="2"/>
-      <x:c r="K166" s="2"/>
+      <x:c r="A166" s="2" t="str">
+        <x:v>GPT-6.1 Sol xhigh</x:v>
+      </x:c>
+      <x:c r="B166" s="12" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C166" s="12" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D166" s="12" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="E166" s="12" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="F166" s="12" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="G166" s="12" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="H166" s="12" t="n">
+        <x:f>'Task 3'!D10</x:f>
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="I166" s="12" t="n">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="J166" s="12" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="K166" s="12" t="str">
+        <x:v>s2_3a</x:v>
+      </x:c>
       <x:c r="L166" s="2"/>
       <x:c r="M166" s="2"/>
       <x:c r="N166" s="2"/>
@@ -9022,17 +10056,40 @@
       <x:c r="V166" s="2"/>
     </x:row>
     <x:row r="167" ht="21" customHeight="1">
-      <x:c r="A167" s="2"/>
-      <x:c r="B167" s="2"/>
-      <x:c r="C167" s="2"/>
-      <x:c r="D167" s="2"/>
-      <x:c r="E167" s="2"/>
-      <x:c r="F167" s="2"/>
-      <x:c r="G167" s="2"/>
-      <x:c r="H167" s="2"/>
-      <x:c r="I167" s="2"/>
-      <x:c r="J167" s="2"/>
-      <x:c r="K167" s="2"/>
+      <x:c r="A167" s="123" t="str">
+        <x:v>GPT-6.1 Sol max</x:v>
+      </x:c>
+      <x:c r="B167" s="124" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C167" s="124" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D167" s="124" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="E167" s="124" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F167" s="124" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="G167" s="124" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="H167" s="124" t="n">
+        <x:f>'Task 3'!D11</x:f>
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="I167" s="124" t="n">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="J167" s="124" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="K167" s="124" t="str">
+        <x:v>s2_3b</x:v>
+      </x:c>
       <x:c r="L167" s="2"/>
       <x:c r="M167" s="2"/>
       <x:c r="N167" s="2"/>
@@ -9093,18 +10150,20 @@
       <x:c r="U169" s="2"/>
       <x:c r="V169" s="2"/>
     </x:row>
-    <x:row r="170" ht="21" customHeight="1">
-      <x:c r="A170" s="2"/>
-      <x:c r="B170" s="2"/>
-      <x:c r="C170" s="2"/>
-      <x:c r="D170" s="2"/>
-      <x:c r="E170" s="2"/>
-      <x:c r="F170" s="2"/>
-      <x:c r="G170" s="2"/>
-      <x:c r="H170" s="2"/>
-      <x:c r="I170" s="2"/>
-      <x:c r="J170" s="2"/>
-      <x:c r="K170" s="2"/>
+    <x:row r="170" ht="24" customHeight="1">
+      <x:c r="A170" s="27" t="str">
+        <x:v>本次完整样本的模型评价</x:v>
+      </x:c>
+      <x:c r="B170" s="27"/>
+      <x:c r="C170" s="27"/>
+      <x:c r="D170" s="27"/>
+      <x:c r="E170" s="27"/>
+      <x:c r="F170" s="27"/>
+      <x:c r="G170" s="27"/>
+      <x:c r="H170" s="27"/>
+      <x:c r="I170" s="27"/>
+      <x:c r="J170" s="27"/>
+      <x:c r="K170" s="27"/>
       <x:c r="L170" s="2"/>
       <x:c r="M170" s="2"/>
       <x:c r="N170" s="2"/>
@@ -9117,7 +10176,510 @@
       <x:c r="U170" s="2"/>
       <x:c r="V170" s="2"/>
     </x:row>
+    <x:row r="171" ht="21" customHeight="1">
+      <x:c r="A171" s="2"/>
+      <x:c r="B171" s="2"/>
+      <x:c r="C171" s="2"/>
+      <x:c r="D171" s="2"/>
+      <x:c r="E171" s="2"/>
+      <x:c r="F171" s="2"/>
+      <x:c r="G171" s="2"/>
+      <x:c r="H171" s="2"/>
+      <x:c r="I171" s="2"/>
+      <x:c r="J171" s="2"/>
+      <x:c r="K171" s="2"/>
+      <x:c r="L171" s="2"/>
+      <x:c r="M171" s="2"/>
+      <x:c r="N171" s="2"/>
+      <x:c r="O171" s="2"/>
+      <x:c r="P171" s="2"/>
+      <x:c r="Q171" s="2"/>
+      <x:c r="R171" s="2"/>
+      <x:c r="S171" s="2"/>
+      <x:c r="T171" s="2"/>
+      <x:c r="U171" s="2"/>
+      <x:c r="V171" s="2"/>
+    </x:row>
+    <x:row r="172" ht="21" customHeight="1">
+      <x:c r="A172" s="4" t="str">
+        <x:v>GPT-6.1 Sol max：294/300，成本 4.576 USD。均分最高；核空间证书、恢复界及最佳波形幂次成立，验证覆盖较完整。</x:v>
+      </x:c>
+      <x:c r="B172" s="4"/>
+      <x:c r="C172" s="4"/>
+      <x:c r="D172" s="4"/>
+      <x:c r="E172" s="4"/>
+      <x:c r="F172" s="4"/>
+      <x:c r="G172" s="4"/>
+      <x:c r="H172" s="4"/>
+      <x:c r="I172" s="4"/>
+      <x:c r="J172" s="4"/>
+      <x:c r="K172" s="4"/>
+      <x:c r="L172" s="2"/>
+      <x:c r="M172" s="2"/>
+      <x:c r="N172" s="2"/>
+      <x:c r="O172" s="2"/>
+      <x:c r="P172" s="2"/>
+      <x:c r="Q172" s="2"/>
+      <x:c r="R172" s="2"/>
+      <x:c r="S172" s="2"/>
+      <x:c r="T172" s="2"/>
+      <x:c r="U172" s="2"/>
+      <x:c r="V172" s="2"/>
+    </x:row>
+    <x:row r="173" ht="21" customHeight="1">
+      <x:c r="A173" s="4" t="str">
+        <x:v>GPT-6.1 Sol xhigh：291/300，成本 4.094 USD。高分与成本折中突出；比 max 少 3 个总分，费用少 0.482 USD。</x:v>
+      </x:c>
+      <x:c r="B173" s="4"/>
+      <x:c r="C173" s="4"/>
+      <x:c r="D173" s="4"/>
+      <x:c r="E173" s="4"/>
+      <x:c r="F173" s="4"/>
+      <x:c r="G173" s="4"/>
+      <x:c r="H173" s="4"/>
+      <x:c r="I173" s="4"/>
+      <x:c r="J173" s="4"/>
+      <x:c r="K173" s="4"/>
+      <x:c r="L173" s="2"/>
+      <x:c r="M173" s="2"/>
+      <x:c r="N173" s="2"/>
+      <x:c r="O173" s="2"/>
+      <x:c r="P173" s="2"/>
+      <x:c r="Q173" s="2"/>
+      <x:c r="R173" s="2"/>
+      <x:c r="S173" s="2"/>
+      <x:c r="T173" s="2"/>
+      <x:c r="U173" s="2"/>
+      <x:c r="V173" s="2"/>
+    </x:row>
+    <x:row r="174" ht="21" customHeight="1">
+      <x:c r="A174" s="4" t="str">
+        <x:v>GPT-6 Astra high：287/300，成本 14.370 USD。三题证据强；在本次中心分数与成本上被两个 6.1 配置支配。</x:v>
+      </x:c>
+      <x:c r="B174" s="4"/>
+      <x:c r="C174" s="4"/>
+      <x:c r="D174" s="4"/>
+      <x:c r="E174" s="4"/>
+      <x:c r="F174" s="4"/>
+      <x:c r="G174" s="4"/>
+      <x:c r="H174" s="4"/>
+      <x:c r="I174" s="4"/>
+      <x:c r="J174" s="4"/>
+      <x:c r="K174" s="4"/>
+      <x:c r="L174" s="2"/>
+      <x:c r="M174" s="2"/>
+      <x:c r="N174" s="2"/>
+      <x:c r="O174" s="2"/>
+      <x:c r="P174" s="2"/>
+      <x:c r="Q174" s="2"/>
+      <x:c r="R174" s="2"/>
+      <x:c r="S174" s="2"/>
+      <x:c r="T174" s="2"/>
+      <x:c r="U174" s="2"/>
+      <x:c r="V174" s="2"/>
+    </x:row>
+    <x:row r="175" ht="21" customHeight="1">
+      <x:c r="A175" s="4" t="str">
+        <x:v>GPT-6 Sol max：283/300，成本 8.252 USD。三题均衡且 ≥94；新 6.1 配置以更低成本取得更高分数。</x:v>
+      </x:c>
+      <x:c r="B175" s="4"/>
+      <x:c r="C175" s="4"/>
+      <x:c r="D175" s="4"/>
+      <x:c r="E175" s="4"/>
+      <x:c r="F175" s="4"/>
+      <x:c r="G175" s="4"/>
+      <x:c r="H175" s="4"/>
+      <x:c r="I175" s="4"/>
+      <x:c r="J175" s="4"/>
+      <x:c r="K175" s="4"/>
+      <x:c r="L175" s="2"/>
+      <x:c r="M175" s="2"/>
+      <x:c r="N175" s="2"/>
+      <x:c r="O175" s="2"/>
+      <x:c r="P175" s="2"/>
+      <x:c r="Q175" s="2"/>
+      <x:c r="R175" s="2"/>
+      <x:c r="S175" s="2"/>
+      <x:c r="T175" s="2"/>
+      <x:c r="U175" s="2"/>
+      <x:c r="V175" s="2"/>
+    </x:row>
+    <x:row r="176" ht="21" customHeight="1">
+      <x:c r="A176" s="4" t="str">
+        <x:v>Opus 5.5 xhigh：261/300，成本 50.770 USD。有价值的低点与解析归约；一般化论证和较高成本限制本次竞争力。</x:v>
+      </x:c>
+      <x:c r="B176" s="4"/>
+      <x:c r="C176" s="4"/>
+      <x:c r="D176" s="4"/>
+      <x:c r="E176" s="4"/>
+      <x:c r="F176" s="4"/>
+      <x:c r="G176" s="4"/>
+      <x:c r="H176" s="4"/>
+      <x:c r="I176" s="4"/>
+      <x:c r="J176" s="4"/>
+      <x:c r="K176" s="4"/>
+      <x:c r="L176" s="2"/>
+      <x:c r="M176" s="2"/>
+      <x:c r="N176" s="2"/>
+      <x:c r="O176" s="2"/>
+      <x:c r="P176" s="2"/>
+      <x:c r="Q176" s="2"/>
+      <x:c r="R176" s="2"/>
+      <x:c r="S176" s="2"/>
+      <x:c r="T176" s="2"/>
+      <x:c r="U176" s="2"/>
+      <x:c r="V176" s="2"/>
+    </x:row>
+    <x:row r="177" ht="21" customHeight="1">
+      <x:c r="A177" s="4" t="str">
+        <x:v>GPT-6 Sol xhigh：236/300，成本 6.184 USD。题 2、3 较强；题 1 的关键输入错误进入核心证书，跨题差异明显。</x:v>
+      </x:c>
+      <x:c r="B177" s="4"/>
+      <x:c r="C177" s="4"/>
+      <x:c r="D177" s="4"/>
+      <x:c r="E177" s="4"/>
+      <x:c r="F177" s="4"/>
+      <x:c r="G177" s="4"/>
+      <x:c r="H177" s="4"/>
+      <x:c r="I177" s="4"/>
+      <x:c r="J177" s="4"/>
+      <x:c r="K177" s="4"/>
+      <x:c r="L177" s="2"/>
+      <x:c r="M177" s="2"/>
+      <x:c r="N177" s="2"/>
+      <x:c r="O177" s="2"/>
+      <x:c r="P177" s="2"/>
+      <x:c r="Q177" s="2"/>
+      <x:c r="R177" s="2"/>
+      <x:c r="S177" s="2"/>
+      <x:c r="T177" s="2"/>
+      <x:c r="U177" s="2"/>
+      <x:c r="V177" s="2"/>
+    </x:row>
+    <x:row r="178" ht="21" customHeight="1">
+      <x:c r="A178" s="4" t="str">
+        <x:v>GPT-5.6 Sol xhigh：226/300，成本 20.805 USD。部分计算正确；目标错配和低频缺口限制结论，记录成本较高。</x:v>
+      </x:c>
+      <x:c r="B178" s="4"/>
+      <x:c r="C178" s="4"/>
+      <x:c r="D178" s="4"/>
+      <x:c r="E178" s="4"/>
+      <x:c r="F178" s="4"/>
+      <x:c r="G178" s="4"/>
+      <x:c r="H178" s="4"/>
+      <x:c r="I178" s="4"/>
+      <x:c r="J178" s="4"/>
+      <x:c r="K178" s="4"/>
+      <x:c r="L178" s="2"/>
+      <x:c r="M178" s="2"/>
+      <x:c r="N178" s="2"/>
+      <x:c r="O178" s="2"/>
+      <x:c r="P178" s="2"/>
+      <x:c r="Q178" s="2"/>
+      <x:c r="R178" s="2"/>
+      <x:c r="S178" s="2"/>
+      <x:c r="T178" s="2"/>
+      <x:c r="U178" s="2"/>
+      <x:c r="V178" s="2"/>
+    </x:row>
+    <x:row r="179" ht="21" customHeight="1">
+      <x:c r="A179" s="4" t="str">
+        <x:v>GPT-6 Luna max：215/300，成本 0.464 USD。最低成本的完整配置；题 2 基础与局部恢复结果较强，研究层仍有缺口。</x:v>
+      </x:c>
+      <x:c r="B179" s="4"/>
+      <x:c r="C179" s="4"/>
+      <x:c r="D179" s="4"/>
+      <x:c r="E179" s="4"/>
+      <x:c r="F179" s="4"/>
+      <x:c r="G179" s="4"/>
+      <x:c r="H179" s="4"/>
+      <x:c r="I179" s="4"/>
+      <x:c r="J179" s="4"/>
+      <x:c r="K179" s="4"/>
+      <x:c r="L179" s="2"/>
+      <x:c r="M179" s="2"/>
+      <x:c r="N179" s="2"/>
+      <x:c r="O179" s="2"/>
+      <x:c r="P179" s="2"/>
+      <x:c r="Q179" s="2"/>
+      <x:c r="R179" s="2"/>
+      <x:c r="S179" s="2"/>
+      <x:c r="T179" s="2"/>
+      <x:c r="U179" s="2"/>
+      <x:c r="V179" s="2"/>
+    </x:row>
+    <x:row r="180" ht="21" customHeight="1">
+      <x:c r="A180" s="4" t="str">
+        <x:v>DeepSeek V4.1 Flash max：176/300，成本 1.321 USD。部分结构成立，但核心输入与统一性推论不足；本次被 Luna 逐题支配。</x:v>
+      </x:c>
+      <x:c r="B180" s="4"/>
+      <x:c r="C180" s="4"/>
+      <x:c r="D180" s="4"/>
+      <x:c r="E180" s="4"/>
+      <x:c r="F180" s="4"/>
+      <x:c r="G180" s="4"/>
+      <x:c r="H180" s="4"/>
+      <x:c r="I180" s="4"/>
+      <x:c r="J180" s="4"/>
+      <x:c r="K180" s="4"/>
+      <x:c r="L180" s="2"/>
+      <x:c r="M180" s="2"/>
+      <x:c r="N180" s="2"/>
+      <x:c r="O180" s="2"/>
+      <x:c r="P180" s="2"/>
+      <x:c r="Q180" s="2"/>
+      <x:c r="R180" s="2"/>
+      <x:c r="S180" s="2"/>
+      <x:c r="T180" s="2"/>
+      <x:c r="U180" s="2"/>
+      <x:c r="V180" s="2"/>
+    </x:row>
+    <x:row r="181" ht="21" customHeight="1">
+      <x:c r="A181" s="4" t="str">
+        <x:v>Grok 4.7 high：169/300，成本 14.676 USD。有局部正确计算；树级相位与恢复基线等校准问题影响主要结论。</x:v>
+      </x:c>
+      <x:c r="B181" s="4"/>
+      <x:c r="C181" s="4"/>
+      <x:c r="D181" s="4"/>
+      <x:c r="E181" s="4"/>
+      <x:c r="F181" s="4"/>
+      <x:c r="G181" s="4"/>
+      <x:c r="H181" s="4"/>
+      <x:c r="I181" s="4"/>
+      <x:c r="J181" s="4"/>
+      <x:c r="K181" s="4"/>
+      <x:c r="L181" s="2"/>
+      <x:c r="M181" s="2"/>
+      <x:c r="N181" s="2"/>
+      <x:c r="O181" s="2"/>
+      <x:c r="P181" s="2"/>
+      <x:c r="Q181" s="2"/>
+      <x:c r="R181" s="2"/>
+      <x:c r="S181" s="2"/>
+      <x:c r="T181" s="2"/>
+      <x:c r="U181" s="2"/>
+      <x:c r="V181" s="2"/>
+    </x:row>
+    <x:row r="182" ht="21" customHeight="1">
+      <x:c r="A182" s="2"/>
+      <x:c r="B182" s="2"/>
+      <x:c r="C182" s="2"/>
+      <x:c r="D182" s="2"/>
+      <x:c r="E182" s="2"/>
+      <x:c r="F182" s="2"/>
+      <x:c r="G182" s="2"/>
+      <x:c r="H182" s="2"/>
+      <x:c r="I182" s="2"/>
+      <x:c r="J182" s="2"/>
+      <x:c r="K182" s="2"/>
+      <x:c r="L182" s="2"/>
+      <x:c r="M182" s="2"/>
+      <x:c r="N182" s="2"/>
+      <x:c r="O182" s="2"/>
+      <x:c r="P182" s="2"/>
+      <x:c r="Q182" s="2"/>
+      <x:c r="R182" s="2"/>
+      <x:c r="S182" s="2"/>
+      <x:c r="T182" s="2"/>
+      <x:c r="U182" s="2"/>
+      <x:c r="V182" s="2"/>
+    </x:row>
+    <x:row r="183" ht="21" customHeight="1">
+      <x:c r="A183" s="2"/>
+      <x:c r="B183" s="2"/>
+      <x:c r="C183" s="2"/>
+      <x:c r="D183" s="2"/>
+      <x:c r="E183" s="2"/>
+      <x:c r="F183" s="2"/>
+      <x:c r="G183" s="2"/>
+      <x:c r="H183" s="2"/>
+      <x:c r="I183" s="2"/>
+      <x:c r="J183" s="2"/>
+      <x:c r="K183" s="2"/>
+      <x:c r="L183" s="2"/>
+      <x:c r="M183" s="2"/>
+      <x:c r="N183" s="2"/>
+      <x:c r="O183" s="2"/>
+      <x:c r="P183" s="2"/>
+      <x:c r="Q183" s="2"/>
+      <x:c r="R183" s="2"/>
+      <x:c r="S183" s="2"/>
+      <x:c r="T183" s="2"/>
+      <x:c r="U183" s="2"/>
+      <x:c r="V183" s="2"/>
+    </x:row>
+    <x:row r="184" ht="21" customHeight="1">
+      <x:c r="A184" s="2"/>
+      <x:c r="B184" s="2"/>
+      <x:c r="C184" s="2"/>
+      <x:c r="D184" s="2"/>
+      <x:c r="E184" s="2"/>
+      <x:c r="F184" s="2"/>
+      <x:c r="G184" s="2"/>
+      <x:c r="H184" s="2"/>
+      <x:c r="I184" s="2"/>
+      <x:c r="J184" s="2"/>
+      <x:c r="K184" s="2"/>
+      <x:c r="L184" s="2"/>
+      <x:c r="M184" s="2"/>
+      <x:c r="N184" s="2"/>
+      <x:c r="O184" s="2"/>
+      <x:c r="P184" s="2"/>
+      <x:c r="Q184" s="2"/>
+      <x:c r="R184" s="2"/>
+      <x:c r="S184" s="2"/>
+      <x:c r="T184" s="2"/>
+      <x:c r="U184" s="2"/>
+      <x:c r="V184" s="2"/>
+    </x:row>
+    <x:row r="185" ht="21" customHeight="1">
+      <x:c r="A185" s="2"/>
+      <x:c r="B185" s="2"/>
+      <x:c r="C185" s="2"/>
+      <x:c r="D185" s="2"/>
+      <x:c r="E185" s="2"/>
+      <x:c r="F185" s="2"/>
+      <x:c r="G185" s="2"/>
+      <x:c r="H185" s="2"/>
+      <x:c r="I185" s="2"/>
+      <x:c r="J185" s="2"/>
+      <x:c r="K185" s="2"/>
+      <x:c r="L185" s="2"/>
+      <x:c r="M185" s="2"/>
+      <x:c r="N185" s="2"/>
+      <x:c r="O185" s="2"/>
+      <x:c r="P185" s="2"/>
+      <x:c r="Q185" s="2"/>
+      <x:c r="R185" s="2"/>
+      <x:c r="S185" s="2"/>
+      <x:c r="T185" s="2"/>
+      <x:c r="U185" s="2"/>
+      <x:c r="V185" s="2"/>
+    </x:row>
+    <x:row r="186" ht="21" customHeight="1">
+      <x:c r="A186" s="2"/>
+      <x:c r="B186" s="2"/>
+      <x:c r="C186" s="2"/>
+      <x:c r="D186" s="2"/>
+      <x:c r="E186" s="2"/>
+      <x:c r="F186" s="2"/>
+      <x:c r="G186" s="2"/>
+      <x:c r="H186" s="2"/>
+      <x:c r="I186" s="2"/>
+      <x:c r="J186" s="2"/>
+      <x:c r="K186" s="2"/>
+      <x:c r="L186" s="2"/>
+      <x:c r="M186" s="2"/>
+      <x:c r="N186" s="2"/>
+      <x:c r="O186" s="2"/>
+      <x:c r="P186" s="2"/>
+      <x:c r="Q186" s="2"/>
+      <x:c r="R186" s="2"/>
+      <x:c r="S186" s="2"/>
+      <x:c r="T186" s="2"/>
+      <x:c r="U186" s="2"/>
+      <x:c r="V186" s="2"/>
+    </x:row>
+    <x:row r="187" ht="21" customHeight="1">
+      <x:c r="A187" s="2"/>
+      <x:c r="B187" s="2"/>
+      <x:c r="C187" s="2"/>
+      <x:c r="D187" s="2"/>
+      <x:c r="E187" s="2"/>
+      <x:c r="F187" s="2"/>
+      <x:c r="G187" s="2"/>
+      <x:c r="H187" s="2"/>
+      <x:c r="I187" s="2"/>
+      <x:c r="J187" s="2"/>
+      <x:c r="K187" s="2"/>
+      <x:c r="L187" s="2"/>
+      <x:c r="M187" s="2"/>
+      <x:c r="N187" s="2"/>
+      <x:c r="O187" s="2"/>
+      <x:c r="P187" s="2"/>
+      <x:c r="Q187" s="2"/>
+      <x:c r="R187" s="2"/>
+      <x:c r="S187" s="2"/>
+      <x:c r="T187" s="2"/>
+      <x:c r="U187" s="2"/>
+      <x:c r="V187" s="2"/>
+    </x:row>
+    <x:row r="188" ht="21" customHeight="1">
+      <x:c r="A188" s="2"/>
+      <x:c r="B188" s="2"/>
+      <x:c r="C188" s="2"/>
+      <x:c r="D188" s="2"/>
+      <x:c r="E188" s="2"/>
+      <x:c r="F188" s="2"/>
+      <x:c r="G188" s="2"/>
+      <x:c r="H188" s="2"/>
+      <x:c r="I188" s="2"/>
+      <x:c r="J188" s="2"/>
+      <x:c r="K188" s="2"/>
+      <x:c r="L188" s="2"/>
+      <x:c r="M188" s="2"/>
+      <x:c r="N188" s="2"/>
+      <x:c r="O188" s="2"/>
+      <x:c r="P188" s="2"/>
+      <x:c r="Q188" s="2"/>
+      <x:c r="R188" s="2"/>
+      <x:c r="S188" s="2"/>
+      <x:c r="T188" s="2"/>
+      <x:c r="U188" s="2"/>
+      <x:c r="V188" s="2"/>
+    </x:row>
+    <x:row r="189" ht="21" customHeight="1">
+      <x:c r="A189" s="2"/>
+      <x:c r="B189" s="2"/>
+      <x:c r="C189" s="2"/>
+      <x:c r="D189" s="2"/>
+      <x:c r="E189" s="2"/>
+      <x:c r="F189" s="2"/>
+      <x:c r="G189" s="2"/>
+      <x:c r="H189" s="2"/>
+      <x:c r="I189" s="2"/>
+      <x:c r="J189" s="2"/>
+      <x:c r="K189" s="2"/>
+      <x:c r="L189" s="2"/>
+      <x:c r="M189" s="2"/>
+      <x:c r="N189" s="2"/>
+      <x:c r="O189" s="2"/>
+      <x:c r="P189" s="2"/>
+      <x:c r="Q189" s="2"/>
+      <x:c r="R189" s="2"/>
+      <x:c r="S189" s="2"/>
+      <x:c r="T189" s="2"/>
+      <x:c r="U189" s="2"/>
+      <x:c r="V189" s="2"/>
+    </x:row>
+    <x:row r="190" ht="21" customHeight="1">
+      <x:c r="A190" s="2"/>
+      <x:c r="B190" s="2"/>
+      <x:c r="C190" s="2"/>
+      <x:c r="D190" s="2"/>
+      <x:c r="E190" s="2"/>
+      <x:c r="F190" s="2"/>
+      <x:c r="G190" s="2"/>
+      <x:c r="H190" s="2"/>
+      <x:c r="I190" s="2"/>
+      <x:c r="J190" s="2"/>
+      <x:c r="K190" s="2"/>
+      <x:c r="L190" s="2"/>
+      <x:c r="M190" s="2"/>
+      <x:c r="N190" s="2"/>
+      <x:c r="O190" s="2"/>
+      <x:c r="P190" s="2"/>
+      <x:c r="Q190" s="2"/>
+      <x:c r="R190" s="2"/>
+      <x:c r="S190" s="2"/>
+      <x:c r="T190" s="2"/>
+      <x:c r="U190" s="2"/>
+      <x:c r="V190" s="2"/>
+    </x:row>
   </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A32:K32"/>
+  </x:mergeCells>
   <x:conditionalFormatting sqref="G19:G25">
     <x:cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="前沿"/>
   </x:conditionalFormatting>
@@ -9128,7 +10690,12 @@
     <x:cfRule type="containsText" dxfId="2" priority="3" operator="containsText" text="前沿"/>
     <x:cfRule type="containsText" dxfId="3" priority="4" operator="containsText" text="前沿"/>
   </x:conditionalFormatting>
+  <x:conditionalFormatting sqref="I21:I30">
+    <x:cfRule type="containsText" dxfId="4" priority="5" operator="containsText" text="前沿"/>
+    <x:cfRule type="containsText" dxfId="5" priority="6" operator="containsText" text="前沿"/>
+    <x:cfRule type="containsText" dxfId="6" priority="7" operator="containsText" text="前沿"/>
+  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4a21b6f095044f5d"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R927b918ad3484b22"/>
 </x:worksheet>
 </file>